--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D966856E-D91B-469E-BA8C-4B13F7224680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A807CA1-E8EC-4409-B334-B288C284BE3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -8663,7 +8663,7 @@
         <v>46176.468981481485</v>
       </c>
       <c r="J289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K289" t="s">
         <v>11</v>
@@ -8692,7 +8692,7 @@
         <v>46176.468981481485</v>
       </c>
       <c r="J290">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K290" t="s">
         <v>11</v>
@@ -8721,7 +8721,7 @@
         <v>46176.469675925924</v>
       </c>
       <c r="J291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K291" t="s">
         <v>11</v>
@@ -8750,7 +8750,7 @@
         <v>46176.469675925924</v>
       </c>
       <c r="J292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K292" t="s">
         <v>11</v>
@@ -8779,7 +8779,7 @@
         <v>46176.469675925924</v>
       </c>
       <c r="J293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K293" t="s">
         <v>11</v>
@@ -8808,7 +8808,7 @@
         <v>46176.470370370371</v>
       </c>
       <c r="J294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K294" t="s">
         <v>11</v>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8BE8625-1B3F-4902-BC96-5C1C0B7D21B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B37EBA-D930-4F6E-97B8-E70CCB13917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,6 +86,9 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -98,10 +101,16 @@
     <t>Space Management-Big 5</t>
   </si>
   <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -113,34 +122,37 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Safe Lifting for Commercial Drivers</t>
-  </si>
-  <si>
     <t>DNU-Driver Health</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
-    <t>In Cab Distractions</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
+    <t>Fatigue</t>
   </si>
   <si>
     <t>Micro-Learn Space Mangement</t>
   </si>
   <si>
-    <t>Work Zone Safety</t>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>Fire Extinguisher Training for CDL</t>
+    <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
-    <t>Vehicle &amp; Roadside Inspections CMV</t>
+    <t>DNU-Speed Management</t>
+  </si>
+  <si>
+    <t>DNU-Def.Drive Distracted Driving</t>
+  </si>
+  <si>
+    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Edington Wrecker Service</t>
@@ -185,19 +197,7 @@
     <t>Scott Comer</t>
   </si>
   <si>
-    <t>DNU-Def.Drive Distracted Driving</t>
-  </si>
-  <si>
-    <t>DNU-Speed Management</t>
-  </si>
-  <si>
     <t>DNUNEW-Space Management Big 5</t>
-  </si>
-  <si>
-    <t>Scene of an Accident</t>
-  </si>
-  <si>
-    <t>Fatigue</t>
   </si>
 </sst>
 </file>
@@ -571,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -620,16 +620,16 @@
     </row>
     <row r="2" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>849</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -649,16 +649,16 @@
     </row>
     <row r="3" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3">
         <v>1133</v>
       </c>
       <c r="F3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -678,16 +678,16 @@
     </row>
     <row r="4" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>1134</v>
       </c>
       <c r="F4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -707,16 +707,16 @@
     </row>
     <row r="5" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5">
         <v>855</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -736,16 +736,16 @@
     </row>
     <row r="6" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6">
         <v>852</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -765,16 +765,16 @@
     </row>
     <row r="7" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7">
         <v>1135</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -794,16 +794,16 @@
     </row>
     <row r="8" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8">
         <v>980</v>
       </c>
       <c r="F8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -823,16 +823,16 @@
     </row>
     <row r="9" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9">
         <v>851</v>
       </c>
       <c r="F9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -852,16 +852,16 @@
     </row>
     <row r="10" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10">
         <v>1136</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -881,16 +881,16 @@
     </row>
     <row r="11" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>981</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -910,16 +910,16 @@
     </row>
     <row r="12" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12">
         <v>848</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -939,16 +939,16 @@
     </row>
     <row r="13" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13">
         <v>1137</v>
       </c>
       <c r="F13" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -968,16 +968,16 @@
     </row>
     <row r="14" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>854</v>
       </c>
       <c r="F14" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -997,16 +997,16 @@
     </row>
     <row r="15" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D15" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E15">
         <v>1138</v>
       </c>
       <c r="F15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1026,16 +1026,16 @@
     </row>
     <row r="16" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16">
         <v>850</v>
       </c>
       <c r="F16" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1055,16 +1055,16 @@
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D17" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E17">
         <v>1139</v>
       </c>
       <c r="F17" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1084,16 +1084,16 @@
     </row>
     <row r="18" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D18" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18">
         <v>853</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1113,16 +1113,16 @@
     </row>
     <row r="19" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E19">
         <v>1140</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1142,16 +1142,16 @@
     </row>
     <row r="20" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D20" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20">
         <v>849</v>
       </c>
       <c r="F20" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>13</v>
@@ -1171,16 +1171,16 @@
     </row>
     <row r="21" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D21" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21">
         <v>855</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>12</v>
@@ -1204,21 +1204,21 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D23" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E23">
         <v>852</v>
       </c>
       <c r="F23" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>13</v>
@@ -1238,16 +1238,16 @@
     </row>
     <row r="24" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D24" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24">
         <v>980</v>
       </c>
       <c r="F24" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>14</v>
@@ -1271,21 +1271,21 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D26" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E26">
         <v>851</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>13</v>
@@ -1305,16 +1305,16 @@
     </row>
     <row r="27" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E27">
         <v>981</v>
       </c>
       <c r="F27" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1334,16 +1334,16 @@
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E28">
         <v>848</v>
       </c>
       <c r="F28" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>13</v>
@@ -1363,16 +1363,16 @@
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E29">
         <v>854</v>
       </c>
       <c r="F29" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1392,16 +1392,16 @@
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30">
         <v>850</v>
       </c>
       <c r="F30" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>13</v>
@@ -1421,16 +1421,16 @@
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D31" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31">
         <v>853</v>
       </c>
       <c r="F31" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>13</v>
@@ -1450,16 +1450,16 @@
     </row>
     <row r="32" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D32" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E32">
         <v>849</v>
       </c>
       <c r="F32" t="s">
+        <v>39</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1479,16 +1479,16 @@
     </row>
     <row r="33" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D33" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E33">
         <v>855</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>12</v>
@@ -1512,21 +1512,21 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E35">
         <v>852</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1546,16 +1546,16 @@
     </row>
     <row r="36" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D36" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E36">
         <v>980</v>
       </c>
       <c r="F36" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>12</v>
@@ -1579,21 +1579,21 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D38" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E38">
         <v>851</v>
       </c>
       <c r="F38" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>13</v>
@@ -1613,16 +1613,16 @@
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D39" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E39">
         <v>981</v>
       </c>
       <c r="F39" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1642,16 +1642,16 @@
     </row>
     <row r="40" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E40">
         <v>848</v>
       </c>
       <c r="F40" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>13</v>
@@ -1671,16 +1671,16 @@
     </row>
     <row r="41" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E41">
         <v>854</v>
       </c>
       <c r="F41" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>12</v>
@@ -1704,21 +1704,21 @@
       <c r="J42" s="2"/>
       <c r="K42" s="1"/>
       <c r="M42" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D43" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E43">
         <v>850</v>
       </c>
       <c r="F43" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>13</v>
@@ -1738,16 +1738,16 @@
     </row>
     <row r="44" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E44">
         <v>853</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>13</v>
@@ -1767,16 +1767,16 @@
     </row>
     <row r="45" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E45">
         <v>849</v>
       </c>
       <c r="F45" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>13</v>
@@ -1796,16 +1796,16 @@
     </row>
     <row r="46" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D46" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E46">
         <v>855</v>
       </c>
       <c r="F46" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>12</v>
@@ -1829,21 +1829,21 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D48" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E48">
         <v>852</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>12</v>
@@ -1867,21 +1867,21 @@
       <c r="J49" s="2"/>
       <c r="K49" s="1"/>
       <c r="M49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D50" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E50">
         <v>980</v>
       </c>
       <c r="F50" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I50" s="1" t="s">
         <v>10</v>
@@ -1901,16 +1901,16 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E51">
         <v>851</v>
       </c>
       <c r="F51" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -1930,16 +1930,16 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E52">
         <v>981</v>
       </c>
       <c r="F52" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -1959,16 +1959,16 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D53" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E53">
         <v>848</v>
       </c>
       <c r="F53" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>13</v>
@@ -1988,16 +1988,16 @@
     </row>
     <row r="54" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E54">
         <v>854</v>
       </c>
       <c r="F54" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>13</v>
@@ -2017,16 +2017,16 @@
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D55" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E55">
         <v>850</v>
       </c>
       <c r="F55" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>12</v>
@@ -2050,21 +2050,21 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D57" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E57">
         <v>853</v>
       </c>
       <c r="F57" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>13</v>
@@ -2084,16 +2084,16 @@
     </row>
     <row r="58" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D58" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E58">
         <v>849</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>12</v>
@@ -2117,21 +2117,21 @@
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
       <c r="M59" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D60" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E60">
         <v>855</v>
       </c>
       <c r="F60" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2151,16 +2151,16 @@
     </row>
     <row r="61" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D61" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E61">
         <v>852</v>
       </c>
       <c r="F61" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2180,16 +2180,16 @@
     </row>
     <row r="62" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D62" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E62">
         <v>851</v>
       </c>
       <c r="F62" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2209,16 +2209,16 @@
     </row>
     <row r="63" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D63" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E63">
         <v>848</v>
       </c>
       <c r="F63" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2238,16 +2238,16 @@
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D64" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E64">
         <v>854</v>
       </c>
       <c r="F64" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2267,16 +2267,16 @@
     </row>
     <row r="65" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D65" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E65">
         <v>850</v>
       </c>
       <c r="F65" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2296,16 +2296,16 @@
     </row>
     <row r="66" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D66" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E66">
         <v>853</v>
       </c>
       <c r="F66" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2325,16 +2325,16 @@
     </row>
     <row r="67" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D67" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E67">
         <v>849</v>
       </c>
       <c r="F67" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>12</v>
@@ -2358,21 +2358,21 @@
       <c r="J68" s="2"/>
       <c r="K68" s="1"/>
       <c r="M68" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D69" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E69">
         <v>855</v>
       </c>
       <c r="F69" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>10</v>
@@ -2392,16 +2392,16 @@
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D70" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E70">
         <v>852</v>
       </c>
       <c r="F70" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>13</v>
@@ -2421,16 +2421,16 @@
     </row>
     <row r="71" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D71" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E71">
         <v>980</v>
       </c>
       <c r="F71" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>14</v>
@@ -2454,21 +2454,21 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D73" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E73">
         <v>851</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2488,16 +2488,16 @@
     </row>
     <row r="74" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D74" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E74">
         <v>981</v>
       </c>
       <c r="F74" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2517,16 +2517,16 @@
     </row>
     <row r="75" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D75" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E75">
         <v>848</v>
       </c>
       <c r="F75" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2546,16 +2546,16 @@
     </row>
     <row r="76" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D76" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E76">
         <v>854</v>
       </c>
       <c r="F76" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>13</v>
@@ -2575,16 +2575,16 @@
     </row>
     <row r="77" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D77" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E77">
         <v>850</v>
       </c>
       <c r="F77" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>10</v>
@@ -2604,16 +2604,16 @@
     </row>
     <row r="78" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D78" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E78">
         <v>853</v>
       </c>
       <c r="F78" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>13</v>
@@ -2633,16 +2633,16 @@
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D79" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E79">
         <v>849</v>
       </c>
       <c r="F79" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2662,16 +2662,16 @@
     </row>
     <row r="80" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D80" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E80">
         <v>855</v>
       </c>
       <c r="F80" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2691,16 +2691,16 @@
     </row>
     <row r="81" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D81" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E81">
         <v>852</v>
       </c>
       <c r="F81" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2720,16 +2720,16 @@
     </row>
     <row r="82" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D82" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E82">
         <v>980</v>
       </c>
       <c r="F82" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2749,16 +2749,16 @@
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D83" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E83">
         <v>851</v>
       </c>
       <c r="F83" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2778,16 +2778,16 @@
     </row>
     <row r="84" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D84" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E84">
         <v>981</v>
       </c>
       <c r="F84" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2807,16 +2807,16 @@
     </row>
     <row r="85" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D85" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E85">
         <v>848</v>
       </c>
       <c r="F85" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2836,16 +2836,16 @@
     </row>
     <row r="86" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D86" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E86">
         <v>854</v>
       </c>
       <c r="F86" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -2865,16 +2865,16 @@
     </row>
     <row r="87" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D87" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E87">
         <v>850</v>
       </c>
       <c r="F87" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>12</v>
@@ -2898,21 +2898,21 @@
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
       <c r="M88" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D89" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E89">
         <v>853</v>
       </c>
       <c r="F89" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2932,16 +2932,16 @@
     </row>
     <row r="90" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D90" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E90">
         <v>849</v>
       </c>
       <c r="F90" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2961,16 +2961,16 @@
     </row>
     <row r="91" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D91" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E91">
         <v>855</v>
       </c>
       <c r="F91" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -2990,16 +2990,16 @@
     </row>
     <row r="92" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D92" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E92">
         <v>852</v>
       </c>
       <c r="F92" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3019,16 +3019,16 @@
     </row>
     <row r="93" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D93" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E93">
         <v>980</v>
       </c>
       <c r="F93" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3048,16 +3048,16 @@
     </row>
     <row r="94" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D94" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E94">
         <v>851</v>
       </c>
       <c r="F94" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>12</v>
@@ -3081,21 +3081,21 @@
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
       <c r="M95" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D96" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E96">
         <v>981</v>
       </c>
       <c r="F96" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3115,16 +3115,16 @@
     </row>
     <row r="97" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D97" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E97">
         <v>848</v>
       </c>
       <c r="F97" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3144,16 +3144,16 @@
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D98" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E98">
         <v>854</v>
       </c>
       <c r="F98" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3173,16 +3173,16 @@
     </row>
     <row r="99" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D99" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E99">
         <v>850</v>
       </c>
       <c r="F99" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3202,16 +3202,16 @@
     </row>
     <row r="100" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D100" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E100">
         <v>853</v>
       </c>
       <c r="F100" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3231,16 +3231,16 @@
     </row>
     <row r="101" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D101" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E101">
         <v>849</v>
       </c>
       <c r="F101" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3260,16 +3260,16 @@
     </row>
     <row r="102" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D102" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E102">
         <v>855</v>
       </c>
       <c r="F102" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3289,16 +3289,16 @@
     </row>
     <row r="103" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D103" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E103">
         <v>852</v>
       </c>
       <c r="F103" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3318,16 +3318,16 @@
     </row>
     <row r="104" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D104" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E104">
         <v>980</v>
       </c>
       <c r="F104" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3347,16 +3347,16 @@
     </row>
     <row r="105" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D105" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E105">
         <v>851</v>
       </c>
       <c r="F105" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3376,16 +3376,16 @@
     </row>
     <row r="106" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D106" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E106">
         <v>981</v>
       </c>
       <c r="F106" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3405,16 +3405,16 @@
     </row>
     <row r="107" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D107" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E107">
         <v>848</v>
       </c>
       <c r="F107" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3434,16 +3434,16 @@
     </row>
     <row r="108" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D108" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E108">
         <v>854</v>
       </c>
       <c r="F108" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3463,16 +3463,16 @@
     </row>
     <row r="109" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D109" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E109">
         <v>850</v>
       </c>
       <c r="F109" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3492,16 +3492,16 @@
     </row>
     <row r="110" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D110" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E110">
         <v>853</v>
       </c>
       <c r="F110" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3521,16 +3521,16 @@
     </row>
     <row r="111" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D111" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E111">
         <v>849</v>
       </c>
       <c r="F111" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>13</v>
@@ -3550,16 +3550,16 @@
     </row>
     <row r="112" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D112" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E112">
         <v>855</v>
       </c>
       <c r="F112" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3579,16 +3579,16 @@
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D113" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E113">
         <v>852</v>
       </c>
       <c r="F113" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3608,16 +3608,16 @@
     </row>
     <row r="114" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D114" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E114">
         <v>980</v>
       </c>
       <c r="F114" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -3637,16 +3637,16 @@
     </row>
     <row r="115" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D115" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E115">
         <v>851</v>
       </c>
       <c r="F115" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3666,16 +3666,16 @@
     </row>
     <row r="116" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D116" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E116">
         <v>981</v>
       </c>
       <c r="F116" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3695,16 +3695,16 @@
     </row>
     <row r="117" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D117" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E117">
         <v>848</v>
       </c>
       <c r="F117" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3724,16 +3724,16 @@
     </row>
     <row r="118" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D118" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E118">
         <v>854</v>
       </c>
       <c r="F118" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3753,16 +3753,16 @@
     </row>
     <row r="119" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D119" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E119">
         <v>850</v>
       </c>
       <c r="F119" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3782,16 +3782,16 @@
     </row>
     <row r="120" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D120" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E120">
         <v>853</v>
       </c>
       <c r="F120" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3811,16 +3811,16 @@
     </row>
     <row r="121" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D121" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E121">
         <v>849</v>
       </c>
       <c r="F121" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3840,16 +3840,16 @@
     </row>
     <row r="122" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D122" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E122">
         <v>855</v>
       </c>
       <c r="F122" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3869,16 +3869,16 @@
     </row>
     <row r="123" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D123" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E123">
         <v>852</v>
       </c>
       <c r="F123" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3898,16 +3898,16 @@
     </row>
     <row r="124" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D124" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E124">
         <v>980</v>
       </c>
       <c r="F124" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -3927,16 +3927,16 @@
     </row>
     <row r="125" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D125" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E125">
         <v>851</v>
       </c>
       <c r="F125" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -3956,16 +3956,16 @@
     </row>
     <row r="126" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D126" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E126">
         <v>981</v>
       </c>
       <c r="F126" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -3985,16 +3985,16 @@
     </row>
     <row r="127" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D127" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E127">
         <v>848</v>
       </c>
       <c r="F127" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4014,16 +4014,16 @@
     </row>
     <row r="128" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D128" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E128">
         <v>854</v>
       </c>
       <c r="F128" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4043,16 +4043,16 @@
     </row>
     <row r="129" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D129" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E129">
         <v>850</v>
       </c>
       <c r="F129" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4072,16 +4072,16 @@
     </row>
     <row r="130" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D130" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E130">
         <v>853</v>
       </c>
       <c r="F130" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4101,16 +4101,16 @@
     </row>
     <row r="131" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D131" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E131">
         <v>849</v>
       </c>
       <c r="F131" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>13</v>
@@ -4130,16 +4130,16 @@
     </row>
     <row r="132" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D132" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E132">
         <v>855</v>
       </c>
       <c r="F132" t="s">
+        <v>41</v>
+      </c>
+      <c r="H132" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4159,16 +4159,16 @@
     </row>
     <row r="133" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D133" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E133">
         <v>852</v>
       </c>
       <c r="F133" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>13</v>
@@ -4188,16 +4188,16 @@
     </row>
     <row r="134" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D134" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E134">
         <v>980</v>
       </c>
       <c r="F134" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>10</v>
@@ -4217,16 +4217,16 @@
     </row>
     <row r="135" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D135" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E135">
         <v>851</v>
       </c>
       <c r="F135" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4246,16 +4246,16 @@
     </row>
     <row r="136" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D136" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E136">
         <v>981</v>
       </c>
       <c r="F136" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4275,16 +4275,16 @@
     </row>
     <row r="137" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D137" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E137">
         <v>848</v>
       </c>
       <c r="F137" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>13</v>
@@ -4304,16 +4304,16 @@
     </row>
     <row r="138" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D138" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E138">
         <v>854</v>
       </c>
       <c r="F138" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>13</v>
@@ -4333,16 +4333,16 @@
     </row>
     <row r="139" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D139" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E139">
         <v>850</v>
       </c>
       <c r="F139" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>13</v>
@@ -4362,16 +4362,16 @@
     </row>
     <row r="140" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D140" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E140">
         <v>853</v>
       </c>
       <c r="F140" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4391,16 +4391,16 @@
     </row>
     <row r="141" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D141" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E141">
         <v>849</v>
       </c>
       <c r="F141" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4420,16 +4420,16 @@
     </row>
     <row r="142" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D142" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E142">
         <v>855</v>
       </c>
       <c r="F142" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4449,16 +4449,16 @@
     </row>
     <row r="143" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D143" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E143">
         <v>852</v>
       </c>
       <c r="F143" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4478,16 +4478,16 @@
     </row>
     <row r="144" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D144" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E144">
         <v>980</v>
       </c>
       <c r="F144" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4507,16 +4507,16 @@
     </row>
     <row r="145" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D145" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E145">
         <v>851</v>
       </c>
       <c r="F145" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4536,16 +4536,16 @@
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D146" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E146">
         <v>981</v>
       </c>
       <c r="F146" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4565,16 +4565,16 @@
     </row>
     <row r="147" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D147" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E147">
         <v>848</v>
       </c>
       <c r="F147" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4594,16 +4594,16 @@
     </row>
     <row r="148" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D148" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E148">
         <v>854</v>
       </c>
       <c r="F148" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4623,16 +4623,16 @@
     </row>
     <row r="149" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D149" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E149">
         <v>850</v>
       </c>
       <c r="F149" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>13</v>
@@ -4652,16 +4652,16 @@
     </row>
     <row r="150" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D150" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E150">
         <v>853</v>
       </c>
       <c r="F150" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>13</v>
@@ -4681,16 +4681,16 @@
     </row>
     <row r="151" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D151" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E151">
         <v>849</v>
       </c>
       <c r="F151" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4710,16 +4710,16 @@
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D152" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E152">
         <v>855</v>
       </c>
       <c r="F152" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4739,16 +4739,16 @@
     </row>
     <row r="153" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D153" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E153">
         <v>852</v>
       </c>
       <c r="F153" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4768,16 +4768,16 @@
     </row>
     <row r="154" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D154" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E154">
         <v>980</v>
       </c>
       <c r="F154" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4797,16 +4797,16 @@
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D155" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E155">
         <v>851</v>
       </c>
       <c r="F155" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4826,16 +4826,16 @@
     </row>
     <row r="156" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D156" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E156">
         <v>981</v>
       </c>
       <c r="F156" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4855,16 +4855,16 @@
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D157" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E157">
         <v>848</v>
       </c>
       <c r="F157" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -4884,16 +4884,16 @@
     </row>
     <row r="158" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D158" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E158">
         <v>854</v>
       </c>
       <c r="F158" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4913,16 +4913,16 @@
     </row>
     <row r="159" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D159" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E159">
         <v>850</v>
       </c>
       <c r="F159" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -4942,16 +4942,16 @@
     </row>
     <row r="160" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D160" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E160">
         <v>853</v>
       </c>
       <c r="F160" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -4971,16 +4971,16 @@
     </row>
     <row r="161" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D161" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E161">
         <v>849</v>
       </c>
       <c r="F161" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5000,16 +5000,16 @@
     </row>
     <row r="162" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D162" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E162">
         <v>855</v>
       </c>
       <c r="F162" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>13</v>
@@ -5029,16 +5029,16 @@
     </row>
     <row r="163" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D163" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E163">
         <v>852</v>
       </c>
       <c r="F163" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>13</v>
@@ -5058,16 +5058,16 @@
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D164" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E164">
         <v>980</v>
       </c>
       <c r="F164" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5087,16 +5087,16 @@
     </row>
     <row r="165" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D165" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E165">
         <v>851</v>
       </c>
       <c r="F165" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5116,16 +5116,16 @@
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D166" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E166">
         <v>981</v>
       </c>
       <c r="F166" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5145,16 +5145,16 @@
     </row>
     <row r="167" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D167" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E167">
         <v>848</v>
       </c>
       <c r="F167" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>13</v>
@@ -5174,16 +5174,16 @@
     </row>
     <row r="168" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D168" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E168">
         <v>854</v>
       </c>
       <c r="F168" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5203,16 +5203,16 @@
     </row>
     <row r="169" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D169" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E169">
         <v>850</v>
       </c>
       <c r="F169" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>12</v>
@@ -5236,21 +5236,21 @@
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
       <c r="M170" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D171" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E171">
         <v>853</v>
       </c>
       <c r="F171" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>13</v>
@@ -5270,16 +5270,16 @@
     </row>
     <row r="172" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D172" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E172">
         <v>849</v>
       </c>
       <c r="F172" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>13</v>
@@ -5299,16 +5299,16 @@
     </row>
     <row r="173" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D173" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E173">
         <v>855</v>
       </c>
       <c r="F173" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5328,16 +5328,16 @@
     </row>
     <row r="174" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D174" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E174">
         <v>852</v>
       </c>
       <c r="F174" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -5357,16 +5357,16 @@
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D175" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E175">
         <v>980</v>
       </c>
       <c r="F175" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5386,16 +5386,16 @@
     </row>
     <row r="176" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D176" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E176">
         <v>851</v>
       </c>
       <c r="F176" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5415,16 +5415,16 @@
     </row>
     <row r="177" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D177" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E177">
         <v>981</v>
       </c>
       <c r="F177" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>13</v>
@@ -5444,16 +5444,16 @@
     </row>
     <row r="178" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D178" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E178">
         <v>848</v>
       </c>
       <c r="F178" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>13</v>
@@ -5473,16 +5473,16 @@
     </row>
     <row r="179" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D179" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E179">
         <v>854</v>
       </c>
       <c r="F179" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>13</v>
@@ -5502,16 +5502,16 @@
     </row>
     <row r="180" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D180" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E180">
         <v>850</v>
       </c>
       <c r="F180" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>13</v>
@@ -5531,16 +5531,16 @@
     </row>
     <row r="181" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D181" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E181">
         <v>853</v>
       </c>
       <c r="F181" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5560,16 +5560,16 @@
     </row>
     <row r="182" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D182" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E182">
         <v>849</v>
       </c>
       <c r="F182" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5589,16 +5589,16 @@
     </row>
     <row r="183" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D183" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E183">
         <v>855</v>
       </c>
       <c r="F183" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5618,16 +5618,16 @@
     </row>
     <row r="184" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D184" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E184">
         <v>852</v>
       </c>
       <c r="F184" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5647,16 +5647,16 @@
     </row>
     <row r="185" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D185" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E185">
         <v>980</v>
       </c>
       <c r="F185" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -5676,16 +5676,16 @@
     </row>
     <row r="186" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D186" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E186">
         <v>851</v>
       </c>
       <c r="F186" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5705,16 +5705,16 @@
     </row>
     <row r="187" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D187" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E187">
         <v>981</v>
       </c>
       <c r="F187" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>13</v>
@@ -5734,16 +5734,16 @@
     </row>
     <row r="188" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D188" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E188">
         <v>848</v>
       </c>
       <c r="F188" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5763,16 +5763,16 @@
     </row>
     <row r="189" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D189" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E189">
         <v>854</v>
       </c>
       <c r="F189" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>13</v>
@@ -5792,16 +5792,16 @@
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D190" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E190">
         <v>850</v>
       </c>
       <c r="F190" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5821,16 +5821,16 @@
     </row>
     <row r="191" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D191" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E191">
         <v>853</v>
       </c>
       <c r="F191" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>13</v>
@@ -5850,16 +5850,16 @@
     </row>
     <row r="192" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D192" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E192">
         <v>849</v>
       </c>
       <c r="F192" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H192" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>13</v>
@@ -5879,16 +5879,16 @@
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D193" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E193">
         <v>855</v>
       </c>
       <c r="F193" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>13</v>
@@ -5908,16 +5908,16 @@
     </row>
     <row r="194" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D194" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E194">
         <v>852</v>
       </c>
       <c r="F194" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>13</v>
@@ -5937,16 +5937,16 @@
     </row>
     <row r="195" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D195" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E195">
         <v>980</v>
       </c>
       <c r="F195" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>13</v>
@@ -5966,16 +5966,16 @@
     </row>
     <row r="196" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D196" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E196">
         <v>851</v>
       </c>
       <c r="F196" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>13</v>
@@ -5995,16 +5995,16 @@
     </row>
     <row r="197" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D197" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E197">
         <v>981</v>
       </c>
       <c r="F197" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>13</v>
@@ -6024,16 +6024,16 @@
     </row>
     <row r="198" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D198" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E198">
         <v>848</v>
       </c>
       <c r="F198" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>13</v>
@@ -6053,16 +6053,16 @@
     </row>
     <row r="199" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D199" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E199">
         <v>854</v>
       </c>
       <c r="F199" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>13</v>
@@ -6082,16 +6082,16 @@
     </row>
     <row r="200" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D200" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E200">
         <v>850</v>
       </c>
       <c r="F200" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>13</v>
@@ -6111,16 +6111,16 @@
     </row>
     <row r="201" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D201" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E201">
         <v>853</v>
       </c>
       <c r="F201" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>13</v>
@@ -6140,16 +6140,16 @@
     </row>
     <row r="202" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D202" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E202">
         <v>849</v>
       </c>
       <c r="F202" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>13</v>
@@ -6169,16 +6169,16 @@
     </row>
     <row r="203" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D203" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E203">
         <v>855</v>
       </c>
       <c r="F203" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>13</v>
@@ -6198,16 +6198,16 @@
     </row>
     <row r="204" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D204" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E204">
         <v>852</v>
       </c>
       <c r="F204" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>13</v>
@@ -6227,16 +6227,16 @@
     </row>
     <row r="205" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D205" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E205">
         <v>980</v>
       </c>
       <c r="F205" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>13</v>
@@ -6256,16 +6256,16 @@
     </row>
     <row r="206" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D206" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E206">
         <v>851</v>
       </c>
       <c r="F206" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>13</v>
@@ -6285,16 +6285,16 @@
     </row>
     <row r="207" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D207" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E207">
         <v>981</v>
       </c>
       <c r="F207" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6314,16 +6314,16 @@
     </row>
     <row r="208" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D208" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E208">
         <v>848</v>
       </c>
       <c r="F208" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6343,16 +6343,16 @@
     </row>
     <row r="209" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D209" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E209">
         <v>854</v>
       </c>
       <c r="F209" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>13</v>
@@ -6372,16 +6372,16 @@
     </row>
     <row r="210" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D210" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E210">
         <v>850</v>
       </c>
       <c r="F210" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6401,16 +6401,16 @@
     </row>
     <row r="211" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D211" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E211">
         <v>853</v>
       </c>
       <c r="F211" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>13</v>
@@ -6430,16 +6430,16 @@
     </row>
     <row r="212" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D212" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E212">
         <v>849</v>
       </c>
       <c r="F212" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>13</v>
@@ -6459,16 +6459,16 @@
     </row>
     <row r="213" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D213" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E213">
         <v>855</v>
       </c>
       <c r="F213" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6488,16 +6488,16 @@
     </row>
     <row r="214" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D214" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E214">
         <v>852</v>
       </c>
       <c r="F214" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6517,16 +6517,16 @@
     </row>
     <row r="215" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D215" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E215">
         <v>980</v>
       </c>
       <c r="F215" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6546,16 +6546,16 @@
     </row>
     <row r="216" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D216" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E216">
         <v>851</v>
       </c>
       <c r="F216" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>13</v>
@@ -6575,16 +6575,16 @@
     </row>
     <row r="217" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D217" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E217">
         <v>848</v>
       </c>
       <c r="F217" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>13</v>
@@ -6604,16 +6604,16 @@
     </row>
     <row r="218" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D218" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E218">
         <v>854</v>
       </c>
       <c r="F218" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6633,16 +6633,16 @@
     </row>
     <row r="219" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D219" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E219">
         <v>850</v>
       </c>
       <c r="F219" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6662,16 +6662,16 @@
     </row>
     <row r="220" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D220" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E220">
         <v>853</v>
       </c>
       <c r="F220" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>13</v>
@@ -6691,16 +6691,16 @@
     </row>
     <row r="221" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D221" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E221">
         <v>849</v>
       </c>
       <c r="F221" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>13</v>
@@ -6720,16 +6720,16 @@
     </row>
     <row r="222" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D222" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E222">
         <v>855</v>
       </c>
       <c r="F222" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>13</v>
@@ -6749,16 +6749,16 @@
     </row>
     <row r="223" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D223" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E223">
         <v>852</v>
       </c>
       <c r="F223" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>13</v>
@@ -6778,16 +6778,16 @@
     </row>
     <row r="224" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D224" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E224">
         <v>980</v>
       </c>
       <c r="F224" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6807,16 +6807,16 @@
     </row>
     <row r="225" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D225" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E225">
         <v>851</v>
       </c>
       <c r="F225" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6836,16 +6836,16 @@
     </row>
     <row r="226" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D226" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E226">
         <v>848</v>
       </c>
       <c r="F226" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6865,16 +6865,16 @@
     </row>
     <row r="227" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D227" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E227">
         <v>854</v>
       </c>
       <c r="F227" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>13</v>
@@ -6894,16 +6894,16 @@
     </row>
     <row r="228" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D228" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E228">
         <v>850</v>
       </c>
       <c r="F228" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6923,16 +6923,16 @@
     </row>
     <row r="229" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D229" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E229">
         <v>853</v>
       </c>
       <c r="F229" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>13</v>
@@ -6952,16 +6952,16 @@
     </row>
     <row r="230" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D230" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E230">
         <v>849</v>
       </c>
       <c r="F230" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>13</v>
@@ -6981,16 +6981,16 @@
     </row>
     <row r="231" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D231" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E231">
         <v>855</v>
       </c>
       <c r="F231" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -7010,16 +7010,16 @@
     </row>
     <row r="232" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D232" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E232">
         <v>852</v>
       </c>
       <c r="F232" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -7039,16 +7039,16 @@
     </row>
     <row r="233" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D233" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E233">
         <v>980</v>
       </c>
       <c r="F233" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -7068,16 +7068,16 @@
     </row>
     <row r="234" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D234" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E234">
         <v>851</v>
       </c>
       <c r="F234" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7097,16 +7097,16 @@
     </row>
     <row r="235" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D235" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E235">
         <v>848</v>
       </c>
       <c r="F235" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7126,16 +7126,16 @@
     </row>
     <row r="236" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D236" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E236">
         <v>854</v>
       </c>
       <c r="F236" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -7155,16 +7155,16 @@
     </row>
     <row r="237" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D237" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E237">
         <v>850</v>
       </c>
       <c r="F237" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7184,16 +7184,16 @@
     </row>
     <row r="238" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D238" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E238">
         <v>853</v>
       </c>
       <c r="F238" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -7213,16 +7213,16 @@
     </row>
     <row r="239" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D239" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E239">
         <v>849</v>
       </c>
       <c r="F239" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7242,16 +7242,16 @@
     </row>
     <row r="240" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D240" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E240">
         <v>855</v>
       </c>
       <c r="F240" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7271,16 +7271,16 @@
     </row>
     <row r="241" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D241" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E241">
         <v>852</v>
       </c>
       <c r="F241" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7300,16 +7300,16 @@
     </row>
     <row r="242" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D242" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E242">
         <v>980</v>
       </c>
       <c r="F242" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7329,16 +7329,16 @@
     </row>
     <row r="243" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D243" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E243">
         <v>851</v>
       </c>
       <c r="F243" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7358,16 +7358,16 @@
     </row>
     <row r="244" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D244" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E244">
         <v>848</v>
       </c>
       <c r="F244" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7387,16 +7387,16 @@
     </row>
     <row r="245" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D245" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E245">
         <v>854</v>
       </c>
       <c r="F245" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>13</v>
@@ -7416,16 +7416,16 @@
     </row>
     <row r="246" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D246" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E246">
         <v>850</v>
       </c>
       <c r="F246" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>10</v>
@@ -7445,16 +7445,16 @@
     </row>
     <row r="247" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D247" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E247">
         <v>853</v>
       </c>
       <c r="F247" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>13</v>
@@ -7474,16 +7474,16 @@
     </row>
     <row r="248" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D248" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E248">
         <v>849</v>
       </c>
       <c r="F248" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7503,16 +7503,16 @@
     </row>
     <row r="249" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D249" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E249">
         <v>855</v>
       </c>
       <c r="F249" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7532,16 +7532,16 @@
     </row>
     <row r="250" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D250" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E250">
         <v>852</v>
       </c>
       <c r="F250" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7561,16 +7561,16 @@
     </row>
     <row r="251" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D251" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E251">
         <v>980</v>
       </c>
       <c r="F251" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7590,16 +7590,16 @@
     </row>
     <row r="252" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D252" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E252">
         <v>851</v>
       </c>
       <c r="F252" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7619,16 +7619,16 @@
     </row>
     <row r="253" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D253" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E253">
         <v>848</v>
       </c>
       <c r="F253" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7648,16 +7648,16 @@
     </row>
     <row r="254" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D254" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E254">
         <v>854</v>
       </c>
       <c r="F254" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>13</v>
@@ -7677,16 +7677,16 @@
     </row>
     <row r="255" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D255" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E255">
         <v>850</v>
       </c>
       <c r="F255" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>12</v>
@@ -7710,21 +7710,21 @@
       <c r="J256" s="2"/>
       <c r="K256" s="1"/>
       <c r="M256" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D257" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E257">
         <v>853</v>
       </c>
       <c r="F257" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>13</v>
@@ -7744,16 +7744,16 @@
     </row>
     <row r="258" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D258" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E258">
         <v>849</v>
       </c>
       <c r="F258" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7773,16 +7773,16 @@
     </row>
     <row r="259" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D259" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E259">
         <v>855</v>
       </c>
       <c r="F259" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7802,16 +7802,16 @@
     </row>
     <row r="260" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D260" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E260">
         <v>852</v>
       </c>
       <c r="F260" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7831,16 +7831,16 @@
     </row>
     <row r="261" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D261" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E261">
         <v>980</v>
       </c>
       <c r="F261" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7860,16 +7860,16 @@
     </row>
     <row r="262" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D262" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E262">
         <v>851</v>
       </c>
       <c r="F262" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7889,16 +7889,16 @@
     </row>
     <row r="263" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D263" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E263">
         <v>848</v>
       </c>
       <c r="F263" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -7918,16 +7918,16 @@
     </row>
     <row r="264" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D264" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E264">
         <v>854</v>
       </c>
       <c r="F264" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>13</v>
@@ -7947,16 +7947,16 @@
     </row>
     <row r="265" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D265" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E265">
         <v>850</v>
       </c>
       <c r="F265" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7976,16 +7976,16 @@
     </row>
     <row r="266" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D266" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E266">
         <v>853</v>
       </c>
       <c r="F266" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>13</v>
@@ -8005,16 +8005,16 @@
     </row>
     <row r="267" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D267" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E267">
         <v>849</v>
       </c>
       <c r="F267" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -8034,16 +8034,16 @@
     </row>
     <row r="268" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D268" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E268">
         <v>855</v>
       </c>
       <c r="F268" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -8063,16 +8063,16 @@
     </row>
     <row r="269" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D269" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E269">
         <v>852</v>
       </c>
       <c r="F269" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>13</v>
@@ -8092,16 +8092,16 @@
     </row>
     <row r="270" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D270" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E270">
         <v>980</v>
       </c>
       <c r="F270" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -8121,16 +8121,16 @@
     </row>
     <row r="271" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D271" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E271">
         <v>851</v>
       </c>
       <c r="F271" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -8150,16 +8150,16 @@
     </row>
     <row r="272" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D272" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E272">
         <v>848</v>
       </c>
       <c r="F272" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8179,16 +8179,16 @@
     </row>
     <row r="273" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D273" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E273">
         <v>854</v>
       </c>
       <c r="F273" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>13</v>
@@ -8208,16 +8208,16 @@
     </row>
     <row r="274" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D274" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E274">
         <v>850</v>
       </c>
       <c r="F274" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>13</v>
@@ -8237,16 +8237,16 @@
     </row>
     <row r="275" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D275" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E275">
         <v>853</v>
       </c>
       <c r="F275" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>13</v>
@@ -8266,16 +8266,16 @@
     </row>
     <row r="276" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D276" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E276">
         <v>849</v>
       </c>
       <c r="F276" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>13</v>
@@ -8295,16 +8295,16 @@
     </row>
     <row r="277" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D277" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E277">
         <v>852</v>
       </c>
       <c r="F277" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8324,16 +8324,16 @@
     </row>
     <row r="278" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D278" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E278">
         <v>980</v>
       </c>
       <c r="F278" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>13</v>
@@ -8353,16 +8353,16 @@
     </row>
     <row r="279" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D279" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E279">
         <v>851</v>
       </c>
       <c r="F279" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8382,16 +8382,16 @@
     </row>
     <row r="280" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D280" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E280">
         <v>848</v>
       </c>
       <c r="F280" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8411,16 +8411,16 @@
     </row>
     <row r="281" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D281" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E281">
         <v>854</v>
       </c>
       <c r="F281" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>13</v>
@@ -8440,16 +8440,16 @@
     </row>
     <row r="282" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D282" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E282">
         <v>850</v>
       </c>
       <c r="F282" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -8469,16 +8469,16 @@
     </row>
     <row r="283" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D283" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E283">
         <v>849</v>
       </c>
       <c r="F283" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>13</v>
@@ -8498,16 +8498,16 @@
     </row>
     <row r="284" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D284" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E284">
         <v>852</v>
       </c>
       <c r="F284" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>13</v>
@@ -8527,16 +8527,16 @@
     </row>
     <row r="285" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D285" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E285">
         <v>980</v>
       </c>
       <c r="F285" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>13</v>
@@ -8556,16 +8556,16 @@
     </row>
     <row r="286" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D286" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E286">
         <v>848</v>
       </c>
       <c r="F286" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>13</v>
@@ -8585,16 +8585,16 @@
     </row>
     <row r="287" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D287" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E287">
         <v>854</v>
       </c>
       <c r="F287" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>13</v>
@@ -8614,16 +8614,16 @@
     </row>
     <row r="288" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D288" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E288">
         <v>850</v>
       </c>
       <c r="F288" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>13</v>
@@ -8643,16 +8643,16 @@
     </row>
     <row r="289" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D289" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E289">
         <v>849</v>
       </c>
       <c r="F289" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>13</v>
@@ -8672,16 +8672,16 @@
     </row>
     <row r="290" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D290" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E290">
         <v>852</v>
       </c>
       <c r="F290" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>13</v>
@@ -8701,16 +8701,16 @@
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D291" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E291">
         <v>980</v>
       </c>
       <c r="F291" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>13</v>
@@ -8730,16 +8730,16 @@
     </row>
     <row r="292" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D292" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E292">
         <v>848</v>
       </c>
       <c r="F292" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8759,16 +8759,16 @@
     </row>
     <row r="293" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D293" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E293">
         <v>854</v>
       </c>
       <c r="F293" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>13</v>
@@ -8788,16 +8788,16 @@
     </row>
     <row r="294" spans="4:13" x14ac:dyDescent="0.3">
       <c r="D294" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E294">
         <v>850</v>
       </c>
       <c r="F294" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>13</v>
@@ -9316,6 +9316,7 @@
     <row r="378" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H378" s="2"/>
       <c r="I378" s="1"/>
+      <c r="J378" s="2"/>
       <c r="K378" s="1"/>
     </row>
     <row r="379" spans="8:11" x14ac:dyDescent="0.3">
@@ -45383,7 +45384,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5B37EBA-D930-4F6E-97B8-E70CCB13917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CC48FFB-8927-4167-8065-97AD317875F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1415" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="53">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,7 +86,16 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -98,43 +107,34 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
-    <t>Space Management-Big 5</t>
+    <t>Fatigue</t>
   </si>
   <si>
     <t>Driver Health</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Micro-Learn Space Mangement</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
+    <t>Space Management-Big 5</t>
+  </si>
+  <si>
     <t>Alert Driving: Big Three</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Fatigue</t>
-  </si>
-  <si>
-    <t>Micro-Learn Space Mangement</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Scene of an Accident</t>
@@ -571,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -629,7 +629,7 @@
         <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -658,7 +658,7 @@
         <v>39</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -687,7 +687,7 @@
         <v>40</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -716,7 +716,7 @@
         <v>41</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -745,7 +745,7 @@
         <v>42</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -774,7 +774,7 @@
         <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -803,7 +803,7 @@
         <v>44</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -832,7 +832,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -861,7 +861,7 @@
         <v>46</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>47</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -919,7 +919,7 @@
         <v>48</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -948,7 +948,7 @@
         <v>48</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -977,7 +977,7 @@
         <v>49</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1006,7 +1006,7 @@
         <v>49</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>10</v>
@@ -1035,7 +1035,7 @@
         <v>50</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>10</v>
@@ -1064,7 +1064,7 @@
         <v>50</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>51</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1122,7 +1122,7 @@
         <v>51</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1204,7 +1204,7 @@
       <c r="J22" s="2"/>
       <c r="K22" s="1"/>
       <c r="M22" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="4:13" x14ac:dyDescent="0.3">
@@ -1271,7 +1271,7 @@
       <c r="J25" s="2"/>
       <c r="K25" s="1"/>
       <c r="M25" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="4:13" x14ac:dyDescent="0.3">
@@ -1512,7 +1512,7 @@
       <c r="J34" s="2"/>
       <c r="K34" s="1"/>
       <c r="M34" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="4:13" x14ac:dyDescent="0.3">
@@ -1579,7 +1579,7 @@
       <c r="J37" s="2"/>
       <c r="K37" s="1"/>
       <c r="M37" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="4:13" x14ac:dyDescent="0.3">
@@ -1704,7 +1704,7 @@
       <c r="J42" s="2"/>
       <c r="K42" s="1"/>
       <c r="M42" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="4:13" x14ac:dyDescent="0.3">
@@ -1829,7 +1829,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
@@ -1867,7 +1867,7 @@
       <c r="J49" s="2"/>
       <c r="K49" s="1"/>
       <c r="M49" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="4:13" x14ac:dyDescent="0.3">
@@ -2050,7 +2050,7 @@
       <c r="J56" s="2"/>
       <c r="K56" s="1"/>
       <c r="M56" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="4:13" x14ac:dyDescent="0.3">
@@ -2093,7 +2093,7 @@
         <v>39</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>12</v>
@@ -2117,7 +2117,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
       <c r="M59" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
@@ -2131,7 +2131,7 @@
         <v>41</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>42</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2189,7 +2189,7 @@
         <v>45</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>13</v>
@@ -2218,7 +2218,7 @@
         <v>48</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>13</v>
@@ -2247,7 +2247,7 @@
         <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>10</v>
@@ -2276,7 +2276,7 @@
         <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2305,7 +2305,7 @@
         <v>51</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>13</v>
@@ -2358,7 +2358,7 @@
       <c r="J68" s="2"/>
       <c r="K68" s="1"/>
       <c r="M68" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="4:13" x14ac:dyDescent="0.3">
@@ -2454,7 +2454,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2642,7 +2642,7 @@
         <v>39</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2671,7 +2671,7 @@
         <v>41</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>10</v>
@@ -2700,7 +2700,7 @@
         <v>42</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>10</v>
@@ -2729,7 +2729,7 @@
         <v>44</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>10</v>
@@ -2758,7 +2758,7 @@
         <v>45</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>10</v>
@@ -2787,7 +2787,7 @@
         <v>47</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2816,7 +2816,7 @@
         <v>48</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>13</v>
@@ -2845,7 +2845,7 @@
         <v>49</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>13</v>
@@ -2874,7 +2874,7 @@
         <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>12</v>
@@ -2898,7 +2898,7 @@
       <c r="J88" s="2"/>
       <c r="K88" s="1"/>
       <c r="M88" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="4:13" x14ac:dyDescent="0.3">
@@ -2912,7 +2912,7 @@
         <v>51</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -2941,7 +2941,7 @@
         <v>39</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -2970,7 +2970,7 @@
         <v>41</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>10</v>
@@ -2999,7 +2999,7 @@
         <v>42</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>10</v>
@@ -3028,7 +3028,7 @@
         <v>44</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3057,7 +3057,7 @@
         <v>45</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>12</v>
@@ -3081,7 +3081,7 @@
       <c r="J95" s="2"/>
       <c r="K95" s="1"/>
       <c r="M95" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="4:13" x14ac:dyDescent="0.3">
@@ -3095,7 +3095,7 @@
         <v>47</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>10</v>
@@ -3124,7 +3124,7 @@
         <v>48</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>13</v>
@@ -3153,7 +3153,7 @@
         <v>49</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3182,7 +3182,7 @@
         <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>13</v>
@@ -3211,7 +3211,7 @@
         <v>51</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>13</v>
@@ -3240,7 +3240,7 @@
         <v>39</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>13</v>
@@ -3269,7 +3269,7 @@
         <v>41</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>10</v>
@@ -3298,7 +3298,7 @@
         <v>42</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3327,7 +3327,7 @@
         <v>44</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>10</v>
@@ -3356,7 +3356,7 @@
         <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>10</v>
@@ -3385,7 +3385,7 @@
         <v>47</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>10</v>
@@ -3414,7 +3414,7 @@
         <v>48</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>13</v>
@@ -3443,7 +3443,7 @@
         <v>49</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3472,7 +3472,7 @@
         <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>13</v>
@@ -3501,7 +3501,7 @@
         <v>51</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>13</v>
@@ -3530,7 +3530,7 @@
         <v>39</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>13</v>
@@ -3559,7 +3559,7 @@
         <v>41</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>10</v>
@@ -3588,7 +3588,7 @@
         <v>42</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>10</v>
@@ -3617,7 +3617,7 @@
         <v>44</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>10</v>
@@ -3646,7 +3646,7 @@
         <v>45</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>10</v>
@@ -3675,7 +3675,7 @@
         <v>47</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3704,7 +3704,7 @@
         <v>48</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>13</v>
@@ -3733,7 +3733,7 @@
         <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3762,7 +3762,7 @@
         <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>10</v>
@@ -3791,7 +3791,7 @@
         <v>51</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3820,7 +3820,7 @@
         <v>39</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>13</v>
@@ -3849,7 +3849,7 @@
         <v>41</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3878,7 +3878,7 @@
         <v>42</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>13</v>
@@ -3907,7 +3907,7 @@
         <v>44</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -3936,7 +3936,7 @@
         <v>45</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>13</v>
@@ -3965,7 +3965,7 @@
         <v>47</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -3994,7 +3994,7 @@
         <v>48</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4023,7 +4023,7 @@
         <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4052,7 +4052,7 @@
         <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4081,7 +4081,7 @@
         <v>51</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4400,7 +4400,7 @@
         <v>39</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>13</v>
@@ -4429,7 +4429,7 @@
         <v>41</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>13</v>
@@ -4458,7 +4458,7 @@
         <v>42</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4487,7 +4487,7 @@
         <v>44</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>13</v>
@@ -4516,7 +4516,7 @@
         <v>45</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>13</v>
@@ -4545,7 +4545,7 @@
         <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>13</v>
@@ -4574,7 +4574,7 @@
         <v>48</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>13</v>
@@ -4603,7 +4603,7 @@
         <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>13</v>
@@ -4632,7 +4632,7 @@
         <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>13</v>
@@ -4661,7 +4661,7 @@
         <v>51</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>13</v>
@@ -4690,7 +4690,7 @@
         <v>39</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>13</v>
@@ -4719,7 +4719,7 @@
         <v>41</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>13</v>
@@ -4748,7 +4748,7 @@
         <v>42</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>13</v>
@@ -4777,7 +4777,7 @@
         <v>44</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>10</v>
@@ -4806,7 +4806,7 @@
         <v>45</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>13</v>
@@ -4835,7 +4835,7 @@
         <v>47</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>13</v>
@@ -4864,7 +4864,7 @@
         <v>48</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -4893,7 +4893,7 @@
         <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4922,7 +4922,7 @@
         <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -4951,7 +4951,7 @@
         <v>51</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>13</v>
@@ -4980,7 +4980,7 @@
         <v>39</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5009,7 +5009,7 @@
         <v>41</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>13</v>
@@ -5038,7 +5038,7 @@
         <v>42</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I163" s="1" t="s">
         <v>13</v>
@@ -5067,7 +5067,7 @@
         <v>44</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>10</v>
@@ -5096,7 +5096,7 @@
         <v>45</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>13</v>
@@ -5125,7 +5125,7 @@
         <v>47</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5154,7 +5154,7 @@
         <v>48</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>13</v>
@@ -5183,7 +5183,7 @@
         <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>13</v>
@@ -5212,7 +5212,7 @@
         <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>12</v>
@@ -5236,7 +5236,7 @@
       <c r="J170" s="2"/>
       <c r="K170" s="1"/>
       <c r="M170" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="171" spans="4:13" x14ac:dyDescent="0.3">
@@ -5250,7 +5250,7 @@
         <v>51</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>13</v>
@@ -5279,7 +5279,7 @@
         <v>39</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>13</v>
@@ -5308,7 +5308,7 @@
         <v>41</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>13</v>
@@ -5337,7 +5337,7 @@
         <v>42</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>13</v>
@@ -5366,7 +5366,7 @@
         <v>44</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>10</v>
@@ -5395,7 +5395,7 @@
         <v>45</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5424,7 +5424,7 @@
         <v>47</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>13</v>
@@ -5453,7 +5453,7 @@
         <v>48</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>13</v>
@@ -5482,7 +5482,7 @@
         <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>13</v>
@@ -5511,7 +5511,7 @@
         <v>50</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>13</v>
@@ -5540,7 +5540,7 @@
         <v>51</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>13</v>
@@ -5569,7 +5569,7 @@
         <v>39</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>13</v>
@@ -5598,7 +5598,7 @@
         <v>41</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>13</v>
@@ -5627,7 +5627,7 @@
         <v>42</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5656,7 +5656,7 @@
         <v>44</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>10</v>
@@ -5685,7 +5685,7 @@
         <v>45</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5714,7 +5714,7 @@
         <v>47</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>13</v>
@@ -5743,7 +5743,7 @@
         <v>48</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>13</v>
@@ -5772,7 +5772,7 @@
         <v>49</v>
       </c>
       <c r="H189" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I189" s="1" t="s">
         <v>13</v>
@@ -5801,7 +5801,7 @@
         <v>50</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>13</v>
@@ -5830,7 +5830,7 @@
         <v>51</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>13</v>
@@ -6439,7 +6439,7 @@
         <v>39</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>13</v>
@@ -6468,7 +6468,7 @@
         <v>41</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6497,7 +6497,7 @@
         <v>42</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>13</v>
@@ -6526,7 +6526,7 @@
         <v>44</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6555,7 +6555,7 @@
         <v>45</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>13</v>
@@ -6584,7 +6584,7 @@
         <v>48</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>13</v>
@@ -6613,7 +6613,7 @@
         <v>49</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6642,7 +6642,7 @@
         <v>50</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6671,7 +6671,7 @@
         <v>51</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>13</v>
@@ -6961,7 +6961,7 @@
         <v>39</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>13</v>
@@ -6990,7 +6990,7 @@
         <v>41</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -7019,7 +7019,7 @@
         <v>42</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>13</v>
@@ -7048,7 +7048,7 @@
         <v>44</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>13</v>
@@ -7077,7 +7077,7 @@
         <v>45</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7106,7 +7106,7 @@
         <v>48</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>13</v>
@@ -7135,7 +7135,7 @@
         <v>49</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>13</v>
@@ -7164,7 +7164,7 @@
         <v>50</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7193,7 +7193,7 @@
         <v>51</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>13</v>
@@ -7222,7 +7222,7 @@
         <v>39</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>13</v>
@@ -7251,7 +7251,7 @@
         <v>41</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7280,7 +7280,7 @@
         <v>42</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7309,7 +7309,7 @@
         <v>44</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7338,7 +7338,7 @@
         <v>45</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7367,7 +7367,7 @@
         <v>48</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7396,7 +7396,7 @@
         <v>49</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>13</v>
@@ -7425,7 +7425,7 @@
         <v>50</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>10</v>
@@ -7454,7 +7454,7 @@
         <v>51</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>13</v>
@@ -7483,7 +7483,7 @@
         <v>39</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>13</v>
@@ -7512,7 +7512,7 @@
         <v>41</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7541,7 +7541,7 @@
         <v>42</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7570,7 +7570,7 @@
         <v>44</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>13</v>
@@ -7599,7 +7599,7 @@
         <v>45</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7628,7 +7628,7 @@
         <v>48</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>13</v>
@@ -7657,7 +7657,7 @@
         <v>49</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>13</v>
@@ -7686,7 +7686,7 @@
         <v>50</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>12</v>
@@ -7710,7 +7710,7 @@
       <c r="J256" s="2"/>
       <c r="K256" s="1"/>
       <c r="M256" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="257" spans="4:13" x14ac:dyDescent="0.3">
@@ -7724,7 +7724,7 @@
         <v>51</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>13</v>
@@ -7753,7 +7753,7 @@
         <v>39</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>13</v>
@@ -7782,7 +7782,7 @@
         <v>41</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>13</v>
@@ -7811,7 +7811,7 @@
         <v>42</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>13</v>
@@ -7840,7 +7840,7 @@
         <v>44</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>10</v>
@@ -7869,7 +7869,7 @@
         <v>45</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7898,7 +7898,7 @@
         <v>48</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>13</v>
@@ -7927,7 +7927,7 @@
         <v>49</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>13</v>
@@ -7956,7 +7956,7 @@
         <v>50</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -7985,7 +7985,7 @@
         <v>51</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>13</v>
@@ -8014,7 +8014,7 @@
         <v>39</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -8043,7 +8043,7 @@
         <v>41</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -8072,7 +8072,7 @@
         <v>42</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>13</v>
@@ -8101,7 +8101,7 @@
         <v>44</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -8130,7 +8130,7 @@
         <v>45</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -8159,7 +8159,7 @@
         <v>48</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>13</v>
@@ -8188,7 +8188,7 @@
         <v>49</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>13</v>
@@ -8217,7 +8217,7 @@
         <v>50</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>13</v>
@@ -8246,7 +8246,7 @@
         <v>51</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>13</v>
@@ -8275,7 +8275,7 @@
         <v>39</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>13</v>
@@ -8304,7 +8304,7 @@
         <v>42</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>13</v>
@@ -8333,7 +8333,7 @@
         <v>44</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>13</v>
@@ -8362,7 +8362,7 @@
         <v>45</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>13</v>
@@ -8391,7 +8391,7 @@
         <v>48</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>13</v>
@@ -8420,7 +8420,7 @@
         <v>49</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>13</v>
@@ -8449,7 +8449,7 @@
         <v>50</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -8478,7 +8478,7 @@
         <v>39</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>13</v>
@@ -8507,7 +8507,7 @@
         <v>42</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>13</v>
@@ -8536,7 +8536,7 @@
         <v>44</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>13</v>
@@ -8565,7 +8565,7 @@
         <v>48</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>13</v>
@@ -8594,7 +8594,7 @@
         <v>49</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>13</v>
@@ -8623,7 +8623,7 @@
         <v>50</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>13</v>
@@ -8652,7 +8652,7 @@
         <v>39</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>13</v>
@@ -8681,7 +8681,7 @@
         <v>42</v>
       </c>
       <c r="H290" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I290" s="1" t="s">
         <v>13</v>
@@ -8710,7 +8710,7 @@
         <v>44</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>13</v>
@@ -8739,7 +8739,7 @@
         <v>48</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>13</v>
@@ -8768,7 +8768,7 @@
         <v>49</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>13</v>
@@ -8797,7 +8797,7 @@
         <v>50</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>13</v>
@@ -8816,40 +8816,178 @@
       </c>
     </row>
     <row r="295" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H295" s="2"/>
-      <c r="I295" s="1"/>
-      <c r="J295" s="2"/>
-      <c r="K295" s="1"/>
+      <c r="D295" t="s">
+        <v>38</v>
+      </c>
+      <c r="E295">
+        <v>849</v>
+      </c>
+      <c r="F295" t="s">
+        <v>39</v>
+      </c>
+      <c r="H295" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I295" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J295" s="2">
+        <v>0</v>
+      </c>
+      <c r="K295" s="1">
+        <v>46219.685416666667</v>
+      </c>
+      <c r="L295">
+        <v>0</v>
+      </c>
+      <c r="M295" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="296" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H296" s="2"/>
-      <c r="I296" s="1"/>
-      <c r="J296" s="2"/>
-      <c r="K296" s="1"/>
+      <c r="D296" t="s">
+        <v>38</v>
+      </c>
+      <c r="E296">
+        <v>852</v>
+      </c>
+      <c r="F296" t="s">
+        <v>42</v>
+      </c>
+      <c r="H296" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J296" s="2">
+        <v>0</v>
+      </c>
+      <c r="K296" s="1">
+        <v>46219.686111111114</v>
+      </c>
+      <c r="L296">
+        <v>0</v>
+      </c>
+      <c r="M296" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="297" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H297" s="2"/>
-      <c r="I297" s="1"/>
-      <c r="J297" s="2"/>
-      <c r="K297" s="1"/>
+      <c r="D297" t="s">
+        <v>38</v>
+      </c>
+      <c r="E297">
+        <v>980</v>
+      </c>
+      <c r="F297" t="s">
+        <v>44</v>
+      </c>
+      <c r="H297" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I297" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J297" s="2">
+        <v>0</v>
+      </c>
+      <c r="K297" s="1">
+        <v>46219.686111111114</v>
+      </c>
+      <c r="L297">
+        <v>0</v>
+      </c>
+      <c r="M297" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="298" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H298" s="2"/>
-      <c r="I298" s="1"/>
-      <c r="J298" s="2"/>
-      <c r="K298" s="1"/>
+      <c r="D298" t="s">
+        <v>38</v>
+      </c>
+      <c r="E298">
+        <v>848</v>
+      </c>
+      <c r="F298" t="s">
+        <v>48</v>
+      </c>
+      <c r="H298" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J298" s="2">
+        <v>0</v>
+      </c>
+      <c r="K298" s="1">
+        <v>46219.686805555553</v>
+      </c>
+      <c r="L298">
+        <v>0</v>
+      </c>
+      <c r="M298" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="299" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H299" s="2"/>
-      <c r="I299" s="1"/>
-      <c r="J299" s="2"/>
-      <c r="K299" s="1"/>
+      <c r="D299" t="s">
+        <v>38</v>
+      </c>
+      <c r="E299">
+        <v>854</v>
+      </c>
+      <c r="F299" t="s">
+        <v>49</v>
+      </c>
+      <c r="H299" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I299" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J299" s="2">
+        <v>0</v>
+      </c>
+      <c r="K299" s="1">
+        <v>46219.6875</v>
+      </c>
+      <c r="L299">
+        <v>0</v>
+      </c>
+      <c r="M299" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="300" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H300" s="2"/>
-      <c r="I300" s="1"/>
-      <c r="J300" s="2"/>
-      <c r="K300" s="1"/>
+      <c r="D300" t="s">
+        <v>38</v>
+      </c>
+      <c r="E300">
+        <v>850</v>
+      </c>
+      <c r="F300" t="s">
+        <v>50</v>
+      </c>
+      <c r="H300" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I300" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J300" s="2">
+        <v>0</v>
+      </c>
+      <c r="K300" s="1">
+        <v>46219.6875</v>
+      </c>
+      <c r="L300">
+        <v>0</v>
+      </c>
+      <c r="M300" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="301" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H301" s="2"/>
@@ -11229,6 +11367,7 @@
     <row r="697" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H697" s="2"/>
       <c r="I697" s="1"/>
+      <c r="J697" s="2"/>
       <c r="K697" s="1"/>
     </row>
     <row r="698" spans="8:11" x14ac:dyDescent="0.3">
@@ -11538,6 +11677,7 @@
     <row r="749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H749" s="2"/>
       <c r="I749" s="1"/>
+      <c r="J749" s="2"/>
       <c r="K749" s="1"/>
     </row>
     <row r="750" spans="8:11" x14ac:dyDescent="0.3">
@@ -11627,6 +11767,7 @@
     <row r="764" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
+      <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
     <row r="765" spans="8:11" x14ac:dyDescent="0.3">
@@ -11733,6 +11874,7 @@
     </row>
     <row r="782" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I782" s="1"/>
+      <c r="J782" s="2"/>
       <c r="K782" s="1"/>
     </row>
     <row r="783" spans="8:11" x14ac:dyDescent="0.3">
@@ -11750,6 +11892,7 @@
     <row r="785" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H785" s="2"/>
       <c r="I785" s="1"/>
+      <c r="J785" s="2"/>
       <c r="K785" s="1"/>
     </row>
     <row r="786" spans="8:11" x14ac:dyDescent="0.3">
@@ -11761,6 +11904,7 @@
     <row r="787" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H787" s="2"/>
       <c r="I787" s="1"/>
+      <c r="J787" s="2"/>
       <c r="K787" s="1"/>
     </row>
     <row r="788" spans="8:11" x14ac:dyDescent="0.3">
@@ -11802,6 +11946,7 @@
     <row r="794" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H794" s="2"/>
       <c r="I794" s="1"/>
+      <c r="J794" s="2"/>
       <c r="K794" s="1"/>
     </row>
     <row r="795" spans="8:11" x14ac:dyDescent="0.3">
@@ -11825,6 +11970,7 @@
     <row r="798" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H798" s="2"/>
       <c r="I798" s="1"/>
+      <c r="J798" s="2"/>
       <c r="K798" s="1"/>
     </row>
     <row r="799" spans="8:11" x14ac:dyDescent="0.3">
@@ -11848,6 +11994,7 @@
     <row r="802" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H802" s="2"/>
       <c r="I802" s="1"/>
+      <c r="J802" s="2"/>
       <c r="K802" s="1"/>
     </row>
     <row r="803" spans="8:11" x14ac:dyDescent="0.3">
@@ -11865,6 +12012,7 @@
     <row r="805" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H805" s="2"/>
       <c r="I805" s="1"/>
+      <c r="J805" s="2"/>
       <c r="K805" s="1"/>
     </row>
     <row r="806" spans="8:11" x14ac:dyDescent="0.3">
@@ -11876,11 +12024,13 @@
     <row r="807" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H807" s="2"/>
       <c r="I807" s="1"/>
+      <c r="J807" s="2"/>
       <c r="K807" s="1"/>
     </row>
     <row r="808" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H808" s="2"/>
       <c r="I808" s="1"/>
+      <c r="J808" s="2"/>
       <c r="K808" s="1"/>
     </row>
     <row r="809" spans="8:11" x14ac:dyDescent="0.3">
@@ -12000,6 +12150,7 @@
     <row r="828" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H828" s="2"/>
       <c r="I828" s="1"/>
+      <c r="J828" s="2"/>
       <c r="K828" s="1"/>
     </row>
     <row r="829" spans="8:11" x14ac:dyDescent="0.3">
@@ -12083,6 +12234,7 @@
     <row r="842" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H842" s="2"/>
       <c r="I842" s="1"/>
+      <c r="J842" s="2"/>
       <c r="K842" s="1"/>
     </row>
     <row r="843" spans="8:11" x14ac:dyDescent="0.3">
@@ -12106,6 +12258,7 @@
     <row r="846" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H846" s="2"/>
       <c r="I846" s="1"/>
+      <c r="J846" s="2"/>
       <c r="K846" s="1"/>
     </row>
     <row r="847" spans="8:11" x14ac:dyDescent="0.3">
@@ -12117,6 +12270,7 @@
     <row r="848" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H848" s="2"/>
       <c r="I848" s="1"/>
+      <c r="J848" s="2"/>
       <c r="K848" s="1"/>
     </row>
     <row r="849" spans="8:11" x14ac:dyDescent="0.3">
@@ -12128,6 +12282,7 @@
     <row r="850" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H850" s="2"/>
       <c r="I850" s="1"/>
+      <c r="J850" s="2"/>
       <c r="K850" s="1"/>
     </row>
     <row r="851" spans="8:11" x14ac:dyDescent="0.3">
@@ -12175,6 +12330,7 @@
     <row r="858" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H858" s="2"/>
       <c r="I858" s="1"/>
+      <c r="J858" s="2"/>
       <c r="K858" s="1"/>
     </row>
     <row r="859" spans="8:11" x14ac:dyDescent="0.3">
@@ -12228,6 +12384,7 @@
     <row r="867" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H867" s="2"/>
       <c r="I867" s="1"/>
+      <c r="J867" s="2"/>
       <c r="K867" s="1"/>
     </row>
     <row r="868" spans="8:11" x14ac:dyDescent="0.3">
@@ -12400,6 +12557,7 @@
     <row r="896" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H896" s="2"/>
       <c r="I896" s="1"/>
+      <c r="J896" s="2"/>
       <c r="K896" s="1"/>
     </row>
     <row r="897" spans="8:11" x14ac:dyDescent="0.3">
@@ -12411,6 +12569,7 @@
     <row r="898" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H898" s="2"/>
       <c r="I898" s="1"/>
+      <c r="J898" s="2"/>
       <c r="K898" s="1"/>
     </row>
     <row r="899" spans="8:11" x14ac:dyDescent="0.3">
@@ -12488,6 +12647,7 @@
     <row r="911" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H911" s="2"/>
       <c r="I911" s="1"/>
+      <c r="J911" s="2"/>
       <c r="K911" s="1"/>
     </row>
     <row r="912" spans="8:11" x14ac:dyDescent="0.3">
@@ -12505,6 +12665,7 @@
     <row r="914" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H914" s="2"/>
       <c r="I914" s="1"/>
+      <c r="J914" s="2"/>
       <c r="K914" s="1"/>
     </row>
     <row r="915" spans="8:11" x14ac:dyDescent="0.3">
@@ -12552,6 +12713,7 @@
     <row r="922" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H922" s="2"/>
       <c r="I922" s="1"/>
+      <c r="J922" s="2"/>
       <c r="K922" s="1"/>
     </row>
     <row r="923" spans="8:11" x14ac:dyDescent="0.3">
@@ -12664,6 +12826,7 @@
     <row r="941" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H941" s="2"/>
       <c r="I941" s="1"/>
+      <c r="J941" s="2"/>
       <c r="K941" s="1"/>
     </row>
     <row r="942" spans="8:11" x14ac:dyDescent="0.3">
@@ -12723,6 +12886,7 @@
     <row r="951" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H951" s="2"/>
       <c r="I951" s="1"/>
+      <c r="J951" s="2"/>
       <c r="K951" s="1"/>
     </row>
     <row r="952" spans="8:11" x14ac:dyDescent="0.3">
@@ -12734,6 +12898,7 @@
     <row r="953" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H953" s="2"/>
       <c r="I953" s="1"/>
+      <c r="J953" s="2"/>
       <c r="K953" s="1"/>
     </row>
     <row r="954" spans="8:11" x14ac:dyDescent="0.3">
@@ -12805,6 +12970,7 @@
     <row r="965" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H965" s="2"/>
       <c r="I965" s="1"/>
+      <c r="J965" s="2"/>
       <c r="K965" s="1"/>
     </row>
     <row r="966" spans="8:11" x14ac:dyDescent="0.3">
@@ -12857,6 +13023,7 @@
     </row>
     <row r="974" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I974" s="1"/>
+      <c r="J974" s="2"/>
       <c r="K974" s="1"/>
     </row>
     <row r="975" spans="8:11" x14ac:dyDescent="0.3">
@@ -12933,11 +13100,13 @@
     <row r="987" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H987" s="2"/>
       <c r="I987" s="1"/>
+      <c r="J987" s="2"/>
       <c r="K987" s="1"/>
     </row>
     <row r="988" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H988" s="2"/>
       <c r="I988" s="1"/>
+      <c r="J988" s="2"/>
       <c r="K988" s="1"/>
     </row>
     <row r="989" spans="8:11" x14ac:dyDescent="0.3">
@@ -12997,6 +13166,7 @@
     <row r="998" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H998" s="2"/>
       <c r="I998" s="1"/>
+      <c r="J998" s="2"/>
       <c r="K998" s="1"/>
     </row>
     <row r="999" spans="8:11" x14ac:dyDescent="0.3">
@@ -13008,6 +13178,7 @@
     <row r="1000" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1000" s="2"/>
       <c r="I1000" s="1"/>
+      <c r="J1000" s="2"/>
       <c r="K1000" s="1"/>
     </row>
     <row r="1001" spans="8:11" x14ac:dyDescent="0.3">
@@ -13019,11 +13190,13 @@
     <row r="1002" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1002" s="2"/>
       <c r="I1002" s="1"/>
+      <c r="J1002" s="2"/>
       <c r="K1002" s="1"/>
     </row>
     <row r="1003" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1003" s="2"/>
       <c r="I1003" s="1"/>
+      <c r="J1003" s="2"/>
       <c r="K1003" s="1"/>
     </row>
     <row r="1004" spans="8:11" x14ac:dyDescent="0.3">
@@ -13077,6 +13250,7 @@
     <row r="1012" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1012" s="2"/>
       <c r="I1012" s="1"/>
+      <c r="J1012" s="2"/>
       <c r="K1012" s="1"/>
     </row>
     <row r="1013" spans="8:11" x14ac:dyDescent="0.3">
@@ -13093,6 +13267,7 @@
     </row>
     <row r="1015" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1015" s="1"/>
+      <c r="J1015" s="2"/>
       <c r="K1015" s="1"/>
     </row>
     <row r="1016" spans="8:11" x14ac:dyDescent="0.3">
@@ -13116,6 +13291,7 @@
     <row r="1019" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1019" s="2"/>
       <c r="I1019" s="1"/>
+      <c r="J1019" s="2"/>
       <c r="K1019" s="1"/>
     </row>
     <row r="1020" spans="8:11" x14ac:dyDescent="0.3">
@@ -13133,6 +13309,7 @@
     <row r="1022" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1022" s="2"/>
       <c r="I1022" s="1"/>
+      <c r="J1022" s="2"/>
       <c r="K1022" s="1"/>
     </row>
     <row r="1023" spans="8:11" x14ac:dyDescent="0.3">
@@ -13179,11 +13356,13 @@
     </row>
     <row r="1030" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1030" s="1"/>
+      <c r="J1030" s="2"/>
       <c r="K1030" s="1"/>
     </row>
     <row r="1031" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1031" s="2"/>
       <c r="I1031" s="1"/>
+      <c r="J1031" s="2"/>
       <c r="K1031" s="1"/>
     </row>
     <row r="1032" spans="8:11" x14ac:dyDescent="0.3">
@@ -13225,11 +13404,13 @@
     <row r="1038" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1038" s="2"/>
       <c r="I1038" s="1"/>
+      <c r="J1038" s="2"/>
       <c r="K1038" s="1"/>
     </row>
     <row r="1039" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1039" s="2"/>
       <c r="I1039" s="1"/>
+      <c r="J1039" s="2"/>
       <c r="K1039" s="1"/>
     </row>
     <row r="1040" spans="8:11" x14ac:dyDescent="0.3">
@@ -13247,6 +13428,7 @@
     <row r="1042" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1042" s="2"/>
       <c r="I1042" s="1"/>
+      <c r="J1042" s="2"/>
       <c r="K1042" s="1"/>
     </row>
     <row r="1043" spans="8:11" x14ac:dyDescent="0.3">
@@ -13258,6 +13440,7 @@
     <row r="1044" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1044" s="2"/>
       <c r="I1044" s="1"/>
+      <c r="J1044" s="2"/>
       <c r="K1044" s="1"/>
     </row>
     <row r="1045" spans="8:11" x14ac:dyDescent="0.3">
@@ -13269,6 +13452,7 @@
     <row r="1046" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1046" s="2"/>
       <c r="I1046" s="1"/>
+      <c r="J1046" s="2"/>
       <c r="K1046" s="1"/>
     </row>
     <row r="1047" spans="8:11" x14ac:dyDescent="0.3">
@@ -13286,6 +13470,7 @@
     <row r="1049" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1049" s="2"/>
       <c r="I1049" s="1"/>
+      <c r="J1049" s="2"/>
       <c r="K1049" s="1"/>
     </row>
     <row r="1050" spans="8:11" x14ac:dyDescent="0.3">
@@ -13363,6 +13548,7 @@
     <row r="1062" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1062" s="2"/>
       <c r="I1062" s="1"/>
+      <c r="J1062" s="2"/>
       <c r="K1062" s="1"/>
     </row>
     <row r="1063" spans="8:11" x14ac:dyDescent="0.3">
@@ -13392,6 +13578,7 @@
     <row r="1067" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1067" s="2"/>
       <c r="I1067" s="1"/>
+      <c r="J1067" s="2"/>
       <c r="K1067" s="1"/>
     </row>
     <row r="1068" spans="8:11" x14ac:dyDescent="0.3">
@@ -13403,16 +13590,19 @@
     <row r="1069" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1069" s="2"/>
       <c r="I1069" s="1"/>
+      <c r="J1069" s="2"/>
       <c r="K1069" s="1"/>
     </row>
     <row r="1070" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1070" s="2"/>
       <c r="I1070" s="1"/>
+      <c r="J1070" s="2"/>
       <c r="K1070" s="1"/>
     </row>
     <row r="1071" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1071" s="2"/>
       <c r="I1071" s="1"/>
+      <c r="J1071" s="2"/>
       <c r="K1071" s="1"/>
     </row>
     <row r="1072" spans="8:11" x14ac:dyDescent="0.3">
@@ -13424,16 +13614,19 @@
     <row r="1073" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1073" s="2"/>
       <c r="I1073" s="1"/>
+      <c r="J1073" s="2"/>
       <c r="K1073" s="1"/>
     </row>
     <row r="1074" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1074" s="2"/>
       <c r="I1074" s="1"/>
+      <c r="J1074" s="2"/>
       <c r="K1074" s="1"/>
     </row>
     <row r="1075" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1075" s="2"/>
       <c r="I1075" s="1"/>
+      <c r="J1075" s="2"/>
       <c r="K1075" s="1"/>
     </row>
     <row r="1076" spans="8:11" x14ac:dyDescent="0.3">
@@ -13445,11 +13638,13 @@
     <row r="1077" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1077" s="2"/>
       <c r="I1077" s="1"/>
+      <c r="J1077" s="2"/>
       <c r="K1077" s="1"/>
     </row>
     <row r="1078" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1078" s="2"/>
       <c r="I1078" s="1"/>
+      <c r="J1078" s="2"/>
       <c r="K1078" s="1"/>
     </row>
     <row r="1079" spans="8:11" x14ac:dyDescent="0.3">
@@ -13473,6 +13668,7 @@
     <row r="1082" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1082" s="2"/>
       <c r="I1082" s="1"/>
+      <c r="J1082" s="2"/>
       <c r="K1082" s="1"/>
     </row>
     <row r="1083" spans="8:11" x14ac:dyDescent="0.3">
@@ -13514,6 +13710,7 @@
     <row r="1089" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1089" s="2"/>
       <c r="I1089" s="1"/>
+      <c r="J1089" s="2"/>
       <c r="K1089" s="1"/>
     </row>
     <row r="1090" spans="8:11" x14ac:dyDescent="0.3">
@@ -13543,21 +13740,25 @@
     <row r="1094" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1094" s="2"/>
       <c r="I1094" s="1"/>
+      <c r="J1094" s="2"/>
       <c r="K1094" s="1"/>
     </row>
     <row r="1095" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1095" s="2"/>
       <c r="I1095" s="1"/>
+      <c r="J1095" s="2"/>
       <c r="K1095" s="1"/>
     </row>
     <row r="1096" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1096" s="2"/>
       <c r="I1096" s="1"/>
+      <c r="J1096" s="2"/>
       <c r="K1096" s="1"/>
     </row>
     <row r="1097" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1097" s="2"/>
       <c r="I1097" s="1"/>
+      <c r="J1097" s="2"/>
       <c r="K1097" s="1"/>
     </row>
     <row r="1098" spans="8:11" x14ac:dyDescent="0.3">
@@ -13569,6 +13770,7 @@
     <row r="1099" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1099" s="2"/>
       <c r="I1099" s="1"/>
+      <c r="J1099" s="2"/>
       <c r="K1099" s="1"/>
     </row>
     <row r="1100" spans="8:11" x14ac:dyDescent="0.3">
@@ -13586,6 +13788,7 @@
     <row r="1102" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1102" s="2"/>
       <c r="I1102" s="1"/>
+      <c r="J1102" s="2"/>
       <c r="K1102" s="1"/>
     </row>
     <row r="1103" spans="8:11" x14ac:dyDescent="0.3">
@@ -13625,11 +13828,13 @@
     <row r="1109" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1109" s="2"/>
       <c r="I1109" s="1"/>
+      <c r="J1109" s="2"/>
       <c r="K1109" s="1"/>
     </row>
     <row r="1110" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1110" s="2"/>
       <c r="I1110" s="1"/>
+      <c r="J1110" s="2"/>
       <c r="K1110" s="1"/>
     </row>
     <row r="1111" spans="8:11" x14ac:dyDescent="0.3">
@@ -13677,6 +13882,7 @@
     <row r="1118" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1118" s="2"/>
       <c r="I1118" s="1"/>
+      <c r="J1118" s="2"/>
       <c r="K1118" s="1"/>
     </row>
     <row r="1119" spans="8:11" x14ac:dyDescent="0.3">
@@ -13706,6 +13912,7 @@
     <row r="1123" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1123" s="2"/>
       <c r="I1123" s="1"/>
+      <c r="J1123" s="2"/>
       <c r="K1123" s="1"/>
     </row>
     <row r="1124" spans="8:11" x14ac:dyDescent="0.3">
@@ -13782,6 +13989,7 @@
     <row r="1136" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1136" s="2"/>
       <c r="I1136" s="1"/>
+      <c r="J1136" s="2"/>
       <c r="K1136" s="1"/>
     </row>
     <row r="1137" spans="8:11" x14ac:dyDescent="0.3">
@@ -13828,6 +14036,7 @@
     <row r="1144" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1144" s="2"/>
       <c r="I1144" s="1"/>
+      <c r="J1144" s="2"/>
       <c r="K1144" s="1"/>
     </row>
     <row r="1145" spans="8:11" x14ac:dyDescent="0.3">
@@ -13863,11 +14072,13 @@
     <row r="1150" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1150" s="2"/>
       <c r="I1150" s="1"/>
+      <c r="J1150" s="2"/>
       <c r="K1150" s="1"/>
     </row>
     <row r="1151" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1151" s="2"/>
       <c r="I1151" s="1"/>
+      <c r="J1151" s="2"/>
       <c r="K1151" s="1"/>
     </row>
     <row r="1152" spans="8:11" x14ac:dyDescent="0.3">
@@ -13884,6 +14095,7 @@
     <row r="1154" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1154" s="2"/>
       <c r="I1154" s="1"/>
+      <c r="J1154" s="2"/>
       <c r="K1154" s="1"/>
     </row>
     <row r="1155" spans="8:11" x14ac:dyDescent="0.3">
@@ -13894,6 +14106,7 @@
     <row r="1156" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1156" s="2"/>
       <c r="I1156" s="1"/>
+      <c r="J1156" s="2"/>
       <c r="K1156" s="1"/>
     </row>
     <row r="1157" spans="8:11" x14ac:dyDescent="0.3">
@@ -13929,6 +14142,7 @@
     <row r="1162" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1162" s="2"/>
       <c r="I1162" s="1"/>
+      <c r="J1162" s="2"/>
       <c r="K1162" s="1"/>
     </row>
     <row r="1163" spans="8:11" x14ac:dyDescent="0.3">
@@ -13940,6 +14154,7 @@
     <row r="1164" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1164" s="2"/>
       <c r="I1164" s="1"/>
+      <c r="J1164" s="2"/>
       <c r="K1164" s="1"/>
     </row>
     <row r="1165" spans="8:11" x14ac:dyDescent="0.3">
@@ -13951,6 +14166,7 @@
     <row r="1166" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1166" s="2"/>
       <c r="I1166" s="1"/>
+      <c r="J1166" s="2"/>
       <c r="K1166" s="1"/>
     </row>
     <row r="1167" spans="8:11" x14ac:dyDescent="0.3">
@@ -13962,6 +14178,7 @@
     <row r="1168" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1168" s="2"/>
       <c r="I1168" s="1"/>
+      <c r="J1168" s="2"/>
       <c r="K1168" s="1"/>
     </row>
     <row r="1169" spans="8:11" x14ac:dyDescent="0.3">
@@ -13973,6 +14190,7 @@
     <row r="1170" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1170" s="2"/>
       <c r="I1170" s="1"/>
+      <c r="J1170" s="2"/>
       <c r="K1170" s="1"/>
     </row>
     <row r="1171" spans="8:11" x14ac:dyDescent="0.3">
@@ -14014,6 +14232,7 @@
     <row r="1177" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1177" s="2"/>
       <c r="I1177" s="1"/>
+      <c r="J1177" s="2"/>
       <c r="K1177" s="1"/>
     </row>
     <row r="1178" spans="8:11" x14ac:dyDescent="0.3">
@@ -14031,6 +14250,7 @@
     <row r="1180" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1180" s="2"/>
       <c r="I1180" s="1"/>
+      <c r="J1180" s="2"/>
       <c r="K1180" s="1"/>
     </row>
     <row r="1181" spans="8:11" x14ac:dyDescent="0.3">
@@ -14048,6 +14268,7 @@
     <row r="1183" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1183" s="2"/>
       <c r="I1183" s="1"/>
+      <c r="J1183" s="2"/>
       <c r="K1183" s="1"/>
     </row>
     <row r="1184" spans="8:11" x14ac:dyDescent="0.3">
@@ -14089,6 +14310,7 @@
     <row r="1190" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1190" s="2"/>
       <c r="I1190" s="1"/>
+      <c r="J1190" s="2"/>
       <c r="K1190" s="1"/>
     </row>
     <row r="1191" spans="8:11" x14ac:dyDescent="0.3">
@@ -14112,6 +14334,7 @@
     <row r="1194" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1194" s="2"/>
       <c r="I1194" s="1"/>
+      <c r="J1194" s="2"/>
       <c r="K1194" s="1"/>
     </row>
     <row r="1195" spans="8:11" x14ac:dyDescent="0.3">
@@ -14158,6 +14381,7 @@
     <row r="1202" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1202" s="2"/>
       <c r="I1202" s="1"/>
+      <c r="J1202" s="2"/>
       <c r="K1202" s="1"/>
     </row>
     <row r="1203" spans="8:11" x14ac:dyDescent="0.3">
@@ -14193,6 +14417,7 @@
     <row r="1208" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1208" s="2"/>
       <c r="I1208" s="1"/>
+      <c r="J1208" s="2"/>
       <c r="K1208" s="1"/>
     </row>
     <row r="1209" spans="8:11" x14ac:dyDescent="0.3">
@@ -14216,6 +14441,7 @@
     <row r="1212" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1212" s="2"/>
       <c r="I1212" s="1"/>
+      <c r="J1212" s="2"/>
       <c r="K1212" s="1"/>
     </row>
     <row r="1213" spans="8:11" x14ac:dyDescent="0.3">
@@ -14256,6 +14482,7 @@
     <row r="1219" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1219" s="2"/>
       <c r="I1219" s="1"/>
+      <c r="J1219" s="2"/>
       <c r="K1219" s="1"/>
     </row>
     <row r="1220" spans="8:11" x14ac:dyDescent="0.3">
@@ -14273,11 +14500,13 @@
     <row r="1222" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1222" s="2"/>
       <c r="I1222" s="1"/>
+      <c r="J1222" s="2"/>
       <c r="K1222" s="1"/>
     </row>
     <row r="1223" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1223" s="2"/>
       <c r="I1223" s="1"/>
+      <c r="J1223" s="2"/>
       <c r="K1223" s="1"/>
     </row>
     <row r="1224" spans="8:11" x14ac:dyDescent="0.3">
@@ -14336,6 +14565,7 @@
     <row r="1233" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1233" s="2"/>
       <c r="I1233" s="1"/>
+      <c r="J1233" s="2"/>
       <c r="K1233" s="1"/>
     </row>
     <row r="1234" spans="8:11" x14ac:dyDescent="0.3">
@@ -14352,6 +14582,7 @@
     <row r="1236" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1236" s="2"/>
       <c r="I1236" s="1"/>
+      <c r="J1236" s="2"/>
       <c r="K1236" s="1"/>
     </row>
     <row r="1237" spans="8:11" x14ac:dyDescent="0.3">
@@ -14363,6 +14594,7 @@
     <row r="1238" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1238" s="2"/>
       <c r="I1238" s="1"/>
+      <c r="J1238" s="2"/>
       <c r="K1238" s="1"/>
     </row>
     <row r="1239" spans="8:11" x14ac:dyDescent="0.3">
@@ -14374,11 +14606,13 @@
     <row r="1240" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1240" s="2"/>
       <c r="I1240" s="1"/>
+      <c r="J1240" s="2"/>
       <c r="K1240" s="1"/>
     </row>
     <row r="1241" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1241" s="2"/>
       <c r="I1241" s="1"/>
+      <c r="J1241" s="2"/>
       <c r="K1241" s="1"/>
     </row>
     <row r="1242" spans="8:11" x14ac:dyDescent="0.3">
@@ -14414,6 +14648,7 @@
     <row r="1247" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1247" s="2"/>
       <c r="I1247" s="1"/>
+      <c r="J1247" s="2"/>
       <c r="K1247" s="1"/>
     </row>
     <row r="1248" spans="8:11" x14ac:dyDescent="0.3">
@@ -14466,6 +14701,7 @@
     <row r="1256" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1256" s="2"/>
       <c r="I1256" s="1"/>
+      <c r="J1256" s="2"/>
       <c r="K1256" s="1"/>
     </row>
     <row r="1257" spans="8:11" x14ac:dyDescent="0.3">
@@ -14476,6 +14712,7 @@
     </row>
     <row r="1258" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1258" s="1"/>
+      <c r="J1258" s="2"/>
       <c r="K1258" s="1"/>
     </row>
     <row r="1259" spans="8:11" x14ac:dyDescent="0.3">
@@ -14491,6 +14728,7 @@
     </row>
     <row r="1261" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1261" s="1"/>
+      <c r="J1261" s="2"/>
       <c r="K1261" s="1"/>
     </row>
     <row r="1262" spans="8:11" x14ac:dyDescent="0.3">
@@ -14514,16 +14752,19 @@
     <row r="1265" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1265" s="2"/>
       <c r="I1265" s="1"/>
+      <c r="J1265" s="2"/>
       <c r="K1265" s="1"/>
     </row>
     <row r="1266" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1266" s="2"/>
       <c r="I1266" s="1"/>
+      <c r="J1266" s="2"/>
       <c r="K1266" s="1"/>
     </row>
     <row r="1267" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1267" s="2"/>
       <c r="I1267" s="1"/>
+      <c r="J1267" s="2"/>
       <c r="K1267" s="1"/>
     </row>
     <row r="1268" spans="8:11" x14ac:dyDescent="0.3">
@@ -14594,6 +14835,7 @@
     <row r="1279" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1279" s="2"/>
       <c r="I1279" s="1"/>
+      <c r="J1279" s="2"/>
       <c r="K1279" s="1"/>
     </row>
     <row r="1280" spans="8:11" x14ac:dyDescent="0.3">
@@ -14605,6 +14847,7 @@
     <row r="1281" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1281" s="2"/>
       <c r="I1281" s="1"/>
+      <c r="J1281" s="2"/>
       <c r="K1281" s="1"/>
     </row>
     <row r="1282" spans="8:11" x14ac:dyDescent="0.3">
@@ -14705,6 +14948,8 @@
     <row r="1298" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1298" s="2"/>
       <c r="I1298" s="1"/>
+      <c r="J1298" s="2"/>
+      <c r="K1298" s="1"/>
     </row>
     <row r="1299" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1299" s="2"/>
@@ -14761,6 +15006,7 @@
     <row r="1308" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1308" s="2"/>
       <c r="I1308" s="1"/>
+      <c r="J1308" s="2"/>
       <c r="K1308" s="1"/>
     </row>
     <row r="1309" spans="8:11" x14ac:dyDescent="0.3">
@@ -14784,6 +15030,7 @@
     <row r="1312" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1312" s="2"/>
       <c r="I1312" s="1"/>
+      <c r="J1312" s="2"/>
       <c r="K1312" s="1"/>
     </row>
     <row r="1313" spans="8:11" x14ac:dyDescent="0.3">
@@ -14908,6 +15155,7 @@
     <row r="1333" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1333" s="2"/>
       <c r="I1333" s="1"/>
+      <c r="J1333" s="2"/>
       <c r="K1333" s="1"/>
     </row>
     <row r="1334" spans="8:11" x14ac:dyDescent="0.3">
@@ -15066,6 +15314,7 @@
     <row r="1360" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1360" s="2"/>
       <c r="I1360" s="1"/>
+      <c r="J1360" s="2"/>
       <c r="K1360" s="1"/>
     </row>
     <row r="1361" spans="8:11" x14ac:dyDescent="0.3">
@@ -15083,6 +15332,7 @@
     <row r="1363" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1363" s="2"/>
       <c r="I1363" s="1"/>
+      <c r="J1363" s="2"/>
       <c r="K1363" s="1"/>
     </row>
     <row r="1364" spans="8:11" x14ac:dyDescent="0.3">
@@ -15123,6 +15373,7 @@
     <row r="1370" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1370" s="2"/>
       <c r="I1370" s="1"/>
+      <c r="J1370" s="2"/>
       <c r="K1370" s="1"/>
     </row>
     <row r="1371" spans="8:11" x14ac:dyDescent="0.3">
@@ -15455,6 +15706,7 @@
     <row r="1427" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1427" s="2"/>
       <c r="I1427" s="1"/>
+      <c r="J1427" s="2"/>
       <c r="K1427" s="1"/>
     </row>
     <row r="1428" spans="8:11" x14ac:dyDescent="0.3">
@@ -15543,6 +15795,7 @@
     <row r="1442" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1442" s="2"/>
       <c r="I1442" s="1"/>
+      <c r="J1442" s="2"/>
       <c r="K1442" s="1"/>
     </row>
     <row r="1443" spans="8:11" x14ac:dyDescent="0.3">
@@ -15636,6 +15889,7 @@
     <row r="1458" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1458" s="2"/>
       <c r="I1458" s="1"/>
+      <c r="J1458" s="2"/>
       <c r="K1458" s="1"/>
     </row>
     <row r="1459" spans="8:11" x14ac:dyDescent="0.3">
@@ -15695,11 +15949,13 @@
     <row r="1468" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1468" s="2"/>
       <c r="I1468" s="1"/>
+      <c r="J1468" s="2"/>
       <c r="K1468" s="1"/>
     </row>
     <row r="1469" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1469" s="2"/>
       <c r="I1469" s="1"/>
+      <c r="J1469" s="2"/>
       <c r="K1469" s="1"/>
     </row>
     <row r="1470" spans="8:11" x14ac:dyDescent="0.3">
@@ -15751,6 +16007,7 @@
     </row>
     <row r="1478" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1478" s="1"/>
+      <c r="J1478" s="2"/>
       <c r="K1478" s="1"/>
     </row>
     <row r="1479" spans="8:11" x14ac:dyDescent="0.3">
@@ -15792,6 +16049,7 @@
     <row r="1485" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1485" s="2"/>
       <c r="I1485" s="1"/>
+      <c r="J1485" s="2"/>
       <c r="K1485" s="1"/>
     </row>
     <row r="1486" spans="8:11" x14ac:dyDescent="0.3">
@@ -15836,6 +16094,7 @@
     </row>
     <row r="1493" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1493" s="1"/>
+      <c r="J1493" s="2"/>
       <c r="K1493" s="1"/>
     </row>
     <row r="1494" spans="8:11" x14ac:dyDescent="0.3">
@@ -15882,11 +16141,13 @@
     <row r="1501" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1501" s="2"/>
       <c r="I1501" s="1"/>
+      <c r="J1501" s="2"/>
       <c r="K1501" s="1"/>
     </row>
     <row r="1502" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1502" s="2"/>
       <c r="I1502" s="1"/>
+      <c r="J1502" s="2"/>
       <c r="K1502" s="1"/>
     </row>
     <row r="1503" spans="8:11" x14ac:dyDescent="0.3">
@@ -16084,6 +16345,7 @@
     <row r="1535" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1535" s="2"/>
       <c r="I1535" s="1"/>
+      <c r="J1535" s="2"/>
       <c r="K1535" s="1"/>
     </row>
     <row r="1536" spans="8:11" x14ac:dyDescent="0.3">
@@ -16113,6 +16375,8 @@
     <row r="1540" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1540" s="2"/>
       <c r="I1540" s="1"/>
+      <c r="J1540" s="2"/>
+      <c r="K1540" s="1"/>
     </row>
     <row r="1541" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1541" s="1"/>
@@ -16128,6 +16392,7 @@
     <row r="1543" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1543" s="2"/>
       <c r="I1543" s="1"/>
+      <c r="J1543" s="2"/>
       <c r="K1543" s="1"/>
     </row>
     <row r="1544" spans="8:11" x14ac:dyDescent="0.3">
@@ -16187,6 +16452,7 @@
     <row r="1553" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1553" s="2"/>
       <c r="I1553" s="1"/>
+      <c r="J1553" s="2"/>
       <c r="K1553" s="1"/>
     </row>
     <row r="1554" spans="8:11" x14ac:dyDescent="0.3">
@@ -16258,6 +16524,7 @@
     <row r="1565" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1565" s="2"/>
       <c r="I1565" s="1"/>
+      <c r="J1565" s="2"/>
       <c r="K1565" s="1"/>
     </row>
     <row r="1566" spans="8:11" x14ac:dyDescent="0.3">
@@ -16299,6 +16566,7 @@
     <row r="1572" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1572" s="2"/>
       <c r="I1572" s="1"/>
+      <c r="J1572" s="2"/>
       <c r="K1572" s="1"/>
     </row>
     <row r="1573" spans="8:11" x14ac:dyDescent="0.3">
@@ -16417,6 +16685,7 @@
     <row r="1592" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1592" s="2"/>
       <c r="I1592" s="1"/>
+      <c r="J1592" s="2"/>
       <c r="K1592" s="1"/>
     </row>
     <row r="1593" spans="8:11" x14ac:dyDescent="0.3">
@@ -16481,6 +16750,7 @@
     <row r="1603" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1603" s="2"/>
       <c r="I1603" s="1"/>
+      <c r="J1603" s="2"/>
       <c r="K1603" s="1"/>
     </row>
     <row r="1604" spans="8:11" x14ac:dyDescent="0.3">
@@ -16605,6 +16875,7 @@
     <row r="1624" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1624" s="2"/>
       <c r="I1624" s="1"/>
+      <c r="J1624" s="2"/>
       <c r="K1624" s="1"/>
     </row>
     <row r="1625" spans="8:11" x14ac:dyDescent="0.3">
@@ -16831,6 +17102,7 @@
     <row r="1662" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1662" s="2"/>
       <c r="I1662" s="1"/>
+      <c r="J1662" s="2"/>
       <c r="K1662" s="1"/>
     </row>
     <row r="1663" spans="8:11" x14ac:dyDescent="0.3">
@@ -16948,6 +17220,7 @@
     <row r="1682" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1682" s="2"/>
       <c r="I1682" s="1"/>
+      <c r="J1682" s="2"/>
       <c r="K1682" s="1"/>
     </row>
     <row r="1683" spans="8:11" x14ac:dyDescent="0.3">
@@ -17031,6 +17304,7 @@
     <row r="1696" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1696" s="2"/>
       <c r="I1696" s="1"/>
+      <c r="J1696" s="2"/>
       <c r="K1696" s="1"/>
     </row>
     <row r="1697" spans="8:11" x14ac:dyDescent="0.3">
@@ -17090,6 +17364,7 @@
     <row r="1706" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1706" s="2"/>
       <c r="I1706" s="1"/>
+      <c r="J1706" s="2"/>
       <c r="K1706" s="1"/>
     </row>
     <row r="1707" spans="8:11" x14ac:dyDescent="0.3">
@@ -17113,6 +17388,7 @@
     <row r="1710" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1710" s="2"/>
       <c r="I1710" s="1"/>
+      <c r="J1710" s="2"/>
       <c r="K1710" s="1"/>
     </row>
     <row r="1711" spans="8:11" x14ac:dyDescent="0.3">
@@ -17160,6 +17436,7 @@
     <row r="1718" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1718" s="2"/>
       <c r="I1718" s="1"/>
+      <c r="J1718" s="2"/>
       <c r="K1718" s="1"/>
     </row>
     <row r="1719" spans="8:11" x14ac:dyDescent="0.3">
@@ -17219,6 +17496,7 @@
     <row r="1728" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1728" s="2"/>
       <c r="I1728" s="1"/>
+      <c r="J1728" s="2"/>
       <c r="K1728" s="1"/>
     </row>
     <row r="1729" spans="8:11" x14ac:dyDescent="0.3">
@@ -17242,6 +17520,7 @@
     <row r="1732" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1732" s="2"/>
       <c r="I1732" s="1"/>
+      <c r="J1732" s="2"/>
       <c r="K1732" s="1"/>
     </row>
     <row r="1733" spans="8:11" x14ac:dyDescent="0.3">
@@ -17259,6 +17538,7 @@
     <row r="1735" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1735" s="2"/>
       <c r="I1735" s="1"/>
+      <c r="J1735" s="2"/>
       <c r="K1735" s="1"/>
     </row>
     <row r="1736" spans="8:11" x14ac:dyDescent="0.3">
@@ -17342,6 +17622,7 @@
     <row r="1749" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1749" s="2"/>
       <c r="I1749" s="1"/>
+      <c r="J1749" s="2"/>
       <c r="K1749" s="1"/>
     </row>
     <row r="1750" spans="8:11" x14ac:dyDescent="0.3">
@@ -17533,6 +17814,7 @@
     <row r="1781" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1781" s="2"/>
       <c r="I1781" s="1"/>
+      <c r="J1781" s="2"/>
       <c r="K1781" s="1"/>
     </row>
     <row r="1782" spans="8:11" x14ac:dyDescent="0.3">
@@ -45389,6 +45671,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -45396,6 +45679,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -45403,6 +45687,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -45418,6 +45703,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -45427,6 +45713,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -45434,9 +45721,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -45444,12 +45737,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -45457,12 +45753,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -45474,9 +45773,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -45491,6 +45792,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -45517,6 +45819,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -45527,7 +45830,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -45535,6 +45843,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -45546,6 +45855,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -45553,6 +45863,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -45567,13 +45878,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -45584,15 +45901,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -45608,6 +45928,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -45626,6 +45947,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -45637,6 +45959,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -45654,18 +45977,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -45694,6 +46022,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -45701,9 +46030,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -45726,12 +46057,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -45746,9 +46080,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -45764,12 +46100,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -45790,6 +46128,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -45801,9 +46140,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -45815,6 +46156,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -45854,9 +46196,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -45864,9 +46208,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -45877,6 +46223,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -45884,18 +46231,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -45903,6 +46258,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -45913,6 +46269,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -45939,15 +46296,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -45969,6 +46330,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -45976,9 +46338,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -45986,6 +46350,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -45997,6 +46362,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -46011,6 +46377,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -46020,6 +46390,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -46031,6 +46402,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -46041,10 +46413,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -46052,6 +46429,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -46066,6 +46444,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -46088,6 +46467,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -46107,25 +46487,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -46133,6 +46525,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -46140,15 +46533,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -46162,6 +46562,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -46180,9 +46581,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -46190,9 +46593,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -46200,6 +46605,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -46216,10 +46622,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB863DCA-2A06-4BDE-8EE1-680930373CE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EA36EB3-7332-4A92-8559-A8BAB25D4C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1505" uniqueCount="54">
   <si>
     <t>Company Name</t>
   </si>
@@ -137,19 +137,22 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
+    <t>Dangers of Distracted Driving</t>
+  </si>
+  <si>
     <t>Scene of an Accident</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
     <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNU-Def.Drive Distracted Driving</t>
+  </si>
+  <si>
+    <t>Vehicle &amp; Roadside Inspections CMV</t>
   </si>
   <si>
     <t>In Cab Distractions</t>
@@ -571,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="B1:K7400"/>
+  <dimension ref="A1:K7404"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -586,47 +589,47 @@
     <col min="11" max="11" width="8.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>849</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -647,15 +650,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>1133</v>
       </c>
       <c r="D3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -676,15 +679,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>1134</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -705,15 +708,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>855</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -734,15 +737,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>852</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -763,15 +766,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>1135</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -792,15 +795,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>980</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -821,15 +824,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>851</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -850,15 +853,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>1136</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -879,15 +882,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>981</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -908,15 +911,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>848</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -937,15 +940,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>1137</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -966,15 +969,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>854</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -995,15 +998,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>1138</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -1024,15 +1027,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>850</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -1055,13 +1058,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1139</v>
       </c>
       <c r="D17" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -1084,13 +1087,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>853</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -1113,13 +1116,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>1140</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -1142,13 +1145,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>849</v>
       </c>
       <c r="D20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
         <v>36</v>
@@ -1171,13 +1174,13 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>855</v>
       </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
         <v>36</v>
@@ -1208,13 +1211,13 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>852</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s">
         <v>36</v>
@@ -1237,13 +1240,13 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>980</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
         <v>36</v>
@@ -1274,13 +1277,13 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <v>851</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
         <v>36</v>
@@ -1303,13 +1306,13 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>981</v>
       </c>
       <c r="D27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
         <v>36</v>
@@ -1332,13 +1335,13 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>848</v>
       </c>
       <c r="D28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
         <v>36</v>
@@ -1361,13 +1364,13 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>854</v>
       </c>
       <c r="D29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
         <v>36</v>
@@ -1390,13 +1393,13 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>850</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
         <v>36</v>
@@ -1419,13 +1422,13 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>853</v>
       </c>
       <c r="D31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s">
         <v>36</v>
@@ -1448,13 +1451,13 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>849</v>
       </c>
       <c r="D32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
         <v>35</v>
@@ -1477,13 +1480,13 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>855</v>
       </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
         <v>35</v>
@@ -1514,13 +1517,13 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C35">
         <v>852</v>
       </c>
       <c r="D35" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
         <v>35</v>
@@ -1543,13 +1546,13 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <v>980</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
         <v>35</v>
@@ -1580,13 +1583,13 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <v>851</v>
       </c>
       <c r="D38" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
         <v>35</v>
@@ -1609,13 +1612,13 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <v>981</v>
       </c>
       <c r="D39" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F39" t="s">
         <v>35</v>
@@ -1638,13 +1641,13 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C40">
         <v>848</v>
       </c>
       <c r="D40" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
         <v>35</v>
@@ -1667,13 +1670,13 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C41">
         <v>854</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F41" t="s">
         <v>35</v>
@@ -1704,13 +1707,13 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>850</v>
       </c>
       <c r="D43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F43" t="s">
         <v>35</v>
@@ -1733,13 +1736,13 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>853</v>
       </c>
       <c r="D44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F44" t="s">
         <v>35</v>
@@ -1762,16 +1765,16 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C45">
         <v>849</v>
       </c>
       <c r="D45" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
@@ -1791,16 +1794,16 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C46">
         <v>855</v>
       </c>
       <c r="D46" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G46" t="s">
         <v>12</v>
@@ -1828,16 +1831,16 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C48">
         <v>852</v>
       </c>
       <c r="D48" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G48" t="s">
         <v>12</v>
@@ -1865,16 +1868,16 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C50">
         <v>980</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -1894,16 +1897,16 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C51">
         <v>851</v>
       </c>
       <c r="D51" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G51" t="s">
         <v>13</v>
@@ -1923,16 +1926,16 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C52">
         <v>981</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -1952,16 +1955,16 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C53">
         <v>848</v>
       </c>
       <c r="D53" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G53" t="s">
         <v>13</v>
@@ -1981,16 +1984,16 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C54">
         <v>854</v>
       </c>
       <c r="D54" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
@@ -2010,16 +2013,16 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C55">
         <v>850</v>
       </c>
       <c r="D55" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G55" t="s">
         <v>12</v>
@@ -2047,16 +2050,16 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C57">
         <v>853</v>
       </c>
       <c r="D57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G57" t="s">
         <v>13</v>
@@ -2076,13 +2079,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C58">
         <v>849</v>
       </c>
       <c r="D58" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
@@ -2113,13 +2116,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C60">
         <v>855</v>
       </c>
       <c r="D60" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -2142,13 +2145,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C61">
         <v>852</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
@@ -2171,13 +2174,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C62">
         <v>851</v>
       </c>
       <c r="D62" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -2200,13 +2203,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C63">
         <v>848</v>
       </c>
       <c r="D63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
@@ -2229,13 +2232,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C64">
         <v>854</v>
       </c>
       <c r="D64" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
@@ -2258,13 +2261,13 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C65">
         <v>850</v>
       </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
@@ -2287,13 +2290,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C66">
         <v>853</v>
       </c>
       <c r="D66" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -2316,16 +2319,16 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C67">
         <v>849</v>
       </c>
       <c r="D67" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G67" t="s">
         <v>12</v>
@@ -2353,16 +2356,16 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C69">
         <v>855</v>
       </c>
       <c r="D69" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G69" t="s">
         <v>10</v>
@@ -2382,16 +2385,16 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C70">
         <v>852</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G70" t="s">
         <v>13</v>
@@ -2411,16 +2414,16 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C71">
         <v>980</v>
       </c>
       <c r="D71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F71" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G71" t="s">
         <v>14</v>
@@ -2448,16 +2451,16 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C73">
         <v>851</v>
       </c>
       <c r="D73" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F73" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G73" t="s">
         <v>10</v>
@@ -2477,16 +2480,16 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C74">
         <v>981</v>
       </c>
       <c r="D74" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G74" t="s">
         <v>10</v>
@@ -2506,16 +2509,16 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C75">
         <v>848</v>
       </c>
       <c r="D75" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
@@ -2535,16 +2538,16 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C76">
         <v>854</v>
       </c>
       <c r="D76" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G76" t="s">
         <v>13</v>
@@ -2564,16 +2567,16 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C77">
         <v>850</v>
       </c>
       <c r="D77" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G77" t="s">
         <v>10</v>
@@ -2593,16 +2596,16 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C78">
         <v>853</v>
       </c>
       <c r="D78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
@@ -2622,13 +2625,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C79">
         <v>849</v>
       </c>
       <c r="D79" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F79" t="s">
         <v>17</v>
@@ -2651,13 +2654,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C80">
         <v>855</v>
       </c>
       <c r="D80" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
@@ -2680,13 +2683,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C81">
         <v>852</v>
       </c>
       <c r="D81" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
@@ -2709,13 +2712,13 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C82">
         <v>980</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F82" t="s">
         <v>17</v>
@@ -2738,13 +2741,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C83">
         <v>851</v>
       </c>
       <c r="D83" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
@@ -2767,13 +2770,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C84">
         <v>981</v>
       </c>
       <c r="D84" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
@@ -2796,13 +2799,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C85">
         <v>848</v>
       </c>
       <c r="D85" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F85" t="s">
         <v>17</v>
@@ -2825,13 +2828,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C86">
         <v>854</v>
       </c>
       <c r="D86" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -2854,13 +2857,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C87">
         <v>850</v>
       </c>
       <c r="D87" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F87" t="s">
         <v>17</v>
@@ -2891,13 +2894,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C89">
         <v>853</v>
       </c>
       <c r="D89" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F89" t="s">
         <v>17</v>
@@ -2920,13 +2923,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C90">
         <v>849</v>
       </c>
       <c r="D90" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2949,13 +2952,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C91">
         <v>855</v>
       </c>
       <c r="D91" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -2978,13 +2981,13 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C92">
         <v>852</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -3007,13 +3010,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C93">
         <v>980</v>
       </c>
       <c r="D93" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -3036,13 +3039,13 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C94">
         <v>851</v>
       </c>
       <c r="D94" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -3073,13 +3076,13 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C96">
         <v>981</v>
       </c>
       <c r="D96" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -3102,13 +3105,13 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C97">
         <v>848</v>
       </c>
       <c r="D97" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -3131,13 +3134,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C98">
         <v>854</v>
       </c>
       <c r="D98" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -3160,13 +3163,13 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C99">
         <v>850</v>
       </c>
       <c r="D99" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -3189,13 +3192,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C100">
         <v>853</v>
       </c>
       <c r="D100" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -3218,13 +3221,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C101">
         <v>849</v>
       </c>
       <c r="D101" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
@@ -3247,13 +3250,13 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C102">
         <v>855</v>
       </c>
       <c r="D102" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F102" t="s">
         <v>20</v>
@@ -3276,13 +3279,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C103">
         <v>852</v>
       </c>
       <c r="D103" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F103" t="s">
         <v>20</v>
@@ -3305,13 +3308,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C104">
         <v>980</v>
       </c>
       <c r="D104" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -3334,13 +3337,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C105">
         <v>851</v>
       </c>
       <c r="D105" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -3363,13 +3366,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C106">
         <v>981</v>
       </c>
       <c r="D106" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
@@ -3392,13 +3395,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C107">
         <v>848</v>
       </c>
       <c r="D107" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F107" t="s">
         <v>20</v>
@@ -3421,13 +3424,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C108">
         <v>854</v>
       </c>
       <c r="D108" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -3450,13 +3453,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C109">
         <v>850</v>
       </c>
       <c r="D109" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F109" t="s">
         <v>20</v>
@@ -3479,13 +3482,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C110">
         <v>853</v>
       </c>
       <c r="D110" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F110" t="s">
         <v>20</v>
@@ -3508,13 +3511,13 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C111">
         <v>849</v>
       </c>
       <c r="D111" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
@@ -3537,13 +3540,13 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C112">
         <v>855</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -3566,13 +3569,13 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C113">
         <v>852</v>
       </c>
       <c r="D113" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F113" t="s">
         <v>21</v>
@@ -3595,13 +3598,13 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C114">
         <v>980</v>
       </c>
       <c r="D114" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F114" t="s">
         <v>21</v>
@@ -3624,13 +3627,13 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C115">
         <v>851</v>
       </c>
       <c r="D115" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F115" t="s">
         <v>21</v>
@@ -3653,13 +3656,13 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C116">
         <v>981</v>
       </c>
       <c r="D116" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -3682,13 +3685,13 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C117">
         <v>848</v>
       </c>
       <c r="D117" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
@@ -3711,13 +3714,13 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C118">
         <v>854</v>
       </c>
       <c r="D118" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F118" t="s">
         <v>21</v>
@@ -3740,13 +3743,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C119">
         <v>850</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F119" t="s">
         <v>21</v>
@@ -3769,13 +3772,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C120">
         <v>853</v>
       </c>
       <c r="D120" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F120" t="s">
         <v>21</v>
@@ -3798,13 +3801,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C121">
         <v>849</v>
       </c>
       <c r="D121" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
         <v>22</v>
@@ -3827,13 +3830,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C122">
         <v>855</v>
       </c>
       <c r="D122" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F122" t="s">
         <v>22</v>
@@ -3856,13 +3859,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C123">
         <v>852</v>
       </c>
       <c r="D123" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
@@ -3885,13 +3888,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C124">
         <v>980</v>
       </c>
       <c r="D124" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F124" t="s">
         <v>22</v>
@@ -3914,13 +3917,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C125">
         <v>851</v>
       </c>
       <c r="D125" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F125" t="s">
         <v>22</v>
@@ -3943,13 +3946,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C126">
         <v>981</v>
       </c>
       <c r="D126" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
@@ -3972,13 +3975,13 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C127">
         <v>848</v>
       </c>
       <c r="D127" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F127" t="s">
         <v>22</v>
@@ -4001,13 +4004,13 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C128">
         <v>854</v>
       </c>
       <c r="D128" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F128" t="s">
         <v>22</v>
@@ -4030,13 +4033,13 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C129">
         <v>850</v>
       </c>
       <c r="D129" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F129" t="s">
         <v>22</v>
@@ -4059,13 +4062,13 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C130">
         <v>853</v>
       </c>
       <c r="D130" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F130" t="s">
         <v>22</v>
@@ -4088,16 +4091,16 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C131">
         <v>849</v>
       </c>
       <c r="D131" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F131" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G131" t="s">
         <v>13</v>
@@ -4117,16 +4120,16 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C132">
         <v>855</v>
       </c>
       <c r="D132" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F132" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4146,16 +4149,16 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C133">
         <v>852</v>
       </c>
       <c r="D133" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F133" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G133" t="s">
         <v>13</v>
@@ -4175,16 +4178,16 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C134">
         <v>980</v>
       </c>
       <c r="D134" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F134" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4204,16 +4207,16 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C135">
         <v>851</v>
       </c>
       <c r="D135" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F135" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4233,16 +4236,16 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C136">
         <v>981</v>
       </c>
       <c r="D136" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F136" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4262,16 +4265,16 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C137">
         <v>848</v>
       </c>
       <c r="D137" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F137" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G137" t="s">
         <v>13</v>
@@ -4291,16 +4294,16 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C138">
         <v>854</v>
       </c>
       <c r="D138" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F138" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G138" t="s">
         <v>13</v>
@@ -4320,16 +4323,16 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C139">
         <v>850</v>
       </c>
       <c r="D139" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F139" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G139" t="s">
         <v>13</v>
@@ -4349,16 +4352,16 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C140">
         <v>853</v>
       </c>
       <c r="D140" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F140" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G140" t="s">
         <v>13</v>
@@ -4378,13 +4381,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C141">
         <v>849</v>
       </c>
       <c r="D141" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F141" t="s">
         <v>26</v>
@@ -4407,13 +4410,13 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C142">
         <v>855</v>
       </c>
       <c r="D142" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F142" t="s">
         <v>26</v>
@@ -4436,13 +4439,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C143">
         <v>852</v>
       </c>
       <c r="D143" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F143" t="s">
         <v>26</v>
@@ -4465,13 +4468,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C144">
         <v>980</v>
       </c>
       <c r="D144" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F144" t="s">
         <v>26</v>
@@ -4494,13 +4497,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C145">
         <v>851</v>
       </c>
       <c r="D145" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F145" t="s">
         <v>26</v>
@@ -4523,13 +4526,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C146">
         <v>981</v>
       </c>
       <c r="D146" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F146" t="s">
         <v>26</v>
@@ -4552,13 +4555,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C147">
         <v>848</v>
       </c>
       <c r="D147" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F147" t="s">
         <v>26</v>
@@ -4581,13 +4584,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C148">
         <v>854</v>
       </c>
       <c r="D148" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F148" t="s">
         <v>26</v>
@@ -4610,13 +4613,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C149">
         <v>850</v>
       </c>
       <c r="D149" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F149" t="s">
         <v>26</v>
@@ -4639,13 +4642,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C150">
         <v>853</v>
       </c>
       <c r="D150" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F150" t="s">
         <v>26</v>
@@ -4668,13 +4671,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C151">
         <v>849</v>
       </c>
       <c r="D151" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F151" t="s">
         <v>24</v>
@@ -4697,13 +4700,13 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C152">
         <v>855</v>
       </c>
       <c r="D152" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F152" t="s">
         <v>24</v>
@@ -4726,13 +4729,13 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C153">
         <v>852</v>
       </c>
       <c r="D153" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F153" t="s">
         <v>24</v>
@@ -4755,13 +4758,13 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C154">
         <v>980</v>
       </c>
       <c r="D154" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F154" t="s">
         <v>24</v>
@@ -4784,13 +4787,13 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C155">
         <v>851</v>
       </c>
       <c r="D155" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F155" t="s">
         <v>24</v>
@@ -4813,13 +4816,13 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C156">
         <v>981</v>
       </c>
       <c r="D156" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -4842,13 +4845,13 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C157">
         <v>848</v>
       </c>
       <c r="D157" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -4871,13 +4874,13 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C158">
         <v>854</v>
       </c>
       <c r="D158" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F158" t="s">
         <v>24</v>
@@ -4900,13 +4903,13 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C159">
         <v>850</v>
       </c>
       <c r="D159" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F159" t="s">
         <v>24</v>
@@ -4929,13 +4932,13 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C160">
         <v>853</v>
       </c>
       <c r="D160" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F160" t="s">
         <v>24</v>
@@ -4958,13 +4961,13 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C161">
         <v>849</v>
       </c>
       <c r="D161" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F161" t="s">
         <v>23</v>
@@ -4987,13 +4990,13 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C162">
         <v>855</v>
       </c>
       <c r="D162" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F162" t="s">
         <v>23</v>
@@ -5016,13 +5019,13 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C163">
         <v>852</v>
       </c>
       <c r="D163" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F163" t="s">
         <v>23</v>
@@ -5045,13 +5048,13 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C164">
         <v>980</v>
       </c>
       <c r="D164" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F164" t="s">
         <v>23</v>
@@ -5074,13 +5077,13 @@
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C165">
         <v>851</v>
       </c>
       <c r="D165" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F165" t="s">
         <v>23</v>
@@ -5103,13 +5106,13 @@
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C166">
         <v>981</v>
       </c>
       <c r="D166" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F166" t="s">
         <v>23</v>
@@ -5132,13 +5135,13 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C167">
         <v>848</v>
       </c>
       <c r="D167" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F167" t="s">
         <v>23</v>
@@ -5161,13 +5164,13 @@
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C168">
         <v>854</v>
       </c>
       <c r="D168" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F168" t="s">
         <v>23</v>
@@ -5190,13 +5193,13 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C169">
         <v>850</v>
       </c>
       <c r="D169" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F169" t="s">
         <v>23</v>
@@ -5227,13 +5230,13 @@
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C171">
         <v>853</v>
       </c>
       <c r="D171" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F171" t="s">
         <v>23</v>
@@ -5256,13 +5259,13 @@
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C172">
         <v>849</v>
       </c>
       <c r="D172" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F172" t="s">
         <v>17</v>
@@ -5285,13 +5288,13 @@
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C173">
         <v>855</v>
       </c>
       <c r="D173" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F173" t="s">
         <v>17</v>
@@ -5314,13 +5317,13 @@
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C174">
         <v>852</v>
       </c>
       <c r="D174" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F174" t="s">
         <v>17</v>
@@ -5343,13 +5346,13 @@
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C175">
         <v>980</v>
       </c>
       <c r="D175" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F175" t="s">
         <v>17</v>
@@ -5372,13 +5375,13 @@
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C176">
         <v>851</v>
       </c>
       <c r="D176" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F176" t="s">
         <v>17</v>
@@ -5401,13 +5404,13 @@
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C177">
         <v>981</v>
       </c>
       <c r="D177" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F177" t="s">
         <v>17</v>
@@ -5430,13 +5433,13 @@
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C178">
         <v>848</v>
       </c>
       <c r="D178" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F178" t="s">
         <v>17</v>
@@ -5459,13 +5462,13 @@
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C179">
         <v>854</v>
       </c>
       <c r="D179" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F179" t="s">
         <v>17</v>
@@ -5488,13 +5491,13 @@
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C180">
         <v>850</v>
       </c>
       <c r="D180" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F180" t="s">
         <v>17</v>
@@ -5517,13 +5520,13 @@
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C181">
         <v>853</v>
       </c>
       <c r="D181" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F181" t="s">
         <v>17</v>
@@ -5546,13 +5549,13 @@
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C182">
         <v>849</v>
       </c>
       <c r="D182" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
@@ -5575,13 +5578,13 @@
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C183">
         <v>855</v>
       </c>
       <c r="D183" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F183" t="s">
         <v>18</v>
@@ -5604,13 +5607,13 @@
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C184">
         <v>852</v>
       </c>
       <c r="D184" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F184" t="s">
         <v>18</v>
@@ -5633,13 +5636,13 @@
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C185">
         <v>980</v>
       </c>
       <c r="D185" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F185" t="s">
         <v>18</v>
@@ -5662,13 +5665,13 @@
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C186">
         <v>851</v>
       </c>
       <c r="D186" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F186" t="s">
         <v>18</v>
@@ -5691,13 +5694,13 @@
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C187">
         <v>981</v>
       </c>
       <c r="D187" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F187" t="s">
         <v>18</v>
@@ -5720,13 +5723,13 @@
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C188">
         <v>848</v>
       </c>
       <c r="D188" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F188" t="s">
         <v>18</v>
@@ -5749,13 +5752,13 @@
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C189">
         <v>854</v>
       </c>
       <c r="D189" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F189" t="s">
         <v>18</v>
@@ -5778,13 +5781,13 @@
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C190">
         <v>850</v>
       </c>
       <c r="D190" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F190" t="s">
         <v>18</v>
@@ -5807,13 +5810,13 @@
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C191">
         <v>853</v>
       </c>
       <c r="D191" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F191" t="s">
         <v>18</v>
@@ -5836,16 +5839,16 @@
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C192">
         <v>849</v>
       </c>
       <c r="D192" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F192" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G192" t="s">
         <v>13</v>
@@ -5865,16 +5868,16 @@
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C193">
         <v>855</v>
       </c>
       <c r="D193" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F193" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G193" t="s">
         <v>13</v>
@@ -5894,16 +5897,16 @@
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C194">
         <v>852</v>
       </c>
       <c r="D194" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F194" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G194" t="s">
         <v>13</v>
@@ -5923,16 +5926,16 @@
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C195">
         <v>980</v>
       </c>
       <c r="D195" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F195" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G195" t="s">
         <v>13</v>
@@ -5952,16 +5955,16 @@
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C196">
         <v>851</v>
       </c>
       <c r="D196" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F196" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G196" t="s">
         <v>13</v>
@@ -5981,16 +5984,16 @@
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C197">
         <v>981</v>
       </c>
       <c r="D197" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F197" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G197" t="s">
         <v>13</v>
@@ -6010,16 +6013,16 @@
     </row>
     <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C198">
         <v>848</v>
       </c>
       <c r="D198" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F198" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G198" t="s">
         <v>13</v>
@@ -6039,16 +6042,16 @@
     </row>
     <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C199">
         <v>854</v>
       </c>
       <c r="D199" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F199" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G199" t="s">
         <v>13</v>
@@ -6068,16 +6071,16 @@
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C200">
         <v>850</v>
       </c>
       <c r="D200" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F200" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G200" t="s">
         <v>13</v>
@@ -6097,16 +6100,16 @@
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C201">
         <v>853</v>
       </c>
       <c r="D201" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F201" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G201" t="s">
         <v>13</v>
@@ -6126,16 +6129,16 @@
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C202">
         <v>849</v>
       </c>
       <c r="D202" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F202" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G202" t="s">
         <v>13</v>
@@ -6155,16 +6158,16 @@
     </row>
     <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C203">
         <v>855</v>
       </c>
       <c r="D203" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F203" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G203" t="s">
         <v>13</v>
@@ -6184,16 +6187,16 @@
     </row>
     <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C204">
         <v>852</v>
       </c>
       <c r="D204" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F204" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G204" t="s">
         <v>13</v>
@@ -6213,16 +6216,16 @@
     </row>
     <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C205">
         <v>980</v>
       </c>
       <c r="D205" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F205" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G205" t="s">
         <v>13</v>
@@ -6242,16 +6245,16 @@
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C206">
         <v>851</v>
       </c>
       <c r="D206" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F206" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G206" t="s">
         <v>13</v>
@@ -6271,16 +6274,16 @@
     </row>
     <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C207">
         <v>981</v>
       </c>
       <c r="D207" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F207" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G207" t="s">
         <v>13</v>
@@ -6300,16 +6303,16 @@
     </row>
     <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C208">
         <v>848</v>
       </c>
       <c r="D208" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F208" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G208" t="s">
         <v>13</v>
@@ -6329,16 +6332,16 @@
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C209">
         <v>854</v>
       </c>
       <c r="D209" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F209" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G209" t="s">
         <v>13</v>
@@ -6358,16 +6361,16 @@
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C210">
         <v>850</v>
       </c>
       <c r="D210" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F210" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G210" t="s">
         <v>13</v>
@@ -6387,16 +6390,16 @@
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C211">
         <v>853</v>
       </c>
       <c r="D211" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F211" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G211" t="s">
         <v>13</v>
@@ -6416,13 +6419,13 @@
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C212">
         <v>849</v>
       </c>
       <c r="D212" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F212" t="s">
         <v>25</v>
@@ -6445,13 +6448,13 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C213">
         <v>855</v>
       </c>
       <c r="D213" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F213" t="s">
         <v>25</v>
@@ -6474,13 +6477,13 @@
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C214">
         <v>852</v>
       </c>
       <c r="D214" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F214" t="s">
         <v>25</v>
@@ -6503,13 +6506,13 @@
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C215">
         <v>980</v>
       </c>
       <c r="D215" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F215" t="s">
         <v>25</v>
@@ -6532,13 +6535,13 @@
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C216">
         <v>851</v>
       </c>
       <c r="D216" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F216" t="s">
         <v>25</v>
@@ -6561,13 +6564,13 @@
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C217">
         <v>848</v>
       </c>
       <c r="D217" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F217" t="s">
         <v>25</v>
@@ -6590,13 +6593,13 @@
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C218">
         <v>854</v>
       </c>
       <c r="D218" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F218" t="s">
         <v>25</v>
@@ -6619,13 +6622,13 @@
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C219">
         <v>850</v>
       </c>
       <c r="D219" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F219" t="s">
         <v>25</v>
@@ -6648,13 +6651,13 @@
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C220">
         <v>853</v>
       </c>
       <c r="D220" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -6677,16 +6680,16 @@
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C221">
         <v>849</v>
       </c>
       <c r="D221" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F221" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6706,16 +6709,16 @@
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C222">
         <v>855</v>
       </c>
       <c r="D222" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F222" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G222" t="s">
         <v>13</v>
@@ -6735,16 +6738,16 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C223">
         <v>852</v>
       </c>
       <c r="D223" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F223" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G223" t="s">
         <v>13</v>
@@ -6764,16 +6767,16 @@
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C224">
         <v>980</v>
       </c>
       <c r="D224" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F224" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G224" t="s">
         <v>10</v>
@@ -6793,16 +6796,16 @@
     </row>
     <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C225">
         <v>851</v>
       </c>
       <c r="D225" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F225" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G225" t="s">
         <v>13</v>
@@ -6822,16 +6825,16 @@
     </row>
     <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C226">
         <v>848</v>
       </c>
       <c r="D226" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F226" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G226" t="s">
         <v>13</v>
@@ -6851,16 +6854,16 @@
     </row>
     <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C227">
         <v>854</v>
       </c>
       <c r="D227" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F227" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G227" t="s">
         <v>13</v>
@@ -6880,16 +6883,16 @@
     </row>
     <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C228">
         <v>850</v>
       </c>
       <c r="D228" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F228" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G228" t="s">
         <v>13</v>
@@ -6909,16 +6912,16 @@
     </row>
     <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C229">
         <v>853</v>
       </c>
       <c r="D229" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F229" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G229" t="s">
         <v>13</v>
@@ -6938,13 +6941,13 @@
     </row>
     <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C230">
         <v>849</v>
       </c>
       <c r="D230" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F230" t="s">
         <v>19</v>
@@ -6967,13 +6970,13 @@
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C231">
         <v>855</v>
       </c>
       <c r="D231" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -6996,13 +6999,13 @@
     </row>
     <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C232">
         <v>852</v>
       </c>
       <c r="D232" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -7025,13 +7028,13 @@
     </row>
     <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C233">
         <v>980</v>
       </c>
       <c r="D233" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F233" t="s">
         <v>19</v>
@@ -7054,13 +7057,13 @@
     </row>
     <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C234">
         <v>851</v>
       </c>
       <c r="D234" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F234" t="s">
         <v>19</v>
@@ -7083,13 +7086,13 @@
     </row>
     <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C235">
         <v>848</v>
       </c>
       <c r="D235" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -7112,13 +7115,13 @@
     </row>
     <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C236">
         <v>854</v>
       </c>
       <c r="D236" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -7141,13 +7144,13 @@
     </row>
     <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C237">
         <v>850</v>
       </c>
       <c r="D237" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F237" t="s">
         <v>19</v>
@@ -7170,13 +7173,13 @@
     </row>
     <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C238">
         <v>853</v>
       </c>
       <c r="D238" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -7199,13 +7202,13 @@
     </row>
     <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C239">
         <v>849</v>
       </c>
       <c r="D239" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F239" t="s">
         <v>20</v>
@@ -7228,13 +7231,13 @@
     </row>
     <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C240">
         <v>855</v>
       </c>
       <c r="D240" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F240" t="s">
         <v>20</v>
@@ -7257,13 +7260,13 @@
     </row>
     <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C241">
         <v>852</v>
       </c>
       <c r="D241" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F241" t="s">
         <v>20</v>
@@ -7286,13 +7289,13 @@
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C242">
         <v>980</v>
       </c>
       <c r="D242" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F242" t="s">
         <v>20</v>
@@ -7315,13 +7318,13 @@
     </row>
     <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C243">
         <v>851</v>
       </c>
       <c r="D243" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F243" t="s">
         <v>20</v>
@@ -7344,13 +7347,13 @@
     </row>
     <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C244">
         <v>848</v>
       </c>
       <c r="D244" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F244" t="s">
         <v>20</v>
@@ -7373,13 +7376,13 @@
     </row>
     <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C245">
         <v>854</v>
       </c>
       <c r="D245" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F245" t="s">
         <v>20</v>
@@ -7402,13 +7405,13 @@
     </row>
     <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C246">
         <v>850</v>
       </c>
       <c r="D246" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F246" t="s">
         <v>20</v>
@@ -7431,13 +7434,13 @@
     </row>
     <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C247">
         <v>853</v>
       </c>
       <c r="D247" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F247" t="s">
         <v>20</v>
@@ -7460,13 +7463,13 @@
     </row>
     <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C248">
         <v>849</v>
       </c>
       <c r="D248" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F248" t="s">
         <v>27</v>
@@ -7489,13 +7492,13 @@
     </row>
     <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C249">
         <v>855</v>
       </c>
       <c r="D249" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F249" t="s">
         <v>27</v>
@@ -7518,13 +7521,13 @@
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C250">
         <v>852</v>
       </c>
       <c r="D250" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F250" t="s">
         <v>27</v>
@@ -7547,13 +7550,13 @@
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C251">
         <v>980</v>
       </c>
       <c r="D251" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F251" t="s">
         <v>27</v>
@@ -7576,13 +7579,13 @@
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C252">
         <v>851</v>
       </c>
       <c r="D252" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F252" t="s">
         <v>27</v>
@@ -7605,13 +7608,13 @@
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C253">
         <v>848</v>
       </c>
       <c r="D253" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F253" t="s">
         <v>27</v>
@@ -7634,13 +7637,13 @@
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C254">
         <v>854</v>
       </c>
       <c r="D254" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F254" t="s">
         <v>27</v>
@@ -7663,13 +7666,13 @@
     </row>
     <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C255">
         <v>850</v>
       </c>
       <c r="D255" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F255" t="s">
         <v>27</v>
@@ -7700,13 +7703,13 @@
     </row>
     <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C257">
         <v>853</v>
       </c>
       <c r="D257" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F257" t="s">
         <v>27</v>
@@ -7729,13 +7732,13 @@
     </row>
     <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C258">
         <v>849</v>
       </c>
       <c r="D258" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -7758,13 +7761,13 @@
     </row>
     <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C259">
         <v>855</v>
       </c>
       <c r="D259" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -7787,13 +7790,13 @@
     </row>
     <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C260">
         <v>852</v>
       </c>
       <c r="D260" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -7816,13 +7819,13 @@
     </row>
     <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C261">
         <v>980</v>
       </c>
       <c r="D261" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -7845,13 +7848,13 @@
     </row>
     <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C262">
         <v>851</v>
       </c>
       <c r="D262" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -7874,13 +7877,13 @@
     </row>
     <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C263">
         <v>848</v>
       </c>
       <c r="D263" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -7903,13 +7906,13 @@
     </row>
     <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C264">
         <v>854</v>
       </c>
       <c r="D264" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -7932,13 +7935,13 @@
     </row>
     <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C265">
         <v>850</v>
       </c>
       <c r="D265" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -7961,13 +7964,13 @@
     </row>
     <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C266">
         <v>853</v>
       </c>
       <c r="D266" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -7990,13 +7993,13 @@
     </row>
     <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C267">
         <v>849</v>
       </c>
       <c r="D267" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F267" t="s">
         <v>29</v>
@@ -8019,13 +8022,13 @@
     </row>
     <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C268">
         <v>855</v>
       </c>
       <c r="D268" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F268" t="s">
         <v>29</v>
@@ -8048,13 +8051,13 @@
     </row>
     <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C269">
         <v>852</v>
       </c>
       <c r="D269" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F269" t="s">
         <v>29</v>
@@ -8077,13 +8080,13 @@
     </row>
     <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C270">
         <v>980</v>
       </c>
       <c r="D270" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F270" t="s">
         <v>29</v>
@@ -8106,13 +8109,13 @@
     </row>
     <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C271">
         <v>851</v>
       </c>
       <c r="D271" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F271" t="s">
         <v>29</v>
@@ -8135,13 +8138,13 @@
     </row>
     <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C272">
         <v>848</v>
       </c>
       <c r="D272" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F272" t="s">
         <v>29</v>
@@ -8164,13 +8167,13 @@
     </row>
     <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C273">
         <v>854</v>
       </c>
       <c r="D273" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F273" t="s">
         <v>29</v>
@@ -8193,13 +8196,13 @@
     </row>
     <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C274">
         <v>850</v>
       </c>
       <c r="D274" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F274" t="s">
         <v>29</v>
@@ -8222,13 +8225,13 @@
     </row>
     <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C275">
         <v>853</v>
       </c>
       <c r="D275" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F275" t="s">
         <v>29</v>
@@ -8251,13 +8254,13 @@
     </row>
     <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C276">
         <v>849</v>
       </c>
       <c r="D276" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F276" t="s">
         <v>30</v>
@@ -8280,13 +8283,13 @@
     </row>
     <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C277">
         <v>852</v>
       </c>
       <c r="D277" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F277" t="s">
         <v>30</v>
@@ -8309,13 +8312,13 @@
     </row>
     <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C278">
         <v>980</v>
       </c>
       <c r="D278" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F278" t="s">
         <v>30</v>
@@ -8338,13 +8341,13 @@
     </row>
     <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C279">
         <v>851</v>
       </c>
       <c r="D279" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F279" t="s">
         <v>30</v>
@@ -8367,13 +8370,13 @@
     </row>
     <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C280">
         <v>848</v>
       </c>
       <c r="D280" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F280" t="s">
         <v>30</v>
@@ -8396,13 +8399,13 @@
     </row>
     <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C281">
         <v>854</v>
       </c>
       <c r="D281" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F281" t="s">
         <v>30</v>
@@ -8425,13 +8428,13 @@
     </row>
     <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C282">
         <v>850</v>
       </c>
       <c r="D282" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F282" t="s">
         <v>30</v>
@@ -8454,13 +8457,13 @@
     </row>
     <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C283">
         <v>849</v>
       </c>
       <c r="D283" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F283" t="s">
         <v>21</v>
@@ -8483,13 +8486,13 @@
     </row>
     <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C284">
         <v>852</v>
       </c>
       <c r="D284" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F284" t="s">
         <v>21</v>
@@ -8512,13 +8515,13 @@
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C285">
         <v>980</v>
       </c>
       <c r="D285" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F285" t="s">
         <v>21</v>
@@ -8541,13 +8544,13 @@
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C286">
         <v>848</v>
       </c>
       <c r="D286" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F286" t="s">
         <v>21</v>
@@ -8570,13 +8573,13 @@
     </row>
     <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C287">
         <v>854</v>
       </c>
       <c r="D287" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F287" t="s">
         <v>21</v>
@@ -8599,13 +8602,13 @@
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C288">
         <v>850</v>
       </c>
       <c r="D288" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F288" t="s">
         <v>21</v>
@@ -8628,13 +8631,13 @@
     </row>
     <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C289">
         <v>849</v>
       </c>
       <c r="D289" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F289" t="s">
         <v>31</v>
@@ -8657,13 +8660,13 @@
     </row>
     <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C290">
         <v>852</v>
       </c>
       <c r="D290" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -8686,13 +8689,13 @@
     </row>
     <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C291">
         <v>980</v>
       </c>
       <c r="D291" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F291" t="s">
         <v>31</v>
@@ -8715,13 +8718,13 @@
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C292">
         <v>848</v>
       </c>
       <c r="D292" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F292" t="s">
         <v>31</v>
@@ -8744,13 +8747,13 @@
     </row>
     <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C293">
         <v>854</v>
       </c>
       <c r="D293" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F293" t="s">
         <v>31</v>
@@ -8773,13 +8776,13 @@
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C294">
         <v>850</v>
       </c>
       <c r="D294" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -8802,13 +8805,13 @@
     </row>
     <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C295">
         <v>849</v>
       </c>
       <c r="D295" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F295" t="s">
         <v>23</v>
@@ -8831,13 +8834,13 @@
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C296">
         <v>852</v>
       </c>
       <c r="D296" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F296" t="s">
         <v>23</v>
@@ -8860,13 +8863,13 @@
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C297">
         <v>980</v>
       </c>
       <c r="D297" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F297" t="s">
         <v>23</v>
@@ -8889,13 +8892,13 @@
     </row>
     <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C298">
         <v>848</v>
       </c>
       <c r="D298" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F298" t="s">
         <v>23</v>
@@ -8918,13 +8921,13 @@
     </row>
     <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C299">
         <v>854</v>
       </c>
       <c r="D299" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F299" t="s">
         <v>23</v>
@@ -8947,13 +8950,13 @@
     </row>
     <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C300">
         <v>850</v>
       </c>
       <c r="D300" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F300" t="s">
         <v>23</v>
@@ -8975,120 +8978,396 @@
       </c>
     </row>
     <row r="301" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H301" s="2"/>
-      <c r="I301" s="1"/>
-      <c r="J301" s="2"/>
-      <c r="K301" s="1"/>
+      <c r="B301" t="s">
+        <v>39</v>
+      </c>
+      <c r="C301">
+        <v>849</v>
+      </c>
+      <c r="D301" t="s">
+        <v>40</v>
+      </c>
+      <c r="F301" t="s">
+        <v>32</v>
+      </c>
+      <c r="G301" t="s">
+        <v>13</v>
+      </c>
+      <c r="H301" s="2">
+        <v>0</v>
+      </c>
+      <c r="I301" s="1">
+        <v>46237.711111111108</v>
+      </c>
+      <c r="J301" s="2">
+        <v>0</v>
+      </c>
+      <c r="K301" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="302" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H302" s="2"/>
-      <c r="I302" s="1"/>
-      <c r="J302" s="2"/>
-      <c r="K302" s="1"/>
+      <c r="B302" t="s">
+        <v>39</v>
+      </c>
+      <c r="C302">
+        <v>852</v>
+      </c>
+      <c r="D302" t="s">
+        <v>43</v>
+      </c>
+      <c r="F302" t="s">
+        <v>32</v>
+      </c>
+      <c r="G302" t="s">
+        <v>13</v>
+      </c>
+      <c r="H302" s="2">
+        <v>0</v>
+      </c>
+      <c r="I302" s="1">
+        <v>46237.711111111108</v>
+      </c>
+      <c r="J302" s="2">
+        <v>0</v>
+      </c>
+      <c r="K302" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="303" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H303" s="2"/>
-      <c r="I303" s="1"/>
-      <c r="J303" s="2"/>
-      <c r="K303" s="1"/>
+      <c r="B303" t="s">
+        <v>39</v>
+      </c>
+      <c r="C303">
+        <v>980</v>
+      </c>
+      <c r="D303" t="s">
+        <v>45</v>
+      </c>
+      <c r="F303" t="s">
+        <v>32</v>
+      </c>
+      <c r="G303" t="s">
+        <v>13</v>
+      </c>
+      <c r="H303" s="2">
+        <v>0</v>
+      </c>
+      <c r="I303" s="1">
+        <v>46237.711805555555</v>
+      </c>
+      <c r="J303" s="2">
+        <v>0</v>
+      </c>
+      <c r="K303" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H304" s="2"/>
-      <c r="I304" s="1"/>
-      <c r="J304" s="2"/>
-      <c r="K304" s="1"/>
-    </row>
-    <row r="305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H305" s="2"/>
-      <c r="I305" s="1"/>
-      <c r="J305" s="2"/>
-      <c r="K305" s="1"/>
-    </row>
-    <row r="306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H306" s="2"/>
-      <c r="I306" s="1"/>
-      <c r="J306" s="2"/>
-      <c r="K306" s="1"/>
-    </row>
-    <row r="307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H307" s="2"/>
-      <c r="I307" s="1"/>
-      <c r="J307" s="2"/>
-      <c r="K307" s="1"/>
-    </row>
-    <row r="308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H308" s="2"/>
-      <c r="I308" s="1"/>
-      <c r="J308" s="2"/>
-      <c r="K308" s="1"/>
-    </row>
-    <row r="309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H309" s="2"/>
-      <c r="I309" s="1"/>
-      <c r="J309" s="2"/>
-      <c r="K309" s="1"/>
-    </row>
-    <row r="310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H310" s="2"/>
-      <c r="I310" s="1"/>
-      <c r="J310" s="2"/>
-      <c r="K310" s="1"/>
-    </row>
-    <row r="311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H311" s="2"/>
-      <c r="I311" s="1"/>
-      <c r="J311" s="2"/>
-      <c r="K311" s="1"/>
-    </row>
-    <row r="312" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H312" s="2"/>
-      <c r="I312" s="1"/>
-      <c r="J312" s="2"/>
-      <c r="K312" s="1"/>
-    </row>
-    <row r="313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="B304" t="s">
+        <v>39</v>
+      </c>
+      <c r="C304">
+        <v>848</v>
+      </c>
+      <c r="D304" t="s">
+        <v>49</v>
+      </c>
+      <c r="F304" t="s">
+        <v>32</v>
+      </c>
+      <c r="G304" t="s">
+        <v>13</v>
+      </c>
+      <c r="H304" s="2">
+        <v>0</v>
+      </c>
+      <c r="I304" s="1">
+        <v>46237.712500000001</v>
+      </c>
+      <c r="J304" s="2">
+        <v>0</v>
+      </c>
+      <c r="K304" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="305" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B305" t="s">
+        <v>39</v>
+      </c>
+      <c r="C305">
+        <v>854</v>
+      </c>
+      <c r="D305" t="s">
+        <v>50</v>
+      </c>
+      <c r="F305" t="s">
+        <v>32</v>
+      </c>
+      <c r="G305" t="s">
+        <v>13</v>
+      </c>
+      <c r="H305" s="2">
+        <v>0</v>
+      </c>
+      <c r="I305" s="1">
+        <v>46237.713194444441</v>
+      </c>
+      <c r="J305" s="2">
+        <v>0</v>
+      </c>
+      <c r="K305" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="306" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B306" t="s">
+        <v>39</v>
+      </c>
+      <c r="C306">
+        <v>850</v>
+      </c>
+      <c r="D306" t="s">
+        <v>51</v>
+      </c>
+      <c r="F306" t="s">
+        <v>32</v>
+      </c>
+      <c r="G306" t="s">
+        <v>13</v>
+      </c>
+      <c r="H306" s="2">
+        <v>0</v>
+      </c>
+      <c r="I306" s="1">
+        <v>46237.713194444441</v>
+      </c>
+      <c r="J306" s="2">
+        <v>0</v>
+      </c>
+      <c r="K306" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="307" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B307" t="s">
+        <v>39</v>
+      </c>
+      <c r="C307">
+        <v>849</v>
+      </c>
+      <c r="D307" t="s">
+        <v>40</v>
+      </c>
+      <c r="F307" t="s">
+        <v>32</v>
+      </c>
+      <c r="G307" t="s">
+        <v>13</v>
+      </c>
+      <c r="H307" s="2">
+        <v>0</v>
+      </c>
+      <c r="I307" s="1">
+        <v>46237.751851851855</v>
+      </c>
+      <c r="J307" s="2">
+        <v>0</v>
+      </c>
+      <c r="K307" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="308" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B308" t="s">
+        <v>39</v>
+      </c>
+      <c r="C308">
+        <v>852</v>
+      </c>
+      <c r="D308" t="s">
+        <v>43</v>
+      </c>
+      <c r="F308" t="s">
+        <v>32</v>
+      </c>
+      <c r="G308" t="s">
+        <v>13</v>
+      </c>
+      <c r="H308" s="2">
+        <v>0</v>
+      </c>
+      <c r="I308" s="1">
+        <v>46237.752546296295</v>
+      </c>
+      <c r="J308" s="2">
+        <v>0</v>
+      </c>
+      <c r="K308" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="309" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B309" t="s">
+        <v>39</v>
+      </c>
+      <c r="C309">
+        <v>980</v>
+      </c>
+      <c r="D309" t="s">
+        <v>45</v>
+      </c>
+      <c r="F309" t="s">
+        <v>32</v>
+      </c>
+      <c r="G309" t="s">
+        <v>13</v>
+      </c>
+      <c r="H309" s="2">
+        <v>0</v>
+      </c>
+      <c r="I309" s="1">
+        <v>46237.752546296295</v>
+      </c>
+      <c r="J309" s="2">
+        <v>0</v>
+      </c>
+      <c r="K309" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="310" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B310" t="s">
+        <v>39</v>
+      </c>
+      <c r="C310">
+        <v>848</v>
+      </c>
+      <c r="D310" t="s">
+        <v>49</v>
+      </c>
+      <c r="F310" t="s">
+        <v>32</v>
+      </c>
+      <c r="G310" t="s">
+        <v>13</v>
+      </c>
+      <c r="H310" s="2">
+        <v>0</v>
+      </c>
+      <c r="I310" s="1">
+        <v>46237.753240740742</v>
+      </c>
+      <c r="J310" s="2">
+        <v>0</v>
+      </c>
+      <c r="K310" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="311" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B311" t="s">
+        <v>39</v>
+      </c>
+      <c r="C311">
+        <v>854</v>
+      </c>
+      <c r="D311" t="s">
+        <v>50</v>
+      </c>
+      <c r="F311" t="s">
+        <v>32</v>
+      </c>
+      <c r="G311" t="s">
+        <v>13</v>
+      </c>
+      <c r="H311" s="2">
+        <v>0</v>
+      </c>
+      <c r="I311" s="1">
+        <v>46237.753935185188</v>
+      </c>
+      <c r="J311" s="2">
+        <v>0</v>
+      </c>
+      <c r="K311" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="312" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B312" t="s">
+        <v>39</v>
+      </c>
+      <c r="C312">
+        <v>850</v>
+      </c>
+      <c r="D312" t="s">
+        <v>51</v>
+      </c>
+      <c r="F312" t="s">
+        <v>32</v>
+      </c>
+      <c r="G312" t="s">
+        <v>13</v>
+      </c>
+      <c r="H312" s="2">
+        <v>0</v>
+      </c>
+      <c r="I312" s="1">
+        <v>46237.754629629628</v>
+      </c>
+      <c r="J312" s="2">
+        <v>0</v>
+      </c>
+      <c r="K312" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="313" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H313" s="2"/>
       <c r="I313" s="1"/>
       <c r="J313" s="2"/>
       <c r="K313" s="1"/>
     </row>
-    <row r="314" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H314" s="2"/>
       <c r="I314" s="1"/>
       <c r="J314" s="2"/>
       <c r="K314" s="1"/>
     </row>
-    <row r="315" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H315" s="2"/>
       <c r="I315" s="1"/>
       <c r="J315" s="2"/>
       <c r="K315" s="1"/>
     </row>
-    <row r="316" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H316" s="2"/>
       <c r="I316" s="1"/>
       <c r="J316" s="2"/>
       <c r="K316" s="1"/>
     </row>
-    <row r="317" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H317" s="2"/>
       <c r="I317" s="1"/>
       <c r="J317" s="2"/>
       <c r="K317" s="1"/>
     </row>
-    <row r="318" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H318" s="2"/>
       <c r="I318" s="1"/>
       <c r="J318" s="2"/>
       <c r="K318" s="1"/>
     </row>
-    <row r="319" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H319" s="2"/>
       <c r="I319" s="1"/>
       <c r="J319" s="2"/>
       <c r="K319" s="1"/>
     </row>
-    <row r="320" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H320" s="2"/>
       <c r="I320" s="1"/>
       <c r="J320" s="2"/>
@@ -49302,6 +49581,7 @@
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
@@ -49316,11 +49596,13 @@
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -49331,10 +49613,13 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
@@ -49352,14 +49637,17 @@
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -49370,14 +49658,17 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
@@ -49404,6 +49695,7 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
@@ -49412,6 +49704,7 @@
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
@@ -49424,22 +49717,27 @@
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -49458,6 +49756,7 @@
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -49468,10 +49767,12 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
@@ -49480,10 +49781,12 @@
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
@@ -49497,82 +49800,97 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
@@ -49586,6 +49904,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -49596,6 +49915,7 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
@@ -49603,6 +49923,7 @@
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
@@ -49611,86 +49932,99 @@
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -49707,26 +50041,32 @@
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
@@ -49757,6 +50097,7 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
@@ -49766,10 +50107,12 @@
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
@@ -49782,14 +50125,17 @@
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
@@ -49798,14 +50144,17 @@
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
@@ -49824,26 +50173,32 @@
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -49862,6 +50217,7 @@
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
@@ -49870,10 +50226,12 @@
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
@@ -49882,6 +50240,7 @@
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
@@ -49894,10 +50253,12 @@
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
@@ -49906,6 +50267,7 @@
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
@@ -49914,14 +50276,17 @@
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
@@ -49930,14 +50295,17 @@
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
@@ -49954,76 +50322,85 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
@@ -50037,31 +50414,38 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
@@ -50074,10 +50458,12 @@
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
@@ -50086,10 +50472,12 @@
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
@@ -50098,6 +50486,7 @@
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -50112,10 +50501,12 @@
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
@@ -50124,10 +50515,12 @@
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
@@ -50141,6 +50534,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -50156,14 +50550,17 @@
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -50181,14 +50578,17 @@
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
@@ -50201,10 +50601,12 @@
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
@@ -50213,14 +50615,17 @@
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
@@ -50229,10 +50634,12 @@
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
@@ -50241,14 +50648,17 @@
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
@@ -50270,6 +50680,7 @@
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
@@ -50278,39 +50689,65 @@
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7395" s="2"/>
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
+    </row>
+    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7402" s="2"/>
+      <c r="I7402" s="1"/>
+    </row>
+    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="I7403" s="1"/>
+    </row>
+    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7404" s="2"/>
+      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EA36EB3-7332-4A92-8559-A8BAB25D4C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{481F2149-0295-4238-8EEE-10F57EBB52D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -574,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7404"/>
+  <dimension ref="A1:K7403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -650,7 +650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>39</v>
       </c>
@@ -824,7 +824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
         <v>39</v>
       </c>
@@ -940,7 +940,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>39</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>39</v>
       </c>
@@ -1449,7 +1449,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>39</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H42" s="2"/>
       <c r="I42" s="1"/>
       <c r="J42" s="2"/>
@@ -1982,7 +1982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>39</v>
       </c>
@@ -2478,7 +2478,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
         <v>39</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
         <v>39</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
         <v>39</v>
       </c>
@@ -3538,7 +3538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
         <v>39</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
         <v>39</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
         <v>39</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
         <v>39</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
         <v>39</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
         <v>39</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
         <v>39</v>
       </c>
@@ -7200,7 +7200,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
         <v>39</v>
       </c>
@@ -9000,7 +9000,7 @@
         <v>46237.711111111108</v>
       </c>
       <c r="J301" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K301" s="1" t="s">
         <v>11</v>
@@ -9029,7 +9029,7 @@
         <v>46237.711111111108</v>
       </c>
       <c r="J302" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K302" s="1" t="s">
         <v>11</v>
@@ -9058,7 +9058,7 @@
         <v>46237.711805555555</v>
       </c>
       <c r="J303" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K303" s="1" t="s">
         <v>11</v>
@@ -9087,7 +9087,7 @@
         <v>46237.712500000001</v>
       </c>
       <c r="J304" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K304" s="1" t="s">
         <v>11</v>
@@ -9116,7 +9116,7 @@
         <v>46237.713194444441</v>
       </c>
       <c r="J305" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K305" s="1" t="s">
         <v>11</v>
@@ -9145,7 +9145,7 @@
         <v>46237.713194444441</v>
       </c>
       <c r="J306" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K306" s="1" t="s">
         <v>11</v>
@@ -9174,7 +9174,7 @@
         <v>46237.751851851855</v>
       </c>
       <c r="J307" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K307" s="1" t="s">
         <v>11</v>
@@ -9203,7 +9203,7 @@
         <v>46237.752546296295</v>
       </c>
       <c r="J308" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K308" s="1" t="s">
         <v>11</v>
@@ -9232,7 +9232,7 @@
         <v>46237.752546296295</v>
       </c>
       <c r="J309" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K309" s="1" t="s">
         <v>11</v>
@@ -9261,7 +9261,7 @@
         <v>46237.753240740742</v>
       </c>
       <c r="J310" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K310" s="1" t="s">
         <v>11</v>
@@ -9290,7 +9290,7 @@
         <v>46237.753935185188</v>
       </c>
       <c r="J311" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K311" s="1" t="s">
         <v>11</v>
@@ -9319,7 +9319,7 @@
         <v>46237.754629629628</v>
       </c>
       <c r="J312" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K312" s="1" t="s">
         <v>11</v>
@@ -9397,7 +9397,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -9463,7 +9463,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -9475,7 +9475,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -9571,7 +9571,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -9583,7 +9583,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -9679,7 +9679,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -9739,7 +9739,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -48692,6 +48692,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -48984,6 +48985,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -49294,6 +49297,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -49418,6 +49422,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -49429,6 +49434,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -49577,6 +49583,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
@@ -49587,10 +49594,12 @@
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
@@ -49624,15 +49633,18 @@
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
@@ -49673,18 +49685,22 @@
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -49700,6 +49716,7 @@
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
@@ -49709,10 +49726,12 @@
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
@@ -49748,10 +49767,12 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
@@ -49777,6 +49798,7 @@
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
@@ -49791,6 +49813,7 @@
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -49825,6 +49848,7 @@
       <c r="K7205" s="1"/>
     </row>
     <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
@@ -49834,6 +49858,7 @@
       <c r="K7207" s="1"/>
     </row>
     <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
@@ -49843,6 +49868,7 @@
       <c r="K7209" s="1"/>
     </row>
     <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
@@ -49857,15 +49883,16 @@
       <c r="K7212" s="1"/>
     </row>
     <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
     <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
     <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
@@ -49895,6 +49922,7 @@
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -49915,11 +49943,13 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
       <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
@@ -49928,6 +49958,7 @@
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
@@ -49957,6 +49988,7 @@
       <c r="K7233" s="1"/>
     </row>
     <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
@@ -49966,10 +49998,12 @@
       <c r="K7235" s="1"/>
     </row>
     <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
     <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
@@ -49984,14 +50018,17 @@
       <c r="K7239" s="1"/>
     </row>
     <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
     <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
     <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
@@ -50011,10 +50048,12 @@
       <c r="K7245" s="1"/>
     </row>
     <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
     <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
@@ -50034,9 +50073,12 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
@@ -50071,18 +50113,22 @@
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -50097,12 +50143,12 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
@@ -50117,10 +50163,12 @@
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
@@ -50140,6 +50188,7 @@
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
@@ -50159,6 +50208,7 @@
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -50168,6 +50218,7 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
@@ -50213,6 +50264,7 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
@@ -50222,6 +50274,7 @@
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
@@ -50236,6 +50289,7 @@
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
@@ -50245,10 +50299,12 @@
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
@@ -50263,6 +50319,7 @@
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
@@ -50272,6 +50329,7 @@
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
@@ -50291,6 +50349,7 @@
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
@@ -50310,10 +50369,12 @@
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -50323,6 +50384,7 @@
       <c r="K7312" s="1"/>
     </row>
     <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
@@ -50333,10 +50395,12 @@
       <c r="K7314" s="1"/>
     </row>
     <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
     <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
@@ -50351,18 +50415,22 @@
       <c r="K7318" s="1"/>
     </row>
     <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
     <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
     <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
     <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
@@ -50382,10 +50450,12 @@
       <c r="K7325" s="1"/>
     </row>
     <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
     <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
@@ -50405,6 +50475,7 @@
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -50435,7 +50506,6 @@
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
@@ -50450,10 +50520,12 @@
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
@@ -50468,6 +50540,7 @@
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
@@ -50482,11 +50555,11 @@
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -50496,6 +50569,7 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
@@ -50511,6 +50585,7 @@
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
@@ -50525,6 +50600,7 @@
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -50545,6 +50621,7 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
@@ -50570,11 +50647,13 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
@@ -50593,15 +50672,16 @@
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
@@ -50611,6 +50691,7 @@
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
@@ -50630,6 +50711,7 @@
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
@@ -50644,6 +50726,7 @@
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
@@ -50663,10 +50746,12 @@
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -50676,6 +50761,7 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
@@ -50686,6 +50772,7 @@
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
@@ -50722,7 +50809,6 @@
       <c r="I7397" s="1"/>
     </row>
     <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
     <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
@@ -50731,6 +50817,7 @@
       <c r="K7399" s="1"/>
     </row>
     <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
       <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
     </row>
@@ -50744,10 +50831,6 @@
     </row>
     <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7403" s="1"/>
-    </row>
-    <row r="7404" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7404" s="2"/>
-      <c r="I7404" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{481F2149-0295-4238-8EEE-10F57EBB52D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{280A0858-C945-4B94-900E-B831A5EF8B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -146,16 +146,10 @@
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>DNU-Speed Management</t>
-  </si>
-  <si>
-    <t>DNU-Def.Drive Distracted Driving</t>
+    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Vehicle &amp; Roadside Inspections CMV</t>
-  </si>
-  <si>
-    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Edington Wrecker Service</t>
@@ -198,6 +192,12 @@
   </si>
   <si>
     <t>Scott Comer</t>
+  </si>
+  <si>
+    <t>DNU-Def.Drive Distracted Driving</t>
+  </si>
+  <si>
+    <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
@@ -574,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7403"/>
+  <dimension ref="A1:K7400"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -623,13 +623,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C2">
         <v>849</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -650,15 +650,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C3">
         <v>1133</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4">
         <v>1134</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>855</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -739,13 +739,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>852</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -768,13 +768,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>1135</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -797,13 +797,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>980</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -824,15 +824,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9">
         <v>851</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -855,13 +855,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10">
         <v>1136</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -884,13 +884,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>981</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -913,13 +913,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>848</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -940,15 +940,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13">
         <v>1137</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -971,13 +971,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>854</v>
       </c>
       <c r="D14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1138</v>
       </c>
       <c r="D15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -1029,13 +1029,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>850</v>
       </c>
       <c r="D16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -1058,13 +1058,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>1139</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18">
         <v>853</v>
       </c>
       <c r="D18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -1116,13 +1116,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>1140</v>
       </c>
       <c r="D19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -1145,16 +1145,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20">
         <v>849</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21">
         <v>855</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F21" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -1211,16 +1211,16 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23">
         <v>852</v>
       </c>
       <c r="D23" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
@@ -1240,16 +1240,16 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <v>980</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1275,18 +1275,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26">
         <v>851</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
@@ -1306,16 +1306,16 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27">
         <v>981</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1335,16 +1335,16 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28">
         <v>848</v>
       </c>
       <c r="D28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F28" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
@@ -1364,16 +1364,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29">
         <v>854</v>
       </c>
       <c r="D29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1393,16 +1393,16 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30">
         <v>850</v>
       </c>
       <c r="D30" t="s">
+        <v>49</v>
+      </c>
+      <c r="F30" t="s">
         <v>51</v>
-      </c>
-      <c r="F30" t="s">
-        <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -1422,16 +1422,16 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>853</v>
       </c>
       <c r="D31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -1449,18 +1449,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>849</v>
       </c>
       <c r="D32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1480,16 +1480,16 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C33">
         <v>855</v>
       </c>
       <c r="D33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1517,16 +1517,16 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35">
         <v>852</v>
       </c>
       <c r="D35" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -1546,16 +1546,16 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36">
         <v>980</v>
       </c>
       <c r="D36" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F36" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -1583,16 +1583,16 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C38">
         <v>851</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -1612,16 +1612,16 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C39">
         <v>981</v>
       </c>
       <c r="D39" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F39" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1641,16 +1641,16 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C40">
         <v>848</v>
       </c>
       <c r="D40" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F40" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -1670,16 +1670,16 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41">
         <v>854</v>
       </c>
       <c r="D41" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F41" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -1697,7 +1697,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H42" s="2"/>
       <c r="I42" s="1"/>
       <c r="J42" s="2"/>
@@ -1707,16 +1707,16 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43">
         <v>850</v>
       </c>
       <c r="D43" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F43" t="s">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44">
         <v>853</v>
       </c>
       <c r="D44" t="s">
+        <v>50</v>
+      </c>
+      <c r="F44" t="s">
         <v>52</v>
-      </c>
-      <c r="F44" t="s">
-        <v>35</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1765,13 +1765,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45">
         <v>849</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F45" t="s">
         <v>53</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46">
         <v>855</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F46" t="s">
         <v>53</v>
@@ -1831,13 +1831,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48">
         <v>852</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F48" t="s">
         <v>53</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50">
         <v>980</v>
       </c>
       <c r="D50" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F50" t="s">
         <v>53</v>
@@ -1897,13 +1897,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51">
         <v>851</v>
       </c>
       <c r="D51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F51" t="s">
         <v>53</v>
@@ -1926,13 +1926,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C52">
         <v>981</v>
       </c>
       <c r="D52" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F52" t="s">
         <v>53</v>
@@ -1955,13 +1955,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53">
         <v>848</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F53" t="s">
         <v>53</v>
@@ -1982,15 +1982,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C54">
         <v>854</v>
       </c>
       <c r="D54" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F54" t="s">
         <v>53</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C55">
         <v>850</v>
       </c>
       <c r="D55" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F55" t="s">
         <v>53</v>
@@ -2050,13 +2050,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C57">
         <v>853</v>
       </c>
       <c r="D57" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F57" t="s">
         <v>53</v>
@@ -2079,13 +2079,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C58">
         <v>849</v>
       </c>
       <c r="D58" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
@@ -2116,13 +2116,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C60">
         <v>855</v>
       </c>
       <c r="D60" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -2145,13 +2145,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C61">
         <v>852</v>
       </c>
       <c r="D61" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
@@ -2174,13 +2174,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C62">
         <v>851</v>
       </c>
       <c r="D62" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -2203,13 +2203,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C63">
         <v>848</v>
       </c>
       <c r="D63" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
@@ -2232,13 +2232,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C64">
         <v>854</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
@@ -2261,13 +2261,13 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C65">
         <v>850</v>
       </c>
       <c r="D65" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
@@ -2290,13 +2290,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C66">
         <v>853</v>
       </c>
       <c r="D66" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C67">
         <v>849</v>
       </c>
       <c r="D67" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F67" t="s">
         <v>33</v>
@@ -2356,13 +2356,13 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C69">
         <v>855</v>
       </c>
       <c r="D69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F69" t="s">
         <v>33</v>
@@ -2385,13 +2385,13 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C70">
         <v>852</v>
       </c>
       <c r="D70" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F70" t="s">
         <v>33</v>
@@ -2414,13 +2414,13 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C71">
         <v>980</v>
       </c>
       <c r="D71" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F71" t="s">
         <v>33</v>
@@ -2451,13 +2451,13 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C73">
         <v>851</v>
       </c>
       <c r="D73" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F73" t="s">
         <v>33</v>
@@ -2478,15 +2478,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C74">
         <v>981</v>
       </c>
       <c r="D74" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F74" t="s">
         <v>33</v>
@@ -2509,13 +2509,13 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C75">
         <v>848</v>
       </c>
       <c r="D75" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F75" t="s">
         <v>33</v>
@@ -2538,13 +2538,13 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C76">
         <v>854</v>
       </c>
       <c r="D76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F76" t="s">
         <v>33</v>
@@ -2567,13 +2567,13 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C77">
         <v>850</v>
       </c>
       <c r="D77" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F77" t="s">
         <v>33</v>
@@ -2596,13 +2596,13 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C78">
         <v>853</v>
       </c>
       <c r="D78" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F78" t="s">
         <v>33</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C79">
         <v>849</v>
       </c>
       <c r="D79" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F79" t="s">
         <v>17</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C80">
         <v>855</v>
       </c>
       <c r="D80" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
@@ -2683,13 +2683,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C81">
         <v>852</v>
       </c>
       <c r="D81" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
@@ -2710,15 +2710,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C82">
         <v>980</v>
       </c>
       <c r="D82" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F82" t="s">
         <v>17</v>
@@ -2741,13 +2741,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C83">
         <v>851</v>
       </c>
       <c r="D83" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
@@ -2770,13 +2770,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C84">
         <v>981</v>
       </c>
       <c r="D84" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
@@ -2799,13 +2799,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C85">
         <v>848</v>
       </c>
       <c r="D85" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F85" t="s">
         <v>17</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C86">
         <v>854</v>
       </c>
       <c r="D86" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -2857,13 +2857,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C87">
         <v>850</v>
       </c>
       <c r="D87" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F87" t="s">
         <v>17</v>
@@ -2894,13 +2894,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C89">
         <v>853</v>
       </c>
       <c r="D89" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F89" t="s">
         <v>17</v>
@@ -2923,13 +2923,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C90">
         <v>849</v>
       </c>
       <c r="D90" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2952,13 +2952,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C91">
         <v>855</v>
       </c>
       <c r="D91" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -2979,15 +2979,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C92">
         <v>852</v>
       </c>
       <c r="D92" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -3010,13 +3010,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C93">
         <v>980</v>
       </c>
       <c r="D93" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -3039,13 +3039,13 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C94">
         <v>851</v>
       </c>
       <c r="D94" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -3076,13 +3076,13 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C96">
         <v>981</v>
       </c>
       <c r="D96" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C97">
         <v>848</v>
       </c>
       <c r="D97" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -3134,13 +3134,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C98">
         <v>854</v>
       </c>
       <c r="D98" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -3163,13 +3163,13 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C99">
         <v>850</v>
       </c>
       <c r="D99" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -3192,13 +3192,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C100">
         <v>853</v>
       </c>
       <c r="D100" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -3221,13 +3221,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C101">
         <v>849</v>
       </c>
       <c r="D101" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
@@ -3250,13 +3250,13 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C102">
         <v>855</v>
       </c>
       <c r="D102" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F102" t="s">
         <v>20</v>
@@ -3279,13 +3279,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C103">
         <v>852</v>
       </c>
       <c r="D103" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F103" t="s">
         <v>20</v>
@@ -3308,13 +3308,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C104">
         <v>980</v>
       </c>
       <c r="D104" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C105">
         <v>851</v>
       </c>
       <c r="D105" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -3366,13 +3366,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C106">
         <v>981</v>
       </c>
       <c r="D106" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
@@ -3395,13 +3395,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C107">
         <v>848</v>
       </c>
       <c r="D107" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F107" t="s">
         <v>20</v>
@@ -3424,13 +3424,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C108">
         <v>854</v>
       </c>
       <c r="D108" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C109">
         <v>850</v>
       </c>
       <c r="D109" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F109" t="s">
         <v>20</v>
@@ -3482,13 +3482,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C110">
         <v>853</v>
       </c>
       <c r="D110" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F110" t="s">
         <v>20</v>
@@ -3511,13 +3511,13 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C111">
         <v>849</v>
       </c>
       <c r="D111" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
@@ -3538,15 +3538,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C112">
         <v>855</v>
       </c>
       <c r="D112" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -3569,13 +3569,13 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C113">
         <v>852</v>
       </c>
       <c r="D113" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F113" t="s">
         <v>21</v>
@@ -3598,13 +3598,13 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C114">
         <v>980</v>
       </c>
       <c r="D114" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F114" t="s">
         <v>21</v>
@@ -3625,15 +3625,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C115">
         <v>851</v>
       </c>
       <c r="D115" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F115" t="s">
         <v>21</v>
@@ -3656,13 +3656,13 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C116">
         <v>981</v>
       </c>
       <c r="D116" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -3685,13 +3685,13 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C117">
         <v>848</v>
       </c>
       <c r="D117" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C118">
         <v>854</v>
       </c>
       <c r="D118" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F118" t="s">
         <v>21</v>
@@ -3743,13 +3743,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C119">
         <v>850</v>
       </c>
       <c r="D119" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F119" t="s">
         <v>21</v>
@@ -3772,13 +3772,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C120">
         <v>853</v>
       </c>
       <c r="D120" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F120" t="s">
         <v>21</v>
@@ -3801,13 +3801,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C121">
         <v>849</v>
       </c>
       <c r="D121" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F121" t="s">
         <v>22</v>
@@ -3830,13 +3830,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C122">
         <v>855</v>
       </c>
       <c r="D122" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F122" t="s">
         <v>22</v>
@@ -3859,13 +3859,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C123">
         <v>852</v>
       </c>
       <c r="D123" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C124">
         <v>980</v>
       </c>
       <c r="D124" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F124" t="s">
         <v>22</v>
@@ -3917,13 +3917,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C125">
         <v>851</v>
       </c>
       <c r="D125" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F125" t="s">
         <v>22</v>
@@ -3946,13 +3946,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C126">
         <v>981</v>
       </c>
       <c r="D126" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
@@ -3973,15 +3973,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C127">
         <v>848</v>
       </c>
       <c r="D127" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F127" t="s">
         <v>22</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C128">
         <v>854</v>
       </c>
       <c r="D128" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F128" t="s">
         <v>22</v>
@@ -4033,13 +4033,13 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C129">
         <v>850</v>
       </c>
       <c r="D129" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F129" t="s">
         <v>22</v>
@@ -4062,13 +4062,13 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C130">
         <v>853</v>
       </c>
       <c r="D130" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F130" t="s">
         <v>22</v>
@@ -4091,16 +4091,16 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C131">
         <v>849</v>
       </c>
       <c r="D131" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F131" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G131" t="s">
         <v>13</v>
@@ -4120,16 +4120,16 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C132">
         <v>855</v>
       </c>
       <c r="D132" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F132" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4149,16 +4149,16 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C133">
         <v>852</v>
       </c>
       <c r="D133" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F133" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G133" t="s">
         <v>13</v>
@@ -4178,16 +4178,16 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C134">
         <v>980</v>
       </c>
       <c r="D134" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F134" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4207,16 +4207,16 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C135">
         <v>851</v>
       </c>
       <c r="D135" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F135" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4236,16 +4236,16 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C136">
         <v>981</v>
       </c>
       <c r="D136" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F136" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4265,16 +4265,16 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C137">
         <v>848</v>
       </c>
       <c r="D137" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F137" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G137" t="s">
         <v>13</v>
@@ -4294,16 +4294,16 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C138">
         <v>854</v>
       </c>
       <c r="D138" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F138" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G138" t="s">
         <v>13</v>
@@ -4323,16 +4323,16 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C139">
         <v>850</v>
       </c>
       <c r="D139" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F139" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G139" t="s">
         <v>13</v>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C140">
         <v>853</v>
       </c>
       <c r="D140" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F140" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G140" t="s">
         <v>13</v>
@@ -4381,13 +4381,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C141">
         <v>849</v>
       </c>
       <c r="D141" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F141" t="s">
         <v>26</v>
@@ -4410,13 +4410,13 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C142">
         <v>855</v>
       </c>
       <c r="D142" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F142" t="s">
         <v>26</v>
@@ -4439,13 +4439,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C143">
         <v>852</v>
       </c>
       <c r="D143" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F143" t="s">
         <v>26</v>
@@ -4468,13 +4468,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C144">
         <v>980</v>
       </c>
       <c r="D144" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F144" t="s">
         <v>26</v>
@@ -4497,13 +4497,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C145">
         <v>851</v>
       </c>
       <c r="D145" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F145" t="s">
         <v>26</v>
@@ -4526,13 +4526,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C146">
         <v>981</v>
       </c>
       <c r="D146" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F146" t="s">
         <v>26</v>
@@ -4555,13 +4555,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C147">
         <v>848</v>
       </c>
       <c r="D147" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F147" t="s">
         <v>26</v>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C148">
         <v>854</v>
       </c>
       <c r="D148" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F148" t="s">
         <v>26</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C149">
         <v>850</v>
       </c>
       <c r="D149" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F149" t="s">
         <v>26</v>
@@ -4642,13 +4642,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C150">
         <v>853</v>
       </c>
       <c r="D150" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F150" t="s">
         <v>26</v>
@@ -4671,13 +4671,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C151">
         <v>849</v>
       </c>
       <c r="D151" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F151" t="s">
         <v>24</v>
@@ -4700,13 +4700,13 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C152">
         <v>855</v>
       </c>
       <c r="D152" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F152" t="s">
         <v>24</v>
@@ -4729,13 +4729,13 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C153">
         <v>852</v>
       </c>
       <c r="D153" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F153" t="s">
         <v>24</v>
@@ -4758,13 +4758,13 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C154">
         <v>980</v>
       </c>
       <c r="D154" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F154" t="s">
         <v>24</v>
@@ -4787,13 +4787,13 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C155">
         <v>851</v>
       </c>
       <c r="D155" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F155" t="s">
         <v>24</v>
@@ -4816,13 +4816,13 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C156">
         <v>981</v>
       </c>
       <c r="D156" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -4845,13 +4845,13 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C157">
         <v>848</v>
       </c>
       <c r="D157" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -4874,13 +4874,13 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C158">
         <v>854</v>
       </c>
       <c r="D158" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F158" t="s">
         <v>24</v>
@@ -4903,13 +4903,13 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C159">
         <v>850</v>
       </c>
       <c r="D159" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F159" t="s">
         <v>24</v>
@@ -4932,13 +4932,13 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C160">
         <v>853</v>
       </c>
       <c r="D160" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F160" t="s">
         <v>24</v>
@@ -4961,13 +4961,13 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C161">
         <v>849</v>
       </c>
       <c r="D161" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F161" t="s">
         <v>23</v>
@@ -4990,13 +4990,13 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C162">
         <v>855</v>
       </c>
       <c r="D162" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F162" t="s">
         <v>23</v>
@@ -5019,13 +5019,13 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C163">
         <v>852</v>
       </c>
       <c r="D163" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F163" t="s">
         <v>23</v>
@@ -5048,13 +5048,13 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C164">
         <v>980</v>
       </c>
       <c r="D164" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F164" t="s">
         <v>23</v>
@@ -5077,13 +5077,13 @@
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C165">
         <v>851</v>
       </c>
       <c r="D165" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F165" t="s">
         <v>23</v>
@@ -5106,13 +5106,13 @@
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C166">
         <v>981</v>
       </c>
       <c r="D166" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F166" t="s">
         <v>23</v>
@@ -5135,13 +5135,13 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C167">
         <v>848</v>
       </c>
       <c r="D167" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F167" t="s">
         <v>23</v>
@@ -5164,13 +5164,13 @@
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C168">
         <v>854</v>
       </c>
       <c r="D168" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F168" t="s">
         <v>23</v>
@@ -5193,13 +5193,13 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C169">
         <v>850</v>
       </c>
       <c r="D169" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F169" t="s">
         <v>23</v>
@@ -5230,13 +5230,13 @@
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C171">
         <v>853</v>
       </c>
       <c r="D171" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F171" t="s">
         <v>23</v>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C172">
         <v>849</v>
       </c>
       <c r="D172" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F172" t="s">
         <v>17</v>
@@ -5288,13 +5288,13 @@
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C173">
         <v>855</v>
       </c>
       <c r="D173" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F173" t="s">
         <v>17</v>
@@ -5315,15 +5315,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="174" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C174">
         <v>852</v>
       </c>
       <c r="D174" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F174" t="s">
         <v>17</v>
@@ -5346,13 +5346,13 @@
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C175">
         <v>980</v>
       </c>
       <c r="D175" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F175" t="s">
         <v>17</v>
@@ -5375,13 +5375,13 @@
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C176">
         <v>851</v>
       </c>
       <c r="D176" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F176" t="s">
         <v>17</v>
@@ -5404,13 +5404,13 @@
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C177">
         <v>981</v>
       </c>
       <c r="D177" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F177" t="s">
         <v>17</v>
@@ -5433,13 +5433,13 @@
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C178">
         <v>848</v>
       </c>
       <c r="D178" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F178" t="s">
         <v>17</v>
@@ -5460,15 +5460,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="179" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C179">
         <v>854</v>
       </c>
       <c r="D179" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F179" t="s">
         <v>17</v>
@@ -5491,13 +5491,13 @@
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C180">
         <v>850</v>
       </c>
       <c r="D180" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F180" t="s">
         <v>17</v>
@@ -5520,13 +5520,13 @@
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C181">
         <v>853</v>
       </c>
       <c r="D181" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F181" t="s">
         <v>17</v>
@@ -5549,13 +5549,13 @@
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C182">
         <v>849</v>
       </c>
       <c r="D182" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
@@ -5578,13 +5578,13 @@
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C183">
         <v>855</v>
       </c>
       <c r="D183" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F183" t="s">
         <v>18</v>
@@ -5607,13 +5607,13 @@
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C184">
         <v>852</v>
       </c>
       <c r="D184" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F184" t="s">
         <v>18</v>
@@ -5636,13 +5636,13 @@
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C185">
         <v>980</v>
       </c>
       <c r="D185" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F185" t="s">
         <v>18</v>
@@ -5665,13 +5665,13 @@
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C186">
         <v>851</v>
       </c>
       <c r="D186" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F186" t="s">
         <v>18</v>
@@ -5694,13 +5694,13 @@
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C187">
         <v>981</v>
       </c>
       <c r="D187" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F187" t="s">
         <v>18</v>
@@ -5723,13 +5723,13 @@
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C188">
         <v>848</v>
       </c>
       <c r="D188" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F188" t="s">
         <v>18</v>
@@ -5750,15 +5750,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="189" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C189">
         <v>854</v>
       </c>
       <c r="D189" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F189" t="s">
         <v>18</v>
@@ -5781,13 +5781,13 @@
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C190">
         <v>850</v>
       </c>
       <c r="D190" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F190" t="s">
         <v>18</v>
@@ -5810,13 +5810,13 @@
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C191">
         <v>853</v>
       </c>
       <c r="D191" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F191" t="s">
         <v>18</v>
@@ -5839,13 +5839,13 @@
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C192">
         <v>849</v>
       </c>
       <c r="D192" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -5868,13 +5868,13 @@
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C193">
         <v>855</v>
       </c>
       <c r="D193" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F193" t="s">
         <v>34</v>
@@ -5897,13 +5897,13 @@
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C194">
         <v>852</v>
       </c>
       <c r="D194" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F194" t="s">
         <v>34</v>
@@ -5926,13 +5926,13 @@
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C195">
         <v>980</v>
       </c>
       <c r="D195" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F195" t="s">
         <v>34</v>
@@ -5955,13 +5955,13 @@
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C196">
         <v>851</v>
       </c>
       <c r="D196" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -5984,13 +5984,13 @@
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C197">
         <v>981</v>
       </c>
       <c r="D197" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F197" t="s">
         <v>34</v>
@@ -6013,13 +6013,13 @@
     </row>
     <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C198">
         <v>848</v>
       </c>
       <c r="D198" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F198" t="s">
         <v>34</v>
@@ -6042,13 +6042,13 @@
     </row>
     <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C199">
         <v>854</v>
       </c>
       <c r="D199" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F199" t="s">
         <v>34</v>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C200">
         <v>850</v>
       </c>
       <c r="D200" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -6100,13 +6100,13 @@
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C201">
         <v>853</v>
       </c>
       <c r="D201" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F201" t="s">
         <v>34</v>
@@ -6129,13 +6129,13 @@
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C202">
         <v>849</v>
       </c>
       <c r="D202" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F202" t="s">
         <v>34</v>
@@ -6158,13 +6158,13 @@
     </row>
     <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C203">
         <v>855</v>
       </c>
       <c r="D203" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F203" t="s">
         <v>34</v>
@@ -6187,13 +6187,13 @@
     </row>
     <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C204">
         <v>852</v>
       </c>
       <c r="D204" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F204" t="s">
         <v>34</v>
@@ -6216,13 +6216,13 @@
     </row>
     <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C205">
         <v>980</v>
       </c>
       <c r="D205" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -6245,13 +6245,13 @@
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C206">
         <v>851</v>
       </c>
       <c r="D206" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F206" t="s">
         <v>34</v>
@@ -6272,15 +6272,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="207" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C207">
         <v>981</v>
       </c>
       <c r="D207" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F207" t="s">
         <v>34</v>
@@ -6303,13 +6303,13 @@
     </row>
     <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C208">
         <v>848</v>
       </c>
       <c r="D208" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F208" t="s">
         <v>34</v>
@@ -6332,13 +6332,13 @@
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C209">
         <v>854</v>
       </c>
       <c r="D209" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -6361,13 +6361,13 @@
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C210">
         <v>850</v>
       </c>
       <c r="D210" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F210" t="s">
         <v>34</v>
@@ -6390,13 +6390,13 @@
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C211">
         <v>853</v>
       </c>
       <c r="D211" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F211" t="s">
         <v>34</v>
@@ -6419,13 +6419,13 @@
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C212">
         <v>849</v>
       </c>
       <c r="D212" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F212" t="s">
         <v>25</v>
@@ -6448,13 +6448,13 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C213">
         <v>855</v>
       </c>
       <c r="D213" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F213" t="s">
         <v>25</v>
@@ -6477,13 +6477,13 @@
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C214">
         <v>852</v>
       </c>
       <c r="D214" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F214" t="s">
         <v>25</v>
@@ -6506,13 +6506,13 @@
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C215">
         <v>980</v>
       </c>
       <c r="D215" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F215" t="s">
         <v>25</v>
@@ -6535,13 +6535,13 @@
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C216">
         <v>851</v>
       </c>
       <c r="D216" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F216" t="s">
         <v>25</v>
@@ -6564,13 +6564,13 @@
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C217">
         <v>848</v>
       </c>
       <c r="D217" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F217" t="s">
         <v>25</v>
@@ -6593,13 +6593,13 @@
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C218">
         <v>854</v>
       </c>
       <c r="D218" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F218" t="s">
         <v>25</v>
@@ -6622,13 +6622,13 @@
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C219">
         <v>850</v>
       </c>
       <c r="D219" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F219" t="s">
         <v>25</v>
@@ -6651,13 +6651,13 @@
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C220">
         <v>853</v>
       </c>
       <c r="D220" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -6680,16 +6680,16 @@
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C221">
         <v>849</v>
       </c>
       <c r="D221" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F221" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6709,16 +6709,16 @@
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C222">
         <v>855</v>
       </c>
       <c r="D222" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F222" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G222" t="s">
         <v>13</v>
@@ -6738,16 +6738,16 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C223">
         <v>852</v>
       </c>
       <c r="D223" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F223" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G223" t="s">
         <v>13</v>
@@ -6767,16 +6767,16 @@
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C224">
         <v>980</v>
       </c>
       <c r="D224" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F224" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G224" t="s">
         <v>10</v>
@@ -6796,16 +6796,16 @@
     </row>
     <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C225">
         <v>851</v>
       </c>
       <c r="D225" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F225" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G225" t="s">
         <v>13</v>
@@ -6825,16 +6825,16 @@
     </row>
     <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C226">
         <v>848</v>
       </c>
       <c r="D226" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F226" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G226" t="s">
         <v>13</v>
@@ -6854,16 +6854,16 @@
     </row>
     <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C227">
         <v>854</v>
       </c>
       <c r="D227" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F227" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G227" t="s">
         <v>13</v>
@@ -6883,16 +6883,16 @@
     </row>
     <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C228">
         <v>850</v>
       </c>
       <c r="D228" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F228" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G228" t="s">
         <v>13</v>
@@ -6912,16 +6912,16 @@
     </row>
     <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C229">
         <v>853</v>
       </c>
       <c r="D229" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F229" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G229" t="s">
         <v>13</v>
@@ -6941,13 +6941,13 @@
     </row>
     <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C230">
         <v>849</v>
       </c>
       <c r="D230" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F230" t="s">
         <v>19</v>
@@ -6970,13 +6970,13 @@
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C231">
         <v>855</v>
       </c>
       <c r="D231" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -6999,13 +6999,13 @@
     </row>
     <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C232">
         <v>852</v>
       </c>
       <c r="D232" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -7028,13 +7028,13 @@
     </row>
     <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C233">
         <v>980</v>
       </c>
       <c r="D233" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F233" t="s">
         <v>19</v>
@@ -7057,13 +7057,13 @@
     </row>
     <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C234">
         <v>851</v>
       </c>
       <c r="D234" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F234" t="s">
         <v>19</v>
@@ -7086,13 +7086,13 @@
     </row>
     <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C235">
         <v>848</v>
       </c>
       <c r="D235" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -7115,13 +7115,13 @@
     </row>
     <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C236">
         <v>854</v>
       </c>
       <c r="D236" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -7144,13 +7144,13 @@
     </row>
     <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C237">
         <v>850</v>
       </c>
       <c r="D237" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F237" t="s">
         <v>19</v>
@@ -7173,13 +7173,13 @@
     </row>
     <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C238">
         <v>853</v>
       </c>
       <c r="D238" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -7200,15 +7200,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="239" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C239">
         <v>849</v>
       </c>
       <c r="D239" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F239" t="s">
         <v>20</v>
@@ -7231,13 +7231,13 @@
     </row>
     <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C240">
         <v>855</v>
       </c>
       <c r="D240" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F240" t="s">
         <v>20</v>
@@ -7260,13 +7260,13 @@
     </row>
     <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C241">
         <v>852</v>
       </c>
       <c r="D241" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F241" t="s">
         <v>20</v>
@@ -7289,13 +7289,13 @@
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C242">
         <v>980</v>
       </c>
       <c r="D242" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F242" t="s">
         <v>20</v>
@@ -7318,13 +7318,13 @@
     </row>
     <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C243">
         <v>851</v>
       </c>
       <c r="D243" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F243" t="s">
         <v>20</v>
@@ -7347,13 +7347,13 @@
     </row>
     <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C244">
         <v>848</v>
       </c>
       <c r="D244" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F244" t="s">
         <v>20</v>
@@ -7376,13 +7376,13 @@
     </row>
     <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C245">
         <v>854</v>
       </c>
       <c r="D245" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F245" t="s">
         <v>20</v>
@@ -7405,13 +7405,13 @@
     </row>
     <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C246">
         <v>850</v>
       </c>
       <c r="D246" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F246" t="s">
         <v>20</v>
@@ -7434,13 +7434,13 @@
     </row>
     <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C247">
         <v>853</v>
       </c>
       <c r="D247" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F247" t="s">
         <v>20</v>
@@ -7463,13 +7463,13 @@
     </row>
     <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C248">
         <v>849</v>
       </c>
       <c r="D248" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F248" t="s">
         <v>27</v>
@@ -7492,13 +7492,13 @@
     </row>
     <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C249">
         <v>855</v>
       </c>
       <c r="D249" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F249" t="s">
         <v>27</v>
@@ -7521,13 +7521,13 @@
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C250">
         <v>852</v>
       </c>
       <c r="D250" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F250" t="s">
         <v>27</v>
@@ -7550,13 +7550,13 @@
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C251">
         <v>980</v>
       </c>
       <c r="D251" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F251" t="s">
         <v>27</v>
@@ -7579,13 +7579,13 @@
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C252">
         <v>851</v>
       </c>
       <c r="D252" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F252" t="s">
         <v>27</v>
@@ -7608,13 +7608,13 @@
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C253">
         <v>848</v>
       </c>
       <c r="D253" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F253" t="s">
         <v>27</v>
@@ -7637,13 +7637,13 @@
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C254">
         <v>854</v>
       </c>
       <c r="D254" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F254" t="s">
         <v>27</v>
@@ -7666,13 +7666,13 @@
     </row>
     <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C255">
         <v>850</v>
       </c>
       <c r="D255" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F255" t="s">
         <v>27</v>
@@ -7703,13 +7703,13 @@
     </row>
     <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C257">
         <v>853</v>
       </c>
       <c r="D257" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F257" t="s">
         <v>27</v>
@@ -7732,13 +7732,13 @@
     </row>
     <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C258">
         <v>849</v>
       </c>
       <c r="D258" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -7761,13 +7761,13 @@
     </row>
     <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C259">
         <v>855</v>
       </c>
       <c r="D259" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -7790,13 +7790,13 @@
     </row>
     <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C260">
         <v>852</v>
       </c>
       <c r="D260" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -7819,13 +7819,13 @@
     </row>
     <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C261">
         <v>980</v>
       </c>
       <c r="D261" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -7848,13 +7848,13 @@
     </row>
     <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C262">
         <v>851</v>
       </c>
       <c r="D262" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -7877,13 +7877,13 @@
     </row>
     <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C263">
         <v>848</v>
       </c>
       <c r="D263" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -7906,13 +7906,13 @@
     </row>
     <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C264">
         <v>854</v>
       </c>
       <c r="D264" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -7935,13 +7935,13 @@
     </row>
     <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C265">
         <v>850</v>
       </c>
       <c r="D265" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -7964,13 +7964,13 @@
     </row>
     <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C266">
         <v>853</v>
       </c>
       <c r="D266" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -7993,13 +7993,13 @@
     </row>
     <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C267">
         <v>849</v>
       </c>
       <c r="D267" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F267" t="s">
         <v>29</v>
@@ -8022,13 +8022,13 @@
     </row>
     <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C268">
         <v>855</v>
       </c>
       <c r="D268" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F268" t="s">
         <v>29</v>
@@ -8051,13 +8051,13 @@
     </row>
     <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C269">
         <v>852</v>
       </c>
       <c r="D269" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F269" t="s">
         <v>29</v>
@@ -8080,13 +8080,13 @@
     </row>
     <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C270">
         <v>980</v>
       </c>
       <c r="D270" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F270" t="s">
         <v>29</v>
@@ -8109,13 +8109,13 @@
     </row>
     <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C271">
         <v>851</v>
       </c>
       <c r="D271" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F271" t="s">
         <v>29</v>
@@ -8138,13 +8138,13 @@
     </row>
     <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C272">
         <v>848</v>
       </c>
       <c r="D272" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F272" t="s">
         <v>29</v>
@@ -8167,13 +8167,13 @@
     </row>
     <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C273">
         <v>854</v>
       </c>
       <c r="D273" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F273" t="s">
         <v>29</v>
@@ -8196,13 +8196,13 @@
     </row>
     <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C274">
         <v>850</v>
       </c>
       <c r="D274" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F274" t="s">
         <v>29</v>
@@ -8225,13 +8225,13 @@
     </row>
     <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C275">
         <v>853</v>
       </c>
       <c r="D275" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F275" t="s">
         <v>29</v>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C276">
         <v>849</v>
       </c>
       <c r="D276" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F276" t="s">
         <v>30</v>
@@ -8283,13 +8283,13 @@
     </row>
     <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C277">
         <v>852</v>
       </c>
       <c r="D277" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F277" t="s">
         <v>30</v>
@@ -8312,13 +8312,13 @@
     </row>
     <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C278">
         <v>980</v>
       </c>
       <c r="D278" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F278" t="s">
         <v>30</v>
@@ -8341,13 +8341,13 @@
     </row>
     <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C279">
         <v>851</v>
       </c>
       <c r="D279" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F279" t="s">
         <v>30</v>
@@ -8370,13 +8370,13 @@
     </row>
     <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C280">
         <v>848</v>
       </c>
       <c r="D280" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F280" t="s">
         <v>30</v>
@@ -8399,13 +8399,13 @@
     </row>
     <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C281">
         <v>854</v>
       </c>
       <c r="D281" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F281" t="s">
         <v>30</v>
@@ -8428,13 +8428,13 @@
     </row>
     <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C282">
         <v>850</v>
       </c>
       <c r="D282" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F282" t="s">
         <v>30</v>
@@ -8457,13 +8457,13 @@
     </row>
     <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C283">
         <v>849</v>
       </c>
       <c r="D283" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F283" t="s">
         <v>21</v>
@@ -8486,13 +8486,13 @@
     </row>
     <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C284">
         <v>852</v>
       </c>
       <c r="D284" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F284" t="s">
         <v>21</v>
@@ -8515,13 +8515,13 @@
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C285">
         <v>980</v>
       </c>
       <c r="D285" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F285" t="s">
         <v>21</v>
@@ -8544,13 +8544,13 @@
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C286">
         <v>848</v>
       </c>
       <c r="D286" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F286" t="s">
         <v>21</v>
@@ -8573,13 +8573,13 @@
     </row>
     <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C287">
         <v>854</v>
       </c>
       <c r="D287" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F287" t="s">
         <v>21</v>
@@ -8602,13 +8602,13 @@
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C288">
         <v>850</v>
       </c>
       <c r="D288" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F288" t="s">
         <v>21</v>
@@ -8631,13 +8631,13 @@
     </row>
     <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C289">
         <v>849</v>
       </c>
       <c r="D289" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F289" t="s">
         <v>31</v>
@@ -8660,13 +8660,13 @@
     </row>
     <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C290">
         <v>852</v>
       </c>
       <c r="D290" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -8689,13 +8689,13 @@
     </row>
     <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C291">
         <v>980</v>
       </c>
       <c r="D291" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F291" t="s">
         <v>31</v>
@@ -8718,13 +8718,13 @@
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C292">
         <v>848</v>
       </c>
       <c r="D292" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F292" t="s">
         <v>31</v>
@@ -8747,13 +8747,13 @@
     </row>
     <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C293">
         <v>854</v>
       </c>
       <c r="D293" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F293" t="s">
         <v>31</v>
@@ -8776,13 +8776,13 @@
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C294">
         <v>850</v>
       </c>
       <c r="D294" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -8805,13 +8805,13 @@
     </row>
     <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C295">
         <v>849</v>
       </c>
       <c r="D295" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F295" t="s">
         <v>23</v>
@@ -8834,13 +8834,13 @@
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C296">
         <v>852</v>
       </c>
       <c r="D296" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F296" t="s">
         <v>23</v>
@@ -8863,13 +8863,13 @@
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C297">
         <v>980</v>
       </c>
       <c r="D297" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F297" t="s">
         <v>23</v>
@@ -8892,13 +8892,13 @@
     </row>
     <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C298">
         <v>848</v>
       </c>
       <c r="D298" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F298" t="s">
         <v>23</v>
@@ -8921,13 +8921,13 @@
     </row>
     <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C299">
         <v>854</v>
       </c>
       <c r="D299" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F299" t="s">
         <v>23</v>
@@ -8950,13 +8950,13 @@
     </row>
     <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C300">
         <v>850</v>
       </c>
       <c r="D300" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F300" t="s">
         <v>23</v>
@@ -8979,13 +8979,13 @@
     </row>
     <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C301">
         <v>849</v>
       </c>
       <c r="D301" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F301" t="s">
         <v>32</v>
@@ -9008,13 +9008,13 @@
     </row>
     <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C302">
         <v>852</v>
       </c>
       <c r="D302" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F302" t="s">
         <v>32</v>
@@ -9037,13 +9037,13 @@
     </row>
     <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C303">
         <v>980</v>
       </c>
       <c r="D303" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F303" t="s">
         <v>32</v>
@@ -9066,13 +9066,13 @@
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C304">
         <v>848</v>
       </c>
       <c r="D304" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F304" t="s">
         <v>32</v>
@@ -9095,13 +9095,13 @@
     </row>
     <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C305">
         <v>854</v>
       </c>
       <c r="D305" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F305" t="s">
         <v>32</v>
@@ -9124,13 +9124,13 @@
     </row>
     <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C306">
         <v>850</v>
       </c>
       <c r="D306" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F306" t="s">
         <v>32</v>
@@ -9153,13 +9153,13 @@
     </row>
     <row r="307" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C307">
         <v>849</v>
       </c>
       <c r="D307" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F307" t="s">
         <v>32</v>
@@ -9182,13 +9182,13 @@
     </row>
     <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C308">
         <v>852</v>
       </c>
       <c r="D308" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F308" t="s">
         <v>32</v>
@@ -9211,13 +9211,13 @@
     </row>
     <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C309">
         <v>980</v>
       </c>
       <c r="D309" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F309" t="s">
         <v>32</v>
@@ -9240,13 +9240,13 @@
     </row>
     <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C310">
         <v>848</v>
       </c>
       <c r="D310" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F310" t="s">
         <v>32</v>
@@ -9269,13 +9269,13 @@
     </row>
     <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C311">
         <v>854</v>
       </c>
       <c r="D311" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F311" t="s">
         <v>32</v>
@@ -9298,13 +9298,13 @@
     </row>
     <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C312">
         <v>850</v>
       </c>
       <c r="D312" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F312" t="s">
         <v>32</v>
@@ -9397,7 +9397,7 @@
       <c r="J324" s="2"/>
       <c r="K324" s="1"/>
     </row>
-    <row r="325" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H325" s="2"/>
       <c r="I325" s="1"/>
       <c r="J325" s="2"/>
@@ -9463,7 +9463,7 @@
       <c r="J335" s="2"/>
       <c r="K335" s="1"/>
     </row>
-    <row r="336" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H336" s="2"/>
       <c r="I336" s="1"/>
       <c r="J336" s="2"/>
@@ -9475,7 +9475,7 @@
       <c r="J337" s="2"/>
       <c r="K337" s="1"/>
     </row>
-    <row r="338" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H338" s="2"/>
       <c r="I338" s="1"/>
       <c r="J338" s="2"/>
@@ -9571,7 +9571,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
     </row>
-    <row r="354" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H354" s="2"/>
       <c r="I354" s="1"/>
       <c r="J354" s="2"/>
@@ -9583,7 +9583,7 @@
       <c r="J355" s="2"/>
       <c r="K355" s="1"/>
     </row>
-    <row r="356" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H356" s="2"/>
       <c r="I356" s="1"/>
       <c r="J356" s="2"/>
@@ -9679,7 +9679,7 @@
       <c r="J371" s="2"/>
       <c r="K371" s="1"/>
     </row>
-    <row r="372" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H372" s="2"/>
       <c r="I372" s="1"/>
       <c r="J372" s="2"/>
@@ -9739,7 +9739,7 @@
       <c r="J381" s="2"/>
       <c r="K381" s="1"/>
     </row>
-    <row r="382" spans="8:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H382" s="2"/>
       <c r="I382" s="1"/>
       <c r="J382" s="2"/>
@@ -48692,7 +48692,6 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -48985,8 +48984,6 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7055" s="2"/>
-      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -49297,7 +49294,6 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -49422,7 +49418,6 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -49434,7 +49429,6 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -49583,35 +49577,29 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -49622,44 +49610,35 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7162" s="2"/>
-      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -49670,37 +49649,30 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -49711,52 +49683,42 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -49767,17 +49729,14 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -49788,32 +49747,26 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -49823,106 +49776,86 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7201" s="2"/>
+    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7202" s="2"/>
+    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7203" s="2"/>
+    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7204" s="2"/>
+    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7205" s="2"/>
+    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7206" s="2"/>
+    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7207" s="2"/>
+    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7208" s="2"/>
+    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7209" s="2"/>
+    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7210" s="2"/>
+    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7211" s="2"/>
+    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7212" s="2"/>
+    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7214" s="2"/>
+    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7215" s="2"/>
+    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7216" s="2"/>
+    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -49932,7 +49865,6 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -49943,127 +49875,101 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7225" s="2"/>
-      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7233" s="2"/>
+    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7234" s="2"/>
+    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7235" s="2"/>
+    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7236" s="2"/>
+    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7237" s="2"/>
+    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7238" s="2"/>
+    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7239" s="2"/>
+    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7240" s="2"/>
+    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7241" s="2"/>
+    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7242" s="2"/>
+    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7243" s="2"/>
+    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7244" s="2"/>
+    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7245" s="2"/>
+    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7246" s="2"/>
+    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7247" s="2"/>
+    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7248" s="2"/>
+    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -50073,62 +49979,49 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7251" s="2"/>
-      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -50148,67 +50041,54 @@
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -50218,38 +50098,31 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -50264,117 +50137,94 @@
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -50383,99 +50233,80 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7313" s="2"/>
+    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7314" s="2"/>
+    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7315" s="2"/>
+    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7316" s="2"/>
+    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7317" s="2"/>
+    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7318" s="2"/>
+    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7319" s="2"/>
+    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7320" s="2"/>
+    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7321" s="2"/>
+    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7322" s="2"/>
+    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7323" s="2"/>
+    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7324" s="2"/>
+    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7325" s="2"/>
+    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7326" s="2"/>
+    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7327" s="2"/>
+    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7328" s="2"/>
+    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -50485,23 +50316,19 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
@@ -50510,52 +50337,42 @@
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
@@ -50569,38 +50386,31 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -50610,7 +50420,6 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -50621,23 +50430,19 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -50647,37 +50452,30 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
@@ -50686,72 +50484,58 @@
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -50761,76 +50545,51 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7393" s="2"/>
+    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7394" s="1"/>
+    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7395" s="2"/>
+    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7396" s="2"/>
+    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7397" s="2"/>
+    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7399" s="2"/>
-      <c r="I7399" s="1"/>
+    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7400" s="2"/>
-      <c r="I7400" s="1"/>
+    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
       <c r="K7400" s="1"/>
-    </row>
-    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7401" s="2"/>
-      <c r="I7401" s="1"/>
-    </row>
-    <row r="7402" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H7402" s="2"/>
-      <c r="I7402" s="1"/>
-    </row>
-    <row r="7403" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="I7403" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Edingtons\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{280A0858-C945-4B94-900E-B831A5EF8B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35BAF8C8-5101-48DB-94CE-D3303A01FD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -146,10 +146,16 @@
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
   </si>
   <si>
-    <t>In Cab Distractions</t>
+    <t>DNU-Speed Management</t>
+  </si>
+  <si>
+    <t>DNU-Def.Drive Distracted Driving</t>
   </si>
   <si>
     <t>Vehicle &amp; Roadside Inspections CMV</t>
+  </si>
+  <si>
+    <t>In Cab Distractions</t>
   </si>
   <si>
     <t>Edington Wrecker Service</t>
@@ -192,12 +198,6 @@
   </si>
   <si>
     <t>Scott Comer</t>
-  </si>
-  <si>
-    <t>DNU-Def.Drive Distracted Driving</t>
-  </si>
-  <si>
-    <t>DNU-Speed Management</t>
   </si>
   <si>
     <t>DNUNEW-Space Management Big 5</t>
@@ -574,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="A1:K7400"/>
+  <dimension ref="A1:K7401"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -623,13 +623,13 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>849</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
@@ -652,13 +652,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3">
         <v>1133</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
@@ -681,13 +681,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4">
         <v>1134</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
@@ -710,13 +710,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C5">
         <v>855</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F5" t="s">
         <v>16</v>
@@ -739,13 +739,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6">
         <v>852</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
@@ -768,13 +768,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7">
         <v>1135</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F7" t="s">
         <v>16</v>
@@ -797,13 +797,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C8">
         <v>980</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
@@ -826,13 +826,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>851</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
@@ -855,13 +855,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>1136</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F10" t="s">
         <v>16</v>
@@ -884,13 +884,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>981</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
         <v>16</v>
@@ -913,13 +913,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C12">
         <v>848</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
         <v>16</v>
@@ -942,13 +942,13 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13">
         <v>1137</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
         <v>16</v>
@@ -971,13 +971,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>854</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
         <v>16</v>
@@ -1000,13 +1000,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C15">
         <v>1138</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>16</v>
@@ -1029,13 +1029,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C16">
         <v>850</v>
       </c>
       <c r="D16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
@@ -1058,13 +1058,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1139</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F17" t="s">
         <v>16</v>
@@ -1087,13 +1087,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>853</v>
       </c>
       <c r="D18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>16</v>
@@ -1116,13 +1116,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19">
         <v>1140</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F19" t="s">
         <v>16</v>
@@ -1145,16 +1145,16 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C20">
         <v>849</v>
       </c>
       <c r="D20" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
@@ -1174,16 +1174,16 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>855</v>
       </c>
       <c r="D21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G21" t="s">
         <v>12</v>
@@ -1211,16 +1211,16 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>852</v>
       </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
@@ -1240,16 +1240,16 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C24">
         <v>980</v>
       </c>
       <c r="D24" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F24" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1277,16 +1277,16 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C26">
         <v>851</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G26" t="s">
         <v>13</v>
@@ -1306,16 +1306,16 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C27">
         <v>981</v>
       </c>
       <c r="D27" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F27" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>10</v>
@@ -1335,16 +1335,16 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C28">
         <v>848</v>
       </c>
       <c r="D28" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
@@ -1364,16 +1364,16 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C29">
         <v>854</v>
       </c>
       <c r="D29" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G29" t="s">
         <v>10</v>
@@ -1393,16 +1393,16 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C30">
         <v>850</v>
       </c>
       <c r="D30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F30" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
@@ -1422,16 +1422,16 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C31">
         <v>853</v>
       </c>
       <c r="D31" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
@@ -1451,16 +1451,16 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>849</v>
       </c>
       <c r="D32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
@@ -1480,16 +1480,16 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>855</v>
       </c>
       <c r="D33" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G33" t="s">
         <v>12</v>
@@ -1517,16 +1517,16 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C35">
         <v>852</v>
       </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
@@ -1546,16 +1546,16 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C36">
         <v>980</v>
       </c>
       <c r="D36" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G36" t="s">
         <v>12</v>
@@ -1583,16 +1583,16 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <v>851</v>
       </c>
       <c r="D38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G38" t="s">
         <v>13</v>
@@ -1612,16 +1612,16 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C39">
         <v>981</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -1641,16 +1641,16 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C40">
         <v>848</v>
       </c>
       <c r="D40" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F40" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
@@ -1670,16 +1670,16 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C41">
         <v>854</v>
       </c>
       <c r="D41" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F41" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G41" t="s">
         <v>12</v>
@@ -1707,16 +1707,16 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>850</v>
       </c>
       <c r="D43" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G43" t="s">
         <v>13</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C44">
         <v>853</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="G44" t="s">
         <v>13</v>
@@ -1765,13 +1765,13 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C45">
         <v>849</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F45" t="s">
         <v>53</v>
@@ -1794,13 +1794,13 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C46">
         <v>855</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F46" t="s">
         <v>53</v>
@@ -1831,13 +1831,13 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C48">
         <v>852</v>
       </c>
       <c r="D48" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F48" t="s">
         <v>53</v>
@@ -1868,13 +1868,13 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C50">
         <v>980</v>
       </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F50" t="s">
         <v>53</v>
@@ -1897,13 +1897,13 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C51">
         <v>851</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F51" t="s">
         <v>53</v>
@@ -1926,13 +1926,13 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C52">
         <v>981</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F52" t="s">
         <v>53</v>
@@ -1955,13 +1955,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C53">
         <v>848</v>
       </c>
       <c r="D53" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F53" t="s">
         <v>53</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C54">
         <v>854</v>
       </c>
       <c r="D54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F54" t="s">
         <v>53</v>
@@ -2013,13 +2013,13 @@
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C55">
         <v>850</v>
       </c>
       <c r="D55" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
         <v>53</v>
@@ -2050,13 +2050,13 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C57">
         <v>853</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F57" t="s">
         <v>53</v>
@@ -2079,13 +2079,13 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C58">
         <v>849</v>
       </c>
       <c r="D58" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F58" t="s">
         <v>26</v>
@@ -2116,13 +2116,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C60">
         <v>855</v>
       </c>
       <c r="D60" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F60" t="s">
         <v>26</v>
@@ -2145,13 +2145,13 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C61">
         <v>852</v>
       </c>
       <c r="D61" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F61" t="s">
         <v>26</v>
@@ -2174,13 +2174,13 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C62">
         <v>851</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F62" t="s">
         <v>26</v>
@@ -2203,13 +2203,13 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C63">
         <v>848</v>
       </c>
       <c r="D63" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F63" t="s">
         <v>26</v>
@@ -2232,13 +2232,13 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C64">
         <v>854</v>
       </c>
       <c r="D64" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F64" t="s">
         <v>26</v>
@@ -2261,13 +2261,13 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C65">
         <v>850</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F65" t="s">
         <v>26</v>
@@ -2290,13 +2290,13 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C66">
         <v>853</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F66" t="s">
         <v>26</v>
@@ -2319,13 +2319,13 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C67">
         <v>849</v>
       </c>
       <c r="D67" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F67" t="s">
         <v>33</v>
@@ -2356,13 +2356,13 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C69">
         <v>855</v>
       </c>
       <c r="D69" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F69" t="s">
         <v>33</v>
@@ -2385,13 +2385,13 @@
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C70">
         <v>852</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F70" t="s">
         <v>33</v>
@@ -2414,13 +2414,13 @@
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C71">
         <v>980</v>
       </c>
       <c r="D71" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F71" t="s">
         <v>33</v>
@@ -2451,13 +2451,13 @@
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C73">
         <v>851</v>
       </c>
       <c r="D73" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F73" t="s">
         <v>33</v>
@@ -2480,13 +2480,13 @@
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B74" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C74">
         <v>981</v>
       </c>
       <c r="D74" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F74" t="s">
         <v>33</v>
@@ -2509,13 +2509,13 @@
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C75">
         <v>848</v>
       </c>
       <c r="D75" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F75" t="s">
         <v>33</v>
@@ -2538,13 +2538,13 @@
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C76">
         <v>854</v>
       </c>
       <c r="D76" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F76" t="s">
         <v>33</v>
@@ -2567,13 +2567,13 @@
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C77">
         <v>850</v>
       </c>
       <c r="D77" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F77" t="s">
         <v>33</v>
@@ -2596,13 +2596,13 @@
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B78" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C78">
         <v>853</v>
       </c>
       <c r="D78" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F78" t="s">
         <v>33</v>
@@ -2625,13 +2625,13 @@
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C79">
         <v>849</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F79" t="s">
         <v>17</v>
@@ -2654,13 +2654,13 @@
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C80">
         <v>855</v>
       </c>
       <c r="D80" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
@@ -2683,13 +2683,13 @@
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C81">
         <v>852</v>
       </c>
       <c r="D81" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F81" t="s">
         <v>17</v>
@@ -2712,13 +2712,13 @@
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B82" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C82">
         <v>980</v>
       </c>
       <c r="D82" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F82" t="s">
         <v>17</v>
@@ -2741,13 +2741,13 @@
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B83" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C83">
         <v>851</v>
       </c>
       <c r="D83" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F83" t="s">
         <v>17</v>
@@ -2770,13 +2770,13 @@
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B84" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C84">
         <v>981</v>
       </c>
       <c r="D84" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
@@ -2799,13 +2799,13 @@
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B85" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C85">
         <v>848</v>
       </c>
       <c r="D85" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F85" t="s">
         <v>17</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B86" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C86">
         <v>854</v>
       </c>
       <c r="D86" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -2857,13 +2857,13 @@
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B87" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C87">
         <v>850</v>
       </c>
       <c r="D87" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F87" t="s">
         <v>17</v>
@@ -2894,13 +2894,13 @@
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B89" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C89">
         <v>853</v>
       </c>
       <c r="D89" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F89" t="s">
         <v>17</v>
@@ -2923,13 +2923,13 @@
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B90" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C90">
         <v>849</v>
       </c>
       <c r="D90" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F90" t="s">
         <v>19</v>
@@ -2952,13 +2952,13 @@
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B91" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C91">
         <v>855</v>
       </c>
       <c r="D91" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -2981,13 +2981,13 @@
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B92" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C92">
         <v>852</v>
       </c>
       <c r="D92" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F92" t="s">
         <v>19</v>
@@ -3010,13 +3010,13 @@
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B93" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C93">
         <v>980</v>
       </c>
       <c r="D93" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F93" t="s">
         <v>19</v>
@@ -3039,13 +3039,13 @@
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B94" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C94">
         <v>851</v>
       </c>
       <c r="D94" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F94" t="s">
         <v>19</v>
@@ -3076,13 +3076,13 @@
     </row>
     <row r="96" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B96" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C96">
         <v>981</v>
       </c>
       <c r="D96" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F96" t="s">
         <v>19</v>
@@ -3105,13 +3105,13 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C97">
         <v>848</v>
       </c>
       <c r="D97" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -3134,13 +3134,13 @@
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B98" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C98">
         <v>854</v>
       </c>
       <c r="D98" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F98" t="s">
         <v>19</v>
@@ -3163,13 +3163,13 @@
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B99" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C99">
         <v>850</v>
       </c>
       <c r="D99" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -3192,13 +3192,13 @@
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C100">
         <v>853</v>
       </c>
       <c r="D100" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F100" t="s">
         <v>19</v>
@@ -3221,13 +3221,13 @@
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B101" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C101">
         <v>849</v>
       </c>
       <c r="D101" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F101" t="s">
         <v>20</v>
@@ -3250,13 +3250,13 @@
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C102">
         <v>855</v>
       </c>
       <c r="D102" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F102" t="s">
         <v>20</v>
@@ -3279,13 +3279,13 @@
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B103" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C103">
         <v>852</v>
       </c>
       <c r="D103" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F103" t="s">
         <v>20</v>
@@ -3308,13 +3308,13 @@
     </row>
     <row r="104" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B104" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C104">
         <v>980</v>
       </c>
       <c r="D104" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F104" t="s">
         <v>20</v>
@@ -3337,13 +3337,13 @@
     </row>
     <row r="105" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B105" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C105">
         <v>851</v>
       </c>
       <c r="D105" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F105" t="s">
         <v>20</v>
@@ -3366,13 +3366,13 @@
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B106" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C106">
         <v>981</v>
       </c>
       <c r="D106" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F106" t="s">
         <v>20</v>
@@ -3395,13 +3395,13 @@
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B107" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C107">
         <v>848</v>
       </c>
       <c r="D107" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F107" t="s">
         <v>20</v>
@@ -3424,13 +3424,13 @@
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B108" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C108">
         <v>854</v>
       </c>
       <c r="D108" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F108" t="s">
         <v>20</v>
@@ -3453,13 +3453,13 @@
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B109" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C109">
         <v>850</v>
       </c>
       <c r="D109" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F109" t="s">
         <v>20</v>
@@ -3482,13 +3482,13 @@
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B110" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C110">
         <v>853</v>
       </c>
       <c r="D110" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F110" t="s">
         <v>20</v>
@@ -3511,13 +3511,13 @@
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B111" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C111">
         <v>849</v>
       </c>
       <c r="D111" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F111" t="s">
         <v>21</v>
@@ -3540,13 +3540,13 @@
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B112" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C112">
         <v>855</v>
       </c>
       <c r="D112" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -3569,13 +3569,13 @@
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B113" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C113">
         <v>852</v>
       </c>
       <c r="D113" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F113" t="s">
         <v>21</v>
@@ -3598,13 +3598,13 @@
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C114">
         <v>980</v>
       </c>
       <c r="D114" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F114" t="s">
         <v>21</v>
@@ -3627,13 +3627,13 @@
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B115" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C115">
         <v>851</v>
       </c>
       <c r="D115" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F115" t="s">
         <v>21</v>
@@ -3656,13 +3656,13 @@
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B116" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C116">
         <v>981</v>
       </c>
       <c r="D116" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F116" t="s">
         <v>21</v>
@@ -3685,13 +3685,13 @@
     </row>
     <row r="117" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B117" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C117">
         <v>848</v>
       </c>
       <c r="D117" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
@@ -3714,13 +3714,13 @@
     </row>
     <row r="118" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B118" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C118">
         <v>854</v>
       </c>
       <c r="D118" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F118" t="s">
         <v>21</v>
@@ -3743,13 +3743,13 @@
     </row>
     <row r="119" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B119" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C119">
         <v>850</v>
       </c>
       <c r="D119" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F119" t="s">
         <v>21</v>
@@ -3772,13 +3772,13 @@
     </row>
     <row r="120" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B120" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C120">
         <v>853</v>
       </c>
       <c r="D120" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F120" t="s">
         <v>21</v>
@@ -3801,13 +3801,13 @@
     </row>
     <row r="121" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B121" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C121">
         <v>849</v>
       </c>
       <c r="D121" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F121" t="s">
         <v>22</v>
@@ -3830,13 +3830,13 @@
     </row>
     <row r="122" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C122">
         <v>855</v>
       </c>
       <c r="D122" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F122" t="s">
         <v>22</v>
@@ -3859,13 +3859,13 @@
     </row>
     <row r="123" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B123" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C123">
         <v>852</v>
       </c>
       <c r="D123" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F123" t="s">
         <v>22</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="124" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C124">
         <v>980</v>
       </c>
       <c r="D124" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F124" t="s">
         <v>22</v>
@@ -3917,13 +3917,13 @@
     </row>
     <row r="125" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B125" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C125">
         <v>851</v>
       </c>
       <c r="D125" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F125" t="s">
         <v>22</v>
@@ -3946,13 +3946,13 @@
     </row>
     <row r="126" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B126" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C126">
         <v>981</v>
       </c>
       <c r="D126" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F126" t="s">
         <v>22</v>
@@ -3975,13 +3975,13 @@
     </row>
     <row r="127" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C127">
         <v>848</v>
       </c>
       <c r="D127" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F127" t="s">
         <v>22</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="128" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B128" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C128">
         <v>854</v>
       </c>
       <c r="D128" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F128" t="s">
         <v>22</v>
@@ -4033,13 +4033,13 @@
     </row>
     <row r="129" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B129" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C129">
         <v>850</v>
       </c>
       <c r="D129" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F129" t="s">
         <v>22</v>
@@ -4062,13 +4062,13 @@
     </row>
     <row r="130" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B130" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C130">
         <v>853</v>
       </c>
       <c r="D130" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F130" t="s">
         <v>22</v>
@@ -4091,16 +4091,16 @@
     </row>
     <row r="131" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B131" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C131">
         <v>849</v>
       </c>
       <c r="D131" t="s">
+        <v>40</v>
+      </c>
+      <c r="F131" t="s">
         <v>38</v>
-      </c>
-      <c r="F131" t="s">
-        <v>35</v>
       </c>
       <c r="G131" t="s">
         <v>13</v>
@@ -4120,16 +4120,16 @@
     </row>
     <row r="132" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B132" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C132">
         <v>855</v>
       </c>
       <c r="D132" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F132" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G132" t="s">
         <v>10</v>
@@ -4149,16 +4149,16 @@
     </row>
     <row r="133" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B133" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C133">
         <v>852</v>
       </c>
       <c r="D133" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F133" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G133" t="s">
         <v>13</v>
@@ -4178,16 +4178,16 @@
     </row>
     <row r="134" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B134" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C134">
         <v>980</v>
       </c>
       <c r="D134" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F134" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G134" t="s">
         <v>10</v>
@@ -4207,16 +4207,16 @@
     </row>
     <row r="135" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B135" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C135">
         <v>851</v>
       </c>
       <c r="D135" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F135" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G135" t="s">
         <v>10</v>
@@ -4236,16 +4236,16 @@
     </row>
     <row r="136" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B136" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C136">
         <v>981</v>
       </c>
       <c r="D136" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F136" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G136" t="s">
         <v>10</v>
@@ -4265,16 +4265,16 @@
     </row>
     <row r="137" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B137" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C137">
         <v>848</v>
       </c>
       <c r="D137" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F137" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G137" t="s">
         <v>13</v>
@@ -4294,16 +4294,16 @@
     </row>
     <row r="138" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B138" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C138">
         <v>854</v>
       </c>
       <c r="D138" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F138" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G138" t="s">
         <v>13</v>
@@ -4323,16 +4323,16 @@
     </row>
     <row r="139" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B139" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C139">
         <v>850</v>
       </c>
       <c r="D139" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F139" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G139" t="s">
         <v>13</v>
@@ -4352,16 +4352,16 @@
     </row>
     <row r="140" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B140" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C140">
         <v>853</v>
       </c>
       <c r="D140" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F140" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G140" t="s">
         <v>13</v>
@@ -4381,13 +4381,13 @@
     </row>
     <row r="141" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B141" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C141">
         <v>849</v>
       </c>
       <c r="D141" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F141" t="s">
         <v>26</v>
@@ -4410,13 +4410,13 @@
     </row>
     <row r="142" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B142" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C142">
         <v>855</v>
       </c>
       <c r="D142" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F142" t="s">
         <v>26</v>
@@ -4439,13 +4439,13 @@
     </row>
     <row r="143" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B143" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C143">
         <v>852</v>
       </c>
       <c r="D143" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F143" t="s">
         <v>26</v>
@@ -4468,13 +4468,13 @@
     </row>
     <row r="144" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B144" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C144">
         <v>980</v>
       </c>
       <c r="D144" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F144" t="s">
         <v>26</v>
@@ -4497,13 +4497,13 @@
     </row>
     <row r="145" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B145" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C145">
         <v>851</v>
       </c>
       <c r="D145" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F145" t="s">
         <v>26</v>
@@ -4526,13 +4526,13 @@
     </row>
     <row r="146" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B146" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C146">
         <v>981</v>
       </c>
       <c r="D146" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F146" t="s">
         <v>26</v>
@@ -4555,13 +4555,13 @@
     </row>
     <row r="147" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B147" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C147">
         <v>848</v>
       </c>
       <c r="D147" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F147" t="s">
         <v>26</v>
@@ -4584,13 +4584,13 @@
     </row>
     <row r="148" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C148">
         <v>854</v>
       </c>
       <c r="D148" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F148" t="s">
         <v>26</v>
@@ -4613,13 +4613,13 @@
     </row>
     <row r="149" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B149" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C149">
         <v>850</v>
       </c>
       <c r="D149" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F149" t="s">
         <v>26</v>
@@ -4642,13 +4642,13 @@
     </row>
     <row r="150" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B150" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C150">
         <v>853</v>
       </c>
       <c r="D150" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F150" t="s">
         <v>26</v>
@@ -4671,13 +4671,13 @@
     </row>
     <row r="151" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B151" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C151">
         <v>849</v>
       </c>
       <c r="D151" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F151" t="s">
         <v>24</v>
@@ -4700,13 +4700,13 @@
     </row>
     <row r="152" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B152" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C152">
         <v>855</v>
       </c>
       <c r="D152" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F152" t="s">
         <v>24</v>
@@ -4729,13 +4729,13 @@
     </row>
     <row r="153" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B153" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C153">
         <v>852</v>
       </c>
       <c r="D153" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F153" t="s">
         <v>24</v>
@@ -4758,13 +4758,13 @@
     </row>
     <row r="154" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B154" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C154">
         <v>980</v>
       </c>
       <c r="D154" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F154" t="s">
         <v>24</v>
@@ -4787,13 +4787,13 @@
     </row>
     <row r="155" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B155" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C155">
         <v>851</v>
       </c>
       <c r="D155" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F155" t="s">
         <v>24</v>
@@ -4816,13 +4816,13 @@
     </row>
     <row r="156" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B156" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C156">
         <v>981</v>
       </c>
       <c r="D156" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F156" t="s">
         <v>24</v>
@@ -4845,13 +4845,13 @@
     </row>
     <row r="157" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B157" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C157">
         <v>848</v>
       </c>
       <c r="D157" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F157" t="s">
         <v>24</v>
@@ -4874,13 +4874,13 @@
     </row>
     <row r="158" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B158" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C158">
         <v>854</v>
       </c>
       <c r="D158" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F158" t="s">
         <v>24</v>
@@ -4903,13 +4903,13 @@
     </row>
     <row r="159" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B159" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C159">
         <v>850</v>
       </c>
       <c r="D159" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F159" t="s">
         <v>24</v>
@@ -4932,13 +4932,13 @@
     </row>
     <row r="160" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B160" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C160">
         <v>853</v>
       </c>
       <c r="D160" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F160" t="s">
         <v>24</v>
@@ -4961,13 +4961,13 @@
     </row>
     <row r="161" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B161" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C161">
         <v>849</v>
       </c>
       <c r="D161" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F161" t="s">
         <v>23</v>
@@ -4990,13 +4990,13 @@
     </row>
     <row r="162" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B162" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C162">
         <v>855</v>
       </c>
       <c r="D162" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F162" t="s">
         <v>23</v>
@@ -5019,13 +5019,13 @@
     </row>
     <row r="163" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B163" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C163">
         <v>852</v>
       </c>
       <c r="D163" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F163" t="s">
         <v>23</v>
@@ -5048,13 +5048,13 @@
     </row>
     <row r="164" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B164" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C164">
         <v>980</v>
       </c>
       <c r="D164" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F164" t="s">
         <v>23</v>
@@ -5077,13 +5077,13 @@
     </row>
     <row r="165" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B165" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C165">
         <v>851</v>
       </c>
       <c r="D165" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F165" t="s">
         <v>23</v>
@@ -5106,13 +5106,13 @@
     </row>
     <row r="166" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B166" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C166">
         <v>981</v>
       </c>
       <c r="D166" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F166" t="s">
         <v>23</v>
@@ -5135,13 +5135,13 @@
     </row>
     <row r="167" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C167">
         <v>848</v>
       </c>
       <c r="D167" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F167" t="s">
         <v>23</v>
@@ -5164,13 +5164,13 @@
     </row>
     <row r="168" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B168" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C168">
         <v>854</v>
       </c>
       <c r="D168" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F168" t="s">
         <v>23</v>
@@ -5193,13 +5193,13 @@
     </row>
     <row r="169" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B169" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C169">
         <v>850</v>
       </c>
       <c r="D169" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F169" t="s">
         <v>23</v>
@@ -5230,13 +5230,13 @@
     </row>
     <row r="171" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B171" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C171">
         <v>853</v>
       </c>
       <c r="D171" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F171" t="s">
         <v>23</v>
@@ -5259,13 +5259,13 @@
     </row>
     <row r="172" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B172" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C172">
         <v>849</v>
       </c>
       <c r="D172" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F172" t="s">
         <v>17</v>
@@ -5288,13 +5288,13 @@
     </row>
     <row r="173" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B173" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C173">
         <v>855</v>
       </c>
       <c r="D173" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F173" t="s">
         <v>17</v>
@@ -5317,13 +5317,13 @@
     </row>
     <row r="174" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B174" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C174">
         <v>852</v>
       </c>
       <c r="D174" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F174" t="s">
         <v>17</v>
@@ -5346,13 +5346,13 @@
     </row>
     <row r="175" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B175" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C175">
         <v>980</v>
       </c>
       <c r="D175" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F175" t="s">
         <v>17</v>
@@ -5375,13 +5375,13 @@
     </row>
     <row r="176" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B176" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C176">
         <v>851</v>
       </c>
       <c r="D176" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F176" t="s">
         <v>17</v>
@@ -5404,13 +5404,13 @@
     </row>
     <row r="177" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B177" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C177">
         <v>981</v>
       </c>
       <c r="D177" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F177" t="s">
         <v>17</v>
@@ -5433,13 +5433,13 @@
     </row>
     <row r="178" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B178" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C178">
         <v>848</v>
       </c>
       <c r="D178" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F178" t="s">
         <v>17</v>
@@ -5462,13 +5462,13 @@
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B179" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C179">
         <v>854</v>
       </c>
       <c r="D179" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F179" t="s">
         <v>17</v>
@@ -5491,13 +5491,13 @@
     </row>
     <row r="180" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B180" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C180">
         <v>850</v>
       </c>
       <c r="D180" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F180" t="s">
         <v>17</v>
@@ -5520,13 +5520,13 @@
     </row>
     <row r="181" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B181" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C181">
         <v>853</v>
       </c>
       <c r="D181" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F181" t="s">
         <v>17</v>
@@ -5549,13 +5549,13 @@
     </row>
     <row r="182" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B182" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C182">
         <v>849</v>
       </c>
       <c r="D182" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F182" t="s">
         <v>18</v>
@@ -5578,13 +5578,13 @@
     </row>
     <row r="183" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B183" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C183">
         <v>855</v>
       </c>
       <c r="D183" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F183" t="s">
         <v>18</v>
@@ -5607,13 +5607,13 @@
     </row>
     <row r="184" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B184" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C184">
         <v>852</v>
       </c>
       <c r="D184" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F184" t="s">
         <v>18</v>
@@ -5636,13 +5636,13 @@
     </row>
     <row r="185" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B185" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C185">
         <v>980</v>
       </c>
       <c r="D185" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F185" t="s">
         <v>18</v>
@@ -5665,13 +5665,13 @@
     </row>
     <row r="186" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B186" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C186">
         <v>851</v>
       </c>
       <c r="D186" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F186" t="s">
         <v>18</v>
@@ -5694,13 +5694,13 @@
     </row>
     <row r="187" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B187" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C187">
         <v>981</v>
       </c>
       <c r="D187" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F187" t="s">
         <v>18</v>
@@ -5723,13 +5723,13 @@
     </row>
     <row r="188" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B188" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C188">
         <v>848</v>
       </c>
       <c r="D188" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F188" t="s">
         <v>18</v>
@@ -5752,13 +5752,13 @@
     </row>
     <row r="189" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B189" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C189">
         <v>854</v>
       </c>
       <c r="D189" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F189" t="s">
         <v>18</v>
@@ -5781,13 +5781,13 @@
     </row>
     <row r="190" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B190" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C190">
         <v>850</v>
       </c>
       <c r="D190" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F190" t="s">
         <v>18</v>
@@ -5810,13 +5810,13 @@
     </row>
     <row r="191" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B191" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C191">
         <v>853</v>
       </c>
       <c r="D191" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F191" t="s">
         <v>18</v>
@@ -5839,13 +5839,13 @@
     </row>
     <row r="192" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B192" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C192">
         <v>849</v>
       </c>
       <c r="D192" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F192" t="s">
         <v>34</v>
@@ -5868,13 +5868,13 @@
     </row>
     <row r="193" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B193" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C193">
         <v>855</v>
       </c>
       <c r="D193" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F193" t="s">
         <v>34</v>
@@ -5897,13 +5897,13 @@
     </row>
     <row r="194" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B194" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C194">
         <v>852</v>
       </c>
       <c r="D194" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F194" t="s">
         <v>34</v>
@@ -5926,13 +5926,13 @@
     </row>
     <row r="195" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B195" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C195">
         <v>980</v>
       </c>
       <c r="D195" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F195" t="s">
         <v>34</v>
@@ -5955,13 +5955,13 @@
     </row>
     <row r="196" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B196" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C196">
         <v>851</v>
       </c>
       <c r="D196" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F196" t="s">
         <v>34</v>
@@ -5984,13 +5984,13 @@
     </row>
     <row r="197" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B197" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C197">
         <v>981</v>
       </c>
       <c r="D197" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F197" t="s">
         <v>34</v>
@@ -6013,13 +6013,13 @@
     </row>
     <row r="198" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B198" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C198">
         <v>848</v>
       </c>
       <c r="D198" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F198" t="s">
         <v>34</v>
@@ -6042,13 +6042,13 @@
     </row>
     <row r="199" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B199" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C199">
         <v>854</v>
       </c>
       <c r="D199" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F199" t="s">
         <v>34</v>
@@ -6071,13 +6071,13 @@
     </row>
     <row r="200" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B200" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C200">
         <v>850</v>
       </c>
       <c r="D200" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F200" t="s">
         <v>34</v>
@@ -6100,13 +6100,13 @@
     </row>
     <row r="201" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B201" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C201">
         <v>853</v>
       </c>
       <c r="D201" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F201" t="s">
         <v>34</v>
@@ -6129,13 +6129,13 @@
     </row>
     <row r="202" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B202" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C202">
         <v>849</v>
       </c>
       <c r="D202" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F202" t="s">
         <v>34</v>
@@ -6158,13 +6158,13 @@
     </row>
     <row r="203" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B203" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C203">
         <v>855</v>
       </c>
       <c r="D203" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F203" t="s">
         <v>34</v>
@@ -6187,13 +6187,13 @@
     </row>
     <row r="204" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B204" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C204">
         <v>852</v>
       </c>
       <c r="D204" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F204" t="s">
         <v>34</v>
@@ -6216,13 +6216,13 @@
     </row>
     <row r="205" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B205" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C205">
         <v>980</v>
       </c>
       <c r="D205" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F205" t="s">
         <v>34</v>
@@ -6245,13 +6245,13 @@
     </row>
     <row r="206" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B206" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C206">
         <v>851</v>
       </c>
       <c r="D206" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F206" t="s">
         <v>34</v>
@@ -6274,13 +6274,13 @@
     </row>
     <row r="207" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B207" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C207">
         <v>981</v>
       </c>
       <c r="D207" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F207" t="s">
         <v>34</v>
@@ -6303,13 +6303,13 @@
     </row>
     <row r="208" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B208" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C208">
         <v>848</v>
       </c>
       <c r="D208" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F208" t="s">
         <v>34</v>
@@ -6332,13 +6332,13 @@
     </row>
     <row r="209" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B209" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C209">
         <v>854</v>
       </c>
       <c r="D209" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F209" t="s">
         <v>34</v>
@@ -6361,13 +6361,13 @@
     </row>
     <row r="210" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B210" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C210">
         <v>850</v>
       </c>
       <c r="D210" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F210" t="s">
         <v>34</v>
@@ -6390,13 +6390,13 @@
     </row>
     <row r="211" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B211" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C211">
         <v>853</v>
       </c>
       <c r="D211" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F211" t="s">
         <v>34</v>
@@ -6419,13 +6419,13 @@
     </row>
     <row r="212" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B212" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C212">
         <v>849</v>
       </c>
       <c r="D212" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F212" t="s">
         <v>25</v>
@@ -6448,13 +6448,13 @@
     </row>
     <row r="213" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B213" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C213">
         <v>855</v>
       </c>
       <c r="D213" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F213" t="s">
         <v>25</v>
@@ -6477,13 +6477,13 @@
     </row>
     <row r="214" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B214" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C214">
         <v>852</v>
       </c>
       <c r="D214" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F214" t="s">
         <v>25</v>
@@ -6506,13 +6506,13 @@
     </row>
     <row r="215" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B215" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C215">
         <v>980</v>
       </c>
       <c r="D215" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F215" t="s">
         <v>25</v>
@@ -6535,13 +6535,13 @@
     </row>
     <row r="216" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B216" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C216">
         <v>851</v>
       </c>
       <c r="D216" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F216" t="s">
         <v>25</v>
@@ -6564,13 +6564,13 @@
     </row>
     <row r="217" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B217" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C217">
         <v>848</v>
       </c>
       <c r="D217" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F217" t="s">
         <v>25</v>
@@ -6593,13 +6593,13 @@
     </row>
     <row r="218" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B218" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C218">
         <v>854</v>
       </c>
       <c r="D218" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F218" t="s">
         <v>25</v>
@@ -6622,13 +6622,13 @@
     </row>
     <row r="219" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B219" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C219">
         <v>850</v>
       </c>
       <c r="D219" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F219" t="s">
         <v>25</v>
@@ -6651,13 +6651,13 @@
     </row>
     <row r="220" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B220" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C220">
         <v>853</v>
       </c>
       <c r="D220" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F220" t="s">
         <v>25</v>
@@ -6680,16 +6680,16 @@
     </row>
     <row r="221" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B221" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C221">
         <v>849</v>
       </c>
       <c r="D221" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F221" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G221" t="s">
         <v>13</v>
@@ -6709,16 +6709,16 @@
     </row>
     <row r="222" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B222" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C222">
         <v>855</v>
       </c>
       <c r="D222" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F222" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G222" t="s">
         <v>13</v>
@@ -6738,16 +6738,16 @@
     </row>
     <row r="223" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B223" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C223">
         <v>852</v>
       </c>
       <c r="D223" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F223" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G223" t="s">
         <v>13</v>
@@ -6767,16 +6767,16 @@
     </row>
     <row r="224" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B224" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C224">
         <v>980</v>
       </c>
       <c r="D224" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F224" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G224" t="s">
         <v>10</v>
@@ -6796,16 +6796,16 @@
     </row>
     <row r="225" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B225" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C225">
         <v>851</v>
       </c>
       <c r="D225" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F225" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G225" t="s">
         <v>13</v>
@@ -6825,16 +6825,16 @@
     </row>
     <row r="226" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B226" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C226">
         <v>848</v>
       </c>
       <c r="D226" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F226" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G226" t="s">
         <v>13</v>
@@ -6854,16 +6854,16 @@
     </row>
     <row r="227" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B227" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C227">
         <v>854</v>
       </c>
       <c r="D227" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F227" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G227" t="s">
         <v>13</v>
@@ -6883,16 +6883,16 @@
     </row>
     <row r="228" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B228" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C228">
         <v>850</v>
       </c>
       <c r="D228" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F228" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G228" t="s">
         <v>13</v>
@@ -6912,16 +6912,16 @@
     </row>
     <row r="229" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B229" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C229">
         <v>853</v>
       </c>
       <c r="D229" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F229" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G229" t="s">
         <v>13</v>
@@ -6941,13 +6941,13 @@
     </row>
     <row r="230" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B230" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C230">
         <v>849</v>
       </c>
       <c r="D230" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F230" t="s">
         <v>19</v>
@@ -6970,13 +6970,13 @@
     </row>
     <row r="231" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B231" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C231">
         <v>855</v>
       </c>
       <c r="D231" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F231" t="s">
         <v>19</v>
@@ -6999,13 +6999,13 @@
     </row>
     <row r="232" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B232" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C232">
         <v>852</v>
       </c>
       <c r="D232" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F232" t="s">
         <v>19</v>
@@ -7028,13 +7028,13 @@
     </row>
     <row r="233" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B233" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C233">
         <v>980</v>
       </c>
       <c r="D233" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F233" t="s">
         <v>19</v>
@@ -7057,13 +7057,13 @@
     </row>
     <row r="234" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B234" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C234">
         <v>851</v>
       </c>
       <c r="D234" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F234" t="s">
         <v>19</v>
@@ -7086,13 +7086,13 @@
     </row>
     <row r="235" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B235" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C235">
         <v>848</v>
       </c>
       <c r="D235" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F235" t="s">
         <v>19</v>
@@ -7115,13 +7115,13 @@
     </row>
     <row r="236" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B236" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C236">
         <v>854</v>
       </c>
       <c r="D236" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F236" t="s">
         <v>19</v>
@@ -7144,13 +7144,13 @@
     </row>
     <row r="237" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B237" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C237">
         <v>850</v>
       </c>
       <c r="D237" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F237" t="s">
         <v>19</v>
@@ -7173,13 +7173,13 @@
     </row>
     <row r="238" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B238" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C238">
         <v>853</v>
       </c>
       <c r="D238" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F238" t="s">
         <v>19</v>
@@ -7202,13 +7202,13 @@
     </row>
     <row r="239" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B239" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C239">
         <v>849</v>
       </c>
       <c r="D239" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F239" t="s">
         <v>20</v>
@@ -7231,13 +7231,13 @@
     </row>
     <row r="240" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B240" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C240">
         <v>855</v>
       </c>
       <c r="D240" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F240" t="s">
         <v>20</v>
@@ -7260,13 +7260,13 @@
     </row>
     <row r="241" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B241" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C241">
         <v>852</v>
       </c>
       <c r="D241" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F241" t="s">
         <v>20</v>
@@ -7289,13 +7289,13 @@
     </row>
     <row r="242" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B242" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C242">
         <v>980</v>
       </c>
       <c r="D242" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F242" t="s">
         <v>20</v>
@@ -7318,13 +7318,13 @@
     </row>
     <row r="243" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B243" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C243">
         <v>851</v>
       </c>
       <c r="D243" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F243" t="s">
         <v>20</v>
@@ -7347,13 +7347,13 @@
     </row>
     <row r="244" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B244" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C244">
         <v>848</v>
       </c>
       <c r="D244" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F244" t="s">
         <v>20</v>
@@ -7376,13 +7376,13 @@
     </row>
     <row r="245" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B245" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C245">
         <v>854</v>
       </c>
       <c r="D245" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F245" t="s">
         <v>20</v>
@@ -7405,13 +7405,13 @@
     </row>
     <row r="246" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B246" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C246">
         <v>850</v>
       </c>
       <c r="D246" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F246" t="s">
         <v>20</v>
@@ -7434,13 +7434,13 @@
     </row>
     <row r="247" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B247" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C247">
         <v>853</v>
       </c>
       <c r="D247" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F247" t="s">
         <v>20</v>
@@ -7463,13 +7463,13 @@
     </row>
     <row r="248" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B248" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C248">
         <v>849</v>
       </c>
       <c r="D248" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F248" t="s">
         <v>27</v>
@@ -7492,13 +7492,13 @@
     </row>
     <row r="249" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B249" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C249">
         <v>855</v>
       </c>
       <c r="D249" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F249" t="s">
         <v>27</v>
@@ -7521,13 +7521,13 @@
     </row>
     <row r="250" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B250" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C250">
         <v>852</v>
       </c>
       <c r="D250" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F250" t="s">
         <v>27</v>
@@ -7550,13 +7550,13 @@
     </row>
     <row r="251" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B251" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C251">
         <v>980</v>
       </c>
       <c r="D251" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F251" t="s">
         <v>27</v>
@@ -7579,13 +7579,13 @@
     </row>
     <row r="252" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B252" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C252">
         <v>851</v>
       </c>
       <c r="D252" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F252" t="s">
         <v>27</v>
@@ -7608,13 +7608,13 @@
     </row>
     <row r="253" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B253" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C253">
         <v>848</v>
       </c>
       <c r="D253" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F253" t="s">
         <v>27</v>
@@ -7637,13 +7637,13 @@
     </row>
     <row r="254" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B254" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C254">
         <v>854</v>
       </c>
       <c r="D254" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F254" t="s">
         <v>27</v>
@@ -7666,13 +7666,13 @@
     </row>
     <row r="255" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B255" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C255">
         <v>850</v>
       </c>
       <c r="D255" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F255" t="s">
         <v>27</v>
@@ -7703,13 +7703,13 @@
     </row>
     <row r="257" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B257" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C257">
         <v>853</v>
       </c>
       <c r="D257" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F257" t="s">
         <v>27</v>
@@ -7732,13 +7732,13 @@
     </row>
     <row r="258" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B258" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C258">
         <v>849</v>
       </c>
       <c r="D258" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F258" t="s">
         <v>28</v>
@@ -7761,13 +7761,13 @@
     </row>
     <row r="259" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B259" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C259">
         <v>855</v>
       </c>
       <c r="D259" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F259" t="s">
         <v>28</v>
@@ -7790,13 +7790,13 @@
     </row>
     <row r="260" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B260" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C260">
         <v>852</v>
       </c>
       <c r="D260" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F260" t="s">
         <v>28</v>
@@ -7819,13 +7819,13 @@
     </row>
     <row r="261" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B261" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C261">
         <v>980</v>
       </c>
       <c r="D261" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F261" t="s">
         <v>28</v>
@@ -7848,13 +7848,13 @@
     </row>
     <row r="262" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C262">
         <v>851</v>
       </c>
       <c r="D262" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F262" t="s">
         <v>28</v>
@@ -7877,13 +7877,13 @@
     </row>
     <row r="263" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B263" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C263">
         <v>848</v>
       </c>
       <c r="D263" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F263" t="s">
         <v>28</v>
@@ -7906,13 +7906,13 @@
     </row>
     <row r="264" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B264" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C264">
         <v>854</v>
       </c>
       <c r="D264" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F264" t="s">
         <v>28</v>
@@ -7935,13 +7935,13 @@
     </row>
     <row r="265" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B265" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C265">
         <v>850</v>
       </c>
       <c r="D265" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F265" t="s">
         <v>28</v>
@@ -7964,13 +7964,13 @@
     </row>
     <row r="266" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B266" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C266">
         <v>853</v>
       </c>
       <c r="D266" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F266" t="s">
         <v>28</v>
@@ -7993,13 +7993,13 @@
     </row>
     <row r="267" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B267" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C267">
         <v>849</v>
       </c>
       <c r="D267" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F267" t="s">
         <v>29</v>
@@ -8022,13 +8022,13 @@
     </row>
     <row r="268" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B268" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C268">
         <v>855</v>
       </c>
       <c r="D268" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F268" t="s">
         <v>29</v>
@@ -8051,13 +8051,13 @@
     </row>
     <row r="269" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B269" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C269">
         <v>852</v>
       </c>
       <c r="D269" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F269" t="s">
         <v>29</v>
@@ -8080,13 +8080,13 @@
     </row>
     <row r="270" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B270" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C270">
         <v>980</v>
       </c>
       <c r="D270" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F270" t="s">
         <v>29</v>
@@ -8109,13 +8109,13 @@
     </row>
     <row r="271" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B271" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C271">
         <v>851</v>
       </c>
       <c r="D271" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F271" t="s">
         <v>29</v>
@@ -8138,13 +8138,13 @@
     </row>
     <row r="272" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B272" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C272">
         <v>848</v>
       </c>
       <c r="D272" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F272" t="s">
         <v>29</v>
@@ -8167,13 +8167,13 @@
     </row>
     <row r="273" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B273" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C273">
         <v>854</v>
       </c>
       <c r="D273" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F273" t="s">
         <v>29</v>
@@ -8196,13 +8196,13 @@
     </row>
     <row r="274" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B274" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C274">
         <v>850</v>
       </c>
       <c r="D274" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F274" t="s">
         <v>29</v>
@@ -8225,13 +8225,13 @@
     </row>
     <row r="275" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B275" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C275">
         <v>853</v>
       </c>
       <c r="D275" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F275" t="s">
         <v>29</v>
@@ -8254,13 +8254,13 @@
     </row>
     <row r="276" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B276" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C276">
         <v>849</v>
       </c>
       <c r="D276" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F276" t="s">
         <v>30</v>
@@ -8283,13 +8283,13 @@
     </row>
     <row r="277" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B277" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C277">
         <v>852</v>
       </c>
       <c r="D277" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F277" t="s">
         <v>30</v>
@@ -8312,13 +8312,13 @@
     </row>
     <row r="278" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B278" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C278">
         <v>980</v>
       </c>
       <c r="D278" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F278" t="s">
         <v>30</v>
@@ -8341,13 +8341,13 @@
     </row>
     <row r="279" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B279" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C279">
         <v>851</v>
       </c>
       <c r="D279" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F279" t="s">
         <v>30</v>
@@ -8370,13 +8370,13 @@
     </row>
     <row r="280" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B280" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C280">
         <v>848</v>
       </c>
       <c r="D280" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F280" t="s">
         <v>30</v>
@@ -8399,13 +8399,13 @@
     </row>
     <row r="281" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B281" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C281">
         <v>854</v>
       </c>
       <c r="D281" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F281" t="s">
         <v>30</v>
@@ -8428,13 +8428,13 @@
     </row>
     <row r="282" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B282" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C282">
         <v>850</v>
       </c>
       <c r="D282" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F282" t="s">
         <v>30</v>
@@ -8457,13 +8457,13 @@
     </row>
     <row r="283" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B283" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C283">
         <v>849</v>
       </c>
       <c r="D283" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F283" t="s">
         <v>21</v>
@@ -8486,13 +8486,13 @@
     </row>
     <row r="284" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C284">
         <v>852</v>
       </c>
       <c r="D284" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F284" t="s">
         <v>21</v>
@@ -8515,13 +8515,13 @@
     </row>
     <row r="285" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B285" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C285">
         <v>980</v>
       </c>
       <c r="D285" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F285" t="s">
         <v>21</v>
@@ -8544,13 +8544,13 @@
     </row>
     <row r="286" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B286" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C286">
         <v>848</v>
       </c>
       <c r="D286" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F286" t="s">
         <v>21</v>
@@ -8573,13 +8573,13 @@
     </row>
     <row r="287" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B287" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C287">
         <v>854</v>
       </c>
       <c r="D287" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F287" t="s">
         <v>21</v>
@@ -8602,13 +8602,13 @@
     </row>
     <row r="288" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B288" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C288">
         <v>850</v>
       </c>
       <c r="D288" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F288" t="s">
         <v>21</v>
@@ -8631,13 +8631,13 @@
     </row>
     <row r="289" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B289" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C289">
         <v>849</v>
       </c>
       <c r="D289" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F289" t="s">
         <v>31</v>
@@ -8660,13 +8660,13 @@
     </row>
     <row r="290" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B290" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C290">
         <v>852</v>
       </c>
       <c r="D290" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F290" t="s">
         <v>31</v>
@@ -8689,13 +8689,13 @@
     </row>
     <row r="291" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C291">
         <v>980</v>
       </c>
       <c r="D291" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F291" t="s">
         <v>31</v>
@@ -8718,13 +8718,13 @@
     </row>
     <row r="292" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B292" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C292">
         <v>848</v>
       </c>
       <c r="D292" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F292" t="s">
         <v>31</v>
@@ -8747,13 +8747,13 @@
     </row>
     <row r="293" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B293" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C293">
         <v>854</v>
       </c>
       <c r="D293" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F293" t="s">
         <v>31</v>
@@ -8776,13 +8776,13 @@
     </row>
     <row r="294" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B294" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C294">
         <v>850</v>
       </c>
       <c r="D294" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F294" t="s">
         <v>31</v>
@@ -8805,13 +8805,13 @@
     </row>
     <row r="295" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B295" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C295">
         <v>849</v>
       </c>
       <c r="D295" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F295" t="s">
         <v>23</v>
@@ -8834,13 +8834,13 @@
     </row>
     <row r="296" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B296" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C296">
         <v>852</v>
       </c>
       <c r="D296" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F296" t="s">
         <v>23</v>
@@ -8863,13 +8863,13 @@
     </row>
     <row r="297" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B297" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C297">
         <v>980</v>
       </c>
       <c r="D297" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F297" t="s">
         <v>23</v>
@@ -8892,13 +8892,13 @@
     </row>
     <row r="298" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B298" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C298">
         <v>848</v>
       </c>
       <c r="D298" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F298" t="s">
         <v>23</v>
@@ -8921,13 +8921,13 @@
     </row>
     <row r="299" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B299" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C299">
         <v>854</v>
       </c>
       <c r="D299" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F299" t="s">
         <v>23</v>
@@ -8950,13 +8950,13 @@
     </row>
     <row r="300" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B300" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C300">
         <v>850</v>
       </c>
       <c r="D300" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F300" t="s">
         <v>23</v>
@@ -8979,13 +8979,13 @@
     </row>
     <row r="301" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B301" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C301">
         <v>849</v>
       </c>
       <c r="D301" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F301" t="s">
         <v>32</v>
@@ -9008,13 +9008,13 @@
     </row>
     <row r="302" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B302" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C302">
         <v>852</v>
       </c>
       <c r="D302" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F302" t="s">
         <v>32</v>
@@ -9037,13 +9037,13 @@
     </row>
     <row r="303" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B303" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C303">
         <v>980</v>
       </c>
       <c r="D303" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F303" t="s">
         <v>32</v>
@@ -9066,13 +9066,13 @@
     </row>
     <row r="304" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B304" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C304">
         <v>848</v>
       </c>
       <c r="D304" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F304" t="s">
         <v>32</v>
@@ -9095,13 +9095,13 @@
     </row>
     <row r="305" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B305" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C305">
         <v>854</v>
       </c>
       <c r="D305" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F305" t="s">
         <v>32</v>
@@ -9124,13 +9124,13 @@
     </row>
     <row r="306" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B306" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C306">
         <v>850</v>
       </c>
       <c r="D306" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F306" t="s">
         <v>32</v>
@@ -9153,13 +9153,13 @@
     </row>
     <row r="307" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B307" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C307">
         <v>849</v>
       </c>
       <c r="D307" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F307" t="s">
         <v>32</v>
@@ -9182,13 +9182,13 @@
     </row>
     <row r="308" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B308" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C308">
         <v>852</v>
       </c>
       <c r="D308" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F308" t="s">
         <v>32</v>
@@ -9211,13 +9211,13 @@
     </row>
     <row r="309" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B309" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C309">
         <v>980</v>
       </c>
       <c r="D309" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F309" t="s">
         <v>32</v>
@@ -9240,13 +9240,13 @@
     </row>
     <row r="310" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B310" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C310">
         <v>848</v>
       </c>
       <c r="D310" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F310" t="s">
         <v>32</v>
@@ -9269,13 +9269,13 @@
     </row>
     <row r="311" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B311" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C311">
         <v>854</v>
       </c>
       <c r="D311" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F311" t="s">
         <v>32</v>
@@ -9298,13 +9298,13 @@
     </row>
     <row r="312" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B312" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C312">
         <v>850</v>
       </c>
       <c r="D312" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F312" t="s">
         <v>32</v>
@@ -48692,6 +48692,7 @@
       <c r="K7005" s="1"/>
     </row>
     <row r="7006" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7006" s="2"/>
       <c r="I7006" s="1"/>
       <c r="K7006" s="1"/>
     </row>
@@ -48984,6 +48985,8 @@
       <c r="K7054" s="1"/>
     </row>
     <row r="7055" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7055" s="2"/>
+      <c r="I7055" s="1"/>
       <c r="J7055" s="2"/>
       <c r="K7055" s="1"/>
     </row>
@@ -49294,6 +49297,7 @@
       <c r="K7106" s="1"/>
     </row>
     <row r="7107" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7107" s="2"/>
       <c r="I7107" s="1"/>
       <c r="K7107" s="1"/>
     </row>
@@ -49418,6 +49422,7 @@
       <c r="K7127" s="1"/>
     </row>
     <row r="7128" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7128" s="2"/>
       <c r="I7128" s="1"/>
       <c r="J7128" s="2"/>
       <c r="K7128" s="1"/>
@@ -49429,6 +49434,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7130" s="2"/>
       <c r="I7130" s="1"/>
       <c r="K7130" s="1"/>
     </row>
@@ -49577,29 +49583,35 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7155" s="2"/>
       <c r="I7155" s="1"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7156" s="2"/>
       <c r="I7156" s="1"/>
       <c r="J7156" s="2"/>
       <c r="K7156" s="1"/>
     </row>
     <row r="7157" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7157" s="2"/>
       <c r="I7157" s="1"/>
       <c r="K7157" s="1"/>
     </row>
     <row r="7158" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7158" s="2"/>
       <c r="I7158" s="1"/>
       <c r="J7158" s="2"/>
       <c r="K7158" s="1"/>
     </row>
     <row r="7159" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7159" s="2"/>
       <c r="I7159" s="1"/>
       <c r="J7159" s="2"/>
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7160" s="2"/>
       <c r="I7160" s="1"/>
       <c r="K7160" s="1"/>
     </row>
@@ -49610,35 +49622,44 @@
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7162" s="2"/>
+      <c r="I7162" s="1"/>
       <c r="J7162" s="2"/>
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7163" s="2"/>
       <c r="I7163" s="1"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7164" s="2"/>
       <c r="I7164" s="1"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7165" s="2"/>
       <c r="I7165" s="1"/>
       <c r="J7165" s="2"/>
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7166" s="2"/>
       <c r="I7166" s="1"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7167" s="2"/>
       <c r="I7167" s="1"/>
       <c r="K7167" s="1"/>
     </row>
     <row r="7168" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7168" s="2"/>
       <c r="I7168" s="1"/>
       <c r="K7168" s="1"/>
     </row>
     <row r="7169" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7169" s="2"/>
       <c r="I7169" s="1"/>
       <c r="K7169" s="1"/>
     </row>
@@ -49649,30 +49670,37 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7171" s="2"/>
       <c r="I7171" s="1"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7172" s="2"/>
       <c r="I7172" s="1"/>
       <c r="K7172" s="1"/>
     </row>
     <row r="7173" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7173" s="2"/>
       <c r="I7173" s="1"/>
       <c r="K7173" s="1"/>
     </row>
     <row r="7174" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7174" s="2"/>
       <c r="I7174" s="1"/>
       <c r="K7174" s="1"/>
     </row>
     <row r="7175" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7175" s="2"/>
       <c r="I7175" s="1"/>
       <c r="K7175" s="1"/>
     </row>
     <row r="7176" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7176" s="2"/>
       <c r="I7176" s="1"/>
       <c r="K7176" s="1"/>
     </row>
     <row r="7177" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7177" s="2"/>
       <c r="I7177" s="1"/>
       <c r="K7177" s="1"/>
     </row>
@@ -49683,42 +49711,52 @@
       <c r="K7178" s="1"/>
     </row>
     <row r="7179" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7179" s="2"/>
       <c r="I7179" s="1"/>
       <c r="K7179" s="1"/>
     </row>
     <row r="7180" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7180" s="2"/>
       <c r="I7180" s="1"/>
       <c r="K7180" s="1"/>
     </row>
     <row r="7181" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7181" s="2"/>
       <c r="I7181" s="1"/>
       <c r="K7181" s="1"/>
     </row>
     <row r="7182" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7182" s="2"/>
       <c r="I7182" s="1"/>
       <c r="K7182" s="1"/>
     </row>
     <row r="7183" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7183" s="2"/>
       <c r="I7183" s="1"/>
       <c r="K7183" s="1"/>
     </row>
     <row r="7184" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7184" s="2"/>
       <c r="I7184" s="1"/>
       <c r="K7184" s="1"/>
     </row>
     <row r="7185" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7185" s="2"/>
       <c r="I7185" s="1"/>
       <c r="K7185" s="1"/>
     </row>
     <row r="7186" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7186" s="2"/>
       <c r="I7186" s="1"/>
       <c r="K7186" s="1"/>
     </row>
     <row r="7187" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7187" s="2"/>
       <c r="I7187" s="1"/>
       <c r="K7187" s="1"/>
     </row>
     <row r="7188" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7188" s="2"/>
       <c r="I7188" s="1"/>
       <c r="K7188" s="1"/>
     </row>
@@ -49729,14 +49767,17 @@
       <c r="K7189" s="1"/>
     </row>
     <row r="7190" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7190" s="2"/>
       <c r="I7190" s="1"/>
       <c r="K7190" s="1"/>
     </row>
     <row r="7191" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7191" s="2"/>
       <c r="I7191" s="1"/>
       <c r="K7191" s="1"/>
     </row>
     <row r="7192" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7192" s="2"/>
       <c r="I7192" s="1"/>
       <c r="K7192" s="1"/>
     </row>
@@ -49747,26 +49788,32 @@
       <c r="K7193" s="1"/>
     </row>
     <row r="7194" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7194" s="2"/>
       <c r="I7194" s="1"/>
       <c r="K7194" s="1"/>
     </row>
     <row r="7195" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7195" s="2"/>
       <c r="I7195" s="1"/>
       <c r="K7195" s="1"/>
     </row>
     <row r="7196" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7196" s="2"/>
       <c r="I7196" s="1"/>
       <c r="K7196" s="1"/>
     </row>
     <row r="7197" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7197" s="2"/>
       <c r="I7197" s="1"/>
       <c r="K7197" s="1"/>
     </row>
     <row r="7198" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7198" s="2"/>
       <c r="I7198" s="1"/>
       <c r="K7198" s="1"/>
     </row>
     <row r="7199" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7199" s="2"/>
       <c r="I7199" s="1"/>
       <c r="K7199" s="1"/>
     </row>
@@ -49776,86 +49823,107 @@
       <c r="J7200" s="2"/>
       <c r="K7200" s="1"/>
     </row>
-    <row r="7201" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7201" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7201" s="2"/>
       <c r="I7201" s="1"/>
     </row>
-    <row r="7202" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7202" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7202" s="2"/>
       <c r="I7202" s="1"/>
       <c r="K7202" s="1"/>
     </row>
-    <row r="7203" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7203" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7203" s="2"/>
       <c r="I7203" s="1"/>
       <c r="K7203" s="1"/>
     </row>
-    <row r="7204" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7204" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7204" s="2"/>
       <c r="I7204" s="1"/>
       <c r="K7204" s="1"/>
     </row>
-    <row r="7205" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7205" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7205" s="2"/>
       <c r="I7205" s="1"/>
       <c r="K7205" s="1"/>
     </row>
-    <row r="7206" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7206" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7206" s="2"/>
       <c r="I7206" s="1"/>
       <c r="K7206" s="1"/>
     </row>
-    <row r="7207" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7207" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7207" s="2"/>
       <c r="I7207" s="1"/>
       <c r="K7207" s="1"/>
     </row>
-    <row r="7208" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7208" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7208" s="2"/>
       <c r="I7208" s="1"/>
       <c r="K7208" s="1"/>
     </row>
-    <row r="7209" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7209" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7209" s="2"/>
       <c r="I7209" s="1"/>
       <c r="K7209" s="1"/>
     </row>
-    <row r="7210" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7210" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7210" s="2"/>
       <c r="I7210" s="1"/>
       <c r="K7210" s="1"/>
     </row>
-    <row r="7211" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7211" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7211" s="2"/>
       <c r="I7211" s="1"/>
       <c r="K7211" s="1"/>
     </row>
-    <row r="7212" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7212" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7212" s="2"/>
       <c r="I7212" s="1"/>
       <c r="K7212" s="1"/>
     </row>
-    <row r="7213" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7213" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7213" s="2"/>
       <c r="I7213" s="1"/>
       <c r="K7213" s="1"/>
     </row>
-    <row r="7214" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7214" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7214" s="2"/>
       <c r="I7214" s="1"/>
       <c r="K7214" s="1"/>
     </row>
-    <row r="7215" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7215" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7215" s="2"/>
       <c r="I7215" s="1"/>
       <c r="K7215" s="1"/>
     </row>
-    <row r="7216" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7216" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7216" s="2"/>
       <c r="I7216" s="1"/>
       <c r="K7216" s="1"/>
     </row>
     <row r="7217" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7217" s="2"/>
       <c r="I7217" s="1"/>
       <c r="K7217" s="1"/>
     </row>
     <row r="7218" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7218" s="2"/>
       <c r="I7218" s="1"/>
       <c r="K7218" s="1"/>
     </row>
     <row r="7219" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7219" s="2"/>
       <c r="I7219" s="1"/>
       <c r="K7219" s="1"/>
     </row>
     <row r="7220" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7220" s="2"/>
       <c r="I7220" s="1"/>
       <c r="K7220" s="1"/>
     </row>
     <row r="7221" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7221" s="2"/>
       <c r="I7221" s="1"/>
       <c r="K7221" s="1"/>
     </row>
@@ -49865,6 +49933,7 @@
       <c r="K7222" s="1"/>
     </row>
     <row r="7223" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7223" s="2"/>
       <c r="I7223" s="1"/>
       <c r="J7223" s="2"/>
       <c r="K7223" s="1"/>
@@ -49875,101 +49944,127 @@
       <c r="K7224" s="1"/>
     </row>
     <row r="7225" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7225" s="2"/>
+      <c r="I7225" s="1"/>
       <c r="J7225" s="2"/>
       <c r="K7225" s="1"/>
     </row>
     <row r="7226" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7226" s="2"/>
       <c r="I7226" s="1"/>
     </row>
     <row r="7227" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7227" s="2"/>
       <c r="I7227" s="1"/>
       <c r="K7227" s="1"/>
     </row>
     <row r="7228" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7228" s="2"/>
       <c r="I7228" s="1"/>
       <c r="K7228" s="1"/>
     </row>
     <row r="7229" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7229" s="2"/>
       <c r="I7229" s="1"/>
       <c r="K7229" s="1"/>
     </row>
     <row r="7230" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7230" s="2"/>
       <c r="I7230" s="1"/>
       <c r="K7230" s="1"/>
     </row>
     <row r="7231" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7231" s="2"/>
       <c r="I7231" s="1"/>
       <c r="K7231" s="1"/>
     </row>
     <row r="7232" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7232" s="2"/>
       <c r="I7232" s="1"/>
       <c r="K7232" s="1"/>
     </row>
-    <row r="7233" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7233" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7233" s="2"/>
       <c r="I7233" s="1"/>
       <c r="K7233" s="1"/>
     </row>
-    <row r="7234" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7234" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7234" s="2"/>
       <c r="I7234" s="1"/>
       <c r="K7234" s="1"/>
     </row>
-    <row r="7235" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7235" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7235" s="2"/>
       <c r="I7235" s="1"/>
       <c r="K7235" s="1"/>
     </row>
-    <row r="7236" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7236" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7236" s="2"/>
       <c r="I7236" s="1"/>
       <c r="K7236" s="1"/>
     </row>
-    <row r="7237" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7237" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7237" s="2"/>
       <c r="I7237" s="1"/>
       <c r="K7237" s="1"/>
     </row>
-    <row r="7238" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7238" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7238" s="2"/>
       <c r="I7238" s="1"/>
       <c r="K7238" s="1"/>
     </row>
-    <row r="7239" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7239" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7239" s="2"/>
       <c r="I7239" s="1"/>
       <c r="K7239" s="1"/>
     </row>
-    <row r="7240" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7240" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7240" s="2"/>
       <c r="I7240" s="1"/>
       <c r="K7240" s="1"/>
     </row>
-    <row r="7241" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7241" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7241" s="2"/>
       <c r="I7241" s="1"/>
       <c r="K7241" s="1"/>
     </row>
-    <row r="7242" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7242" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7242" s="2"/>
       <c r="I7242" s="1"/>
       <c r="K7242" s="1"/>
     </row>
-    <row r="7243" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7243" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7243" s="2"/>
       <c r="I7243" s="1"/>
       <c r="K7243" s="1"/>
     </row>
-    <row r="7244" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7244" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7244" s="2"/>
       <c r="I7244" s="1"/>
       <c r="K7244" s="1"/>
     </row>
-    <row r="7245" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7245" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7245" s="2"/>
       <c r="I7245" s="1"/>
       <c r="K7245" s="1"/>
     </row>
-    <row r="7246" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7246" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7246" s="2"/>
       <c r="I7246" s="1"/>
       <c r="K7246" s="1"/>
     </row>
-    <row r="7247" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7247" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7247" s="2"/>
       <c r="I7247" s="1"/>
       <c r="K7247" s="1"/>
     </row>
-    <row r="7248" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7248" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7248" s="2"/>
       <c r="I7248" s="1"/>
       <c r="K7248" s="1"/>
     </row>
     <row r="7249" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7249" s="2"/>
       <c r="I7249" s="1"/>
       <c r="K7249" s="1"/>
     </row>
@@ -49979,49 +50074,62 @@
       <c r="K7250" s="1"/>
     </row>
     <row r="7251" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7251" s="2"/>
+      <c r="I7251" s="1"/>
       <c r="K7251" s="1"/>
     </row>
     <row r="7252" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7252" s="2"/>
       <c r="I7252" s="1"/>
       <c r="K7252" s="1"/>
     </row>
     <row r="7253" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7253" s="2"/>
       <c r="I7253" s="1"/>
       <c r="K7253" s="1"/>
     </row>
     <row r="7254" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7254" s="2"/>
       <c r="I7254" s="1"/>
       <c r="K7254" s="1"/>
     </row>
     <row r="7255" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7255" s="2"/>
       <c r="I7255" s="1"/>
       <c r="K7255" s="1"/>
     </row>
     <row r="7256" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7256" s="2"/>
       <c r="I7256" s="1"/>
       <c r="K7256" s="1"/>
     </row>
     <row r="7257" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7257" s="2"/>
       <c r="I7257" s="1"/>
       <c r="K7257" s="1"/>
     </row>
     <row r="7258" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7258" s="2"/>
       <c r="I7258" s="1"/>
       <c r="K7258" s="1"/>
     </row>
     <row r="7259" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7259" s="2"/>
       <c r="I7259" s="1"/>
       <c r="K7259" s="1"/>
     </row>
     <row r="7260" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7260" s="2"/>
       <c r="I7260" s="1"/>
       <c r="K7260" s="1"/>
     </row>
     <row r="7261" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7261" s="2"/>
       <c r="I7261" s="1"/>
       <c r="K7261" s="1"/>
     </row>
     <row r="7262" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7262" s="2"/>
       <c r="I7262" s="1"/>
       <c r="K7262" s="1"/>
     </row>
@@ -50036,59 +50144,73 @@
       <c r="I7264" s="1"/>
     </row>
     <row r="7265" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7265" s="2"/>
       <c r="I7265" s="1"/>
       <c r="J7265" s="2"/>
       <c r="K7265" s="1"/>
     </row>
     <row r="7266" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7266" s="2"/>
       <c r="I7266" s="1"/>
       <c r="K7266" s="1"/>
     </row>
     <row r="7267" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7267" s="2"/>
       <c r="I7267" s="1"/>
       <c r="K7267" s="1"/>
     </row>
     <row r="7268" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7268" s="2"/>
       <c r="I7268" s="1"/>
       <c r="K7268" s="1"/>
     </row>
     <row r="7269" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7269" s="2"/>
       <c r="I7269" s="1"/>
       <c r="K7269" s="1"/>
     </row>
     <row r="7270" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7270" s="2"/>
       <c r="I7270" s="1"/>
       <c r="K7270" s="1"/>
     </row>
     <row r="7271" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7271" s="2"/>
       <c r="I7271" s="1"/>
       <c r="K7271" s="1"/>
     </row>
     <row r="7272" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7272" s="2"/>
       <c r="I7272" s="1"/>
       <c r="K7272" s="1"/>
     </row>
     <row r="7273" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7273" s="2"/>
       <c r="I7273" s="1"/>
       <c r="K7273" s="1"/>
     </row>
     <row r="7274" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7274" s="2"/>
       <c r="I7274" s="1"/>
       <c r="K7274" s="1"/>
     </row>
     <row r="7275" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7275" s="2"/>
       <c r="I7275" s="1"/>
       <c r="K7275" s="1"/>
     </row>
     <row r="7276" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7276" s="2"/>
       <c r="I7276" s="1"/>
       <c r="K7276" s="1"/>
     </row>
     <row r="7277" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7277" s="2"/>
       <c r="I7277" s="1"/>
       <c r="K7277" s="1"/>
     </row>
     <row r="7278" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7278" s="2"/>
       <c r="I7278" s="1"/>
       <c r="K7278" s="1"/>
     </row>
@@ -50098,31 +50220,38 @@
       <c r="K7279" s="1"/>
     </row>
     <row r="7280" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7280" s="2"/>
       <c r="I7280" s="1"/>
       <c r="J7280" s="2"/>
       <c r="K7280" s="1"/>
     </row>
     <row r="7281" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7281" s="2"/>
       <c r="I7281" s="1"/>
       <c r="K7281" s="1"/>
     </row>
     <row r="7282" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7282" s="2"/>
       <c r="I7282" s="1"/>
       <c r="K7282" s="1"/>
     </row>
     <row r="7283" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7283" s="2"/>
       <c r="I7283" s="1"/>
       <c r="K7283" s="1"/>
     </row>
     <row r="7284" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7284" s="2"/>
       <c r="I7284" s="1"/>
       <c r="K7284" s="1"/>
     </row>
     <row r="7285" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7285" s="2"/>
       <c r="I7285" s="1"/>
       <c r="K7285" s="1"/>
     </row>
     <row r="7286" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7286" s="2"/>
       <c r="I7286" s="1"/>
       <c r="K7286" s="1"/>
     </row>
@@ -50132,99 +50261,123 @@
       <c r="K7287" s="1"/>
     </row>
     <row r="7288" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7288" s="2"/>
       <c r="I7288" s="1"/>
       <c r="J7288" s="2"/>
       <c r="K7288" s="1"/>
     </row>
     <row r="7289" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7289" s="2"/>
       <c r="I7289" s="1"/>
       <c r="K7289" s="1"/>
     </row>
     <row r="7290" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7290" s="2"/>
       <c r="I7290" s="1"/>
       <c r="K7290" s="1"/>
     </row>
     <row r="7291" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7291" s="2"/>
       <c r="I7291" s="1"/>
       <c r="K7291" s="1"/>
     </row>
     <row r="7292" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7292" s="2"/>
       <c r="I7292" s="1"/>
       <c r="K7292" s="1"/>
     </row>
     <row r="7293" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7293" s="2"/>
       <c r="I7293" s="1"/>
       <c r="K7293" s="1"/>
     </row>
     <row r="7294" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7294" s="2"/>
       <c r="I7294" s="1"/>
       <c r="K7294" s="1"/>
     </row>
     <row r="7295" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7295" s="2"/>
       <c r="I7295" s="1"/>
       <c r="K7295" s="1"/>
     </row>
     <row r="7296" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7296" s="2"/>
       <c r="I7296" s="1"/>
       <c r="K7296" s="1"/>
     </row>
     <row r="7297" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7297" s="2"/>
       <c r="I7297" s="1"/>
       <c r="K7297" s="1"/>
     </row>
     <row r="7298" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7298" s="2"/>
       <c r="I7298" s="1"/>
       <c r="K7298" s="1"/>
     </row>
     <row r="7299" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7299" s="2"/>
       <c r="I7299" s="1"/>
       <c r="K7299" s="1"/>
     </row>
     <row r="7300" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7300" s="2"/>
       <c r="I7300" s="1"/>
       <c r="K7300" s="1"/>
     </row>
     <row r="7301" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7301" s="2"/>
       <c r="I7301" s="1"/>
       <c r="K7301" s="1"/>
     </row>
     <row r="7302" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7302" s="2"/>
       <c r="I7302" s="1"/>
       <c r="K7302" s="1"/>
     </row>
     <row r="7303" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7303" s="2"/>
       <c r="I7303" s="1"/>
       <c r="K7303" s="1"/>
     </row>
     <row r="7304" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7304" s="2"/>
       <c r="I7304" s="1"/>
       <c r="K7304" s="1"/>
     </row>
     <row r="7305" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7305" s="2"/>
       <c r="I7305" s="1"/>
       <c r="K7305" s="1"/>
     </row>
     <row r="7306" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7306" s="2"/>
       <c r="I7306" s="1"/>
       <c r="K7306" s="1"/>
     </row>
     <row r="7307" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7307" s="2"/>
       <c r="I7307" s="1"/>
       <c r="K7307" s="1"/>
     </row>
     <row r="7308" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7308" s="2"/>
       <c r="I7308" s="1"/>
       <c r="K7308" s="1"/>
     </row>
     <row r="7309" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7309" s="2"/>
       <c r="I7309" s="1"/>
       <c r="K7309" s="1"/>
     </row>
     <row r="7310" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7310" s="2"/>
       <c r="I7310" s="1"/>
       <c r="K7310" s="1"/>
     </row>
     <row r="7311" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7311" s="2"/>
       <c r="I7311" s="1"/>
       <c r="K7311" s="1"/>
     </row>
@@ -50233,80 +50386,99 @@
       <c r="I7312" s="1"/>
       <c r="K7312" s="1"/>
     </row>
-    <row r="7313" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7313" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7313" s="2"/>
       <c r="I7313" s="1"/>
       <c r="J7313" s="2"/>
       <c r="K7313" s="1"/>
     </row>
-    <row r="7314" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7314" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7314" s="2"/>
       <c r="I7314" s="1"/>
       <c r="K7314" s="1"/>
     </row>
-    <row r="7315" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7315" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7315" s="2"/>
       <c r="I7315" s="1"/>
       <c r="K7315" s="1"/>
     </row>
-    <row r="7316" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7316" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7316" s="2"/>
       <c r="I7316" s="1"/>
       <c r="K7316" s="1"/>
     </row>
-    <row r="7317" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7317" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7317" s="2"/>
       <c r="I7317" s="1"/>
       <c r="K7317" s="1"/>
     </row>
-    <row r="7318" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7318" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7318" s="2"/>
       <c r="I7318" s="1"/>
       <c r="K7318" s="1"/>
     </row>
-    <row r="7319" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7319" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7319" s="2"/>
       <c r="I7319" s="1"/>
       <c r="K7319" s="1"/>
     </row>
-    <row r="7320" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7320" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7320" s="2"/>
       <c r="I7320" s="1"/>
       <c r="K7320" s="1"/>
     </row>
-    <row r="7321" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7321" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7321" s="2"/>
       <c r="I7321" s="1"/>
       <c r="K7321" s="1"/>
     </row>
-    <row r="7322" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7322" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7322" s="2"/>
       <c r="I7322" s="1"/>
       <c r="K7322" s="1"/>
     </row>
-    <row r="7323" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7323" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7323" s="2"/>
       <c r="I7323" s="1"/>
       <c r="K7323" s="1"/>
     </row>
-    <row r="7324" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7324" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7324" s="2"/>
       <c r="I7324" s="1"/>
       <c r="K7324" s="1"/>
     </row>
-    <row r="7325" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7325" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7325" s="2"/>
       <c r="I7325" s="1"/>
       <c r="K7325" s="1"/>
     </row>
-    <row r="7326" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7326" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7326" s="2"/>
       <c r="I7326" s="1"/>
       <c r="K7326" s="1"/>
     </row>
-    <row r="7327" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7327" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7327" s="2"/>
       <c r="I7327" s="1"/>
       <c r="K7327" s="1"/>
     </row>
-    <row r="7328" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7328" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7328" s="2"/>
       <c r="I7328" s="1"/>
       <c r="K7328" s="1"/>
     </row>
     <row r="7329" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7329" s="2"/>
       <c r="I7329" s="1"/>
       <c r="K7329" s="1"/>
     </row>
     <row r="7330" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7330" s="2"/>
       <c r="I7330" s="1"/>
       <c r="K7330" s="1"/>
     </row>
     <row r="7331" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7331" s="2"/>
       <c r="I7331" s="1"/>
       <c r="K7331" s="1"/>
     </row>
@@ -50316,67 +50488,83 @@
       <c r="K7332" s="1"/>
     </row>
     <row r="7333" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7333" s="2"/>
       <c r="I7333" s="1"/>
       <c r="J7333" s="2"/>
       <c r="K7333" s="1"/>
     </row>
     <row r="7334" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7334" s="2"/>
       <c r="I7334" s="1"/>
       <c r="K7334" s="1"/>
     </row>
     <row r="7335" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7335" s="2"/>
       <c r="I7335" s="1"/>
       <c r="K7335" s="1"/>
     </row>
     <row r="7336" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7336" s="2"/>
       <c r="I7336" s="1"/>
       <c r="K7336" s="1"/>
     </row>
     <row r="7337" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7337" s="2"/>
       <c r="I7337" s="1"/>
       <c r="K7337" s="1"/>
     </row>
     <row r="7338" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7338" s="2"/>
       <c r="I7338" s="1"/>
       <c r="K7338" s="1"/>
     </row>
     <row r="7339" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7339" s="2"/>
       <c r="I7339" s="1"/>
       <c r="K7339" s="1"/>
     </row>
     <row r="7340" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7340" s="2"/>
       <c r="I7340" s="1"/>
       <c r="K7340" s="1"/>
     </row>
     <row r="7341" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7341" s="2"/>
       <c r="I7341" s="1"/>
       <c r="K7341" s="1"/>
     </row>
     <row r="7342" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7342" s="2"/>
       <c r="I7342" s="1"/>
       <c r="K7342" s="1"/>
     </row>
     <row r="7343" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7343" s="2"/>
       <c r="I7343" s="1"/>
       <c r="K7343" s="1"/>
     </row>
     <row r="7344" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7344" s="2"/>
       <c r="I7344" s="1"/>
       <c r="K7344" s="1"/>
     </row>
     <row r="7345" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7345" s="2"/>
       <c r="I7345" s="1"/>
       <c r="K7345" s="1"/>
     </row>
     <row r="7346" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7346" s="2"/>
       <c r="I7346" s="1"/>
       <c r="K7346" s="1"/>
     </row>
     <row r="7347" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7347" s="2"/>
       <c r="I7347" s="1"/>
       <c r="K7347" s="1"/>
     </row>
     <row r="7348" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7348" s="2"/>
       <c r="I7348" s="1"/>
       <c r="K7348" s="1"/>
     </row>
@@ -50386,31 +50574,38 @@
       <c r="K7349" s="1"/>
     </row>
     <row r="7350" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7350" s="2"/>
       <c r="I7350" s="1"/>
       <c r="J7350" s="2"/>
       <c r="K7350" s="1"/>
     </row>
     <row r="7351" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7351" s="2"/>
       <c r="I7351" s="1"/>
       <c r="K7351" s="1"/>
     </row>
     <row r="7352" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7352" s="2"/>
       <c r="I7352" s="1"/>
       <c r="K7352" s="1"/>
     </row>
     <row r="7353" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7353" s="2"/>
       <c r="I7353" s="1"/>
       <c r="K7353" s="1"/>
     </row>
     <row r="7354" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7354" s="2"/>
       <c r="I7354" s="1"/>
       <c r="K7354" s="1"/>
     </row>
     <row r="7355" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7355" s="2"/>
       <c r="I7355" s="1"/>
       <c r="K7355" s="1"/>
     </row>
     <row r="7356" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7356" s="2"/>
       <c r="I7356" s="1"/>
       <c r="K7356" s="1"/>
     </row>
@@ -50420,6 +50615,7 @@
       <c r="K7357" s="1"/>
     </row>
     <row r="7358" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7358" s="2"/>
       <c r="I7358" s="1"/>
       <c r="J7358" s="2"/>
       <c r="K7358" s="1"/>
@@ -50430,19 +50626,23 @@
       <c r="K7359" s="1"/>
     </row>
     <row r="7360" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7360" s="2"/>
       <c r="I7360" s="1"/>
       <c r="J7360" s="2"/>
       <c r="K7360" s="1"/>
     </row>
     <row r="7361" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7361" s="2"/>
       <c r="I7361" s="1"/>
       <c r="K7361" s="1"/>
     </row>
     <row r="7362" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7362" s="2"/>
       <c r="I7362" s="1"/>
       <c r="K7362" s="1"/>
     </row>
     <row r="7363" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7363" s="2"/>
       <c r="I7363" s="1"/>
       <c r="K7363" s="1"/>
     </row>
@@ -50452,90 +50652,112 @@
       <c r="K7364" s="1"/>
     </row>
     <row r="7365" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7365" s="2"/>
       <c r="I7365" s="1"/>
       <c r="J7365" s="2"/>
       <c r="K7365" s="1"/>
     </row>
     <row r="7366" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7366" s="2"/>
       <c r="I7366" s="1"/>
     </row>
     <row r="7367" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7367" s="2"/>
       <c r="I7367" s="1"/>
       <c r="K7367" s="1"/>
     </row>
     <row r="7368" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7368" s="2"/>
       <c r="I7368" s="1"/>
       <c r="K7368" s="1"/>
     </row>
     <row r="7369" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7369" s="2"/>
       <c r="I7369" s="1"/>
       <c r="K7369" s="1"/>
     </row>
     <row r="7370" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7370" s="2"/>
       <c r="I7370" s="1"/>
       <c r="K7370" s="1"/>
     </row>
     <row r="7371" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7371" s="2"/>
       <c r="I7371" s="1"/>
       <c r="K7371" s="1"/>
     </row>
     <row r="7372" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7372" s="2"/>
       <c r="I7372" s="1"/>
       <c r="K7372" s="1"/>
     </row>
     <row r="7373" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7373" s="2"/>
       <c r="I7373" s="1"/>
       <c r="K7373" s="1"/>
     </row>
     <row r="7374" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7374" s="2"/>
       <c r="I7374" s="1"/>
       <c r="K7374" s="1"/>
     </row>
     <row r="7375" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7375" s="2"/>
       <c r="I7375" s="1"/>
       <c r="K7375" s="1"/>
     </row>
     <row r="7376" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7376" s="2"/>
       <c r="I7376" s="1"/>
       <c r="K7376" s="1"/>
     </row>
     <row r="7377" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7377" s="2"/>
       <c r="I7377" s="1"/>
       <c r="K7377" s="1"/>
     </row>
     <row r="7378" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7378" s="2"/>
       <c r="I7378" s="1"/>
       <c r="K7378" s="1"/>
     </row>
     <row r="7379" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7379" s="2"/>
       <c r="I7379" s="1"/>
       <c r="K7379" s="1"/>
     </row>
     <row r="7380" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7380" s="2"/>
       <c r="I7380" s="1"/>
       <c r="K7380" s="1"/>
     </row>
     <row r="7381" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7381" s="2"/>
       <c r="I7381" s="1"/>
       <c r="K7381" s="1"/>
     </row>
     <row r="7382" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7382" s="2"/>
       <c r="I7382" s="1"/>
       <c r="K7382" s="1"/>
     </row>
     <row r="7383" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7383" s="2"/>
       <c r="I7383" s="1"/>
       <c r="K7383" s="1"/>
     </row>
     <row r="7384" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7384" s="2"/>
       <c r="I7384" s="1"/>
       <c r="K7384" s="1"/>
     </row>
     <row r="7385" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7385" s="2"/>
       <c r="I7385" s="1"/>
       <c r="K7385" s="1"/>
     </row>
     <row r="7386" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7386" s="2"/>
       <c r="I7386" s="1"/>
       <c r="K7386" s="1"/>
     </row>
@@ -50545,51 +50767,71 @@
       <c r="K7387" s="1"/>
     </row>
     <row r="7388" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7388" s="2"/>
       <c r="I7388" s="1"/>
       <c r="K7388" s="1"/>
     </row>
     <row r="7389" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7389" s="2"/>
       <c r="I7389" s="1"/>
       <c r="J7389" s="2"/>
       <c r="K7389" s="1"/>
     </row>
     <row r="7390" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7390" s="2"/>
       <c r="I7390" s="1"/>
     </row>
     <row r="7391" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7391" s="2"/>
       <c r="I7391" s="1"/>
       <c r="K7391" s="1"/>
     </row>
     <row r="7392" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7392" s="2"/>
       <c r="I7392" s="1"/>
       <c r="K7392" s="1"/>
     </row>
-    <row r="7393" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7393" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7393" s="2"/>
       <c r="I7393" s="1"/>
       <c r="K7393" s="1"/>
     </row>
-    <row r="7394" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7394" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7394" s="2"/>
+      <c r="I7394" s="1"/>
       <c r="K7394" s="1"/>
     </row>
-    <row r="7395" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7395" spans="8:11" x14ac:dyDescent="0.25">
       <c r="I7395" s="1"/>
       <c r="K7395" s="1"/>
     </row>
-    <row r="7396" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7396" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7396" s="2"/>
       <c r="I7396" s="1"/>
       <c r="K7396" s="1"/>
     </row>
-    <row r="7397" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7397" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7397" s="2"/>
       <c r="I7397" s="1"/>
     </row>
-    <row r="7398" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7398" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7398" s="2"/>
+      <c r="I7398" s="1"/>
       <c r="K7398" s="1"/>
     </row>
-    <row r="7399" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7399" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7399" s="2"/>
+      <c r="I7399" s="1"/>
       <c r="K7399" s="1"/>
     </row>
-    <row r="7400" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="7400" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7400" s="2"/>
+      <c r="I7400" s="1"/>
       <c r="K7400" s="1"/>
+    </row>
+    <row r="7401" spans="8:11" x14ac:dyDescent="0.25">
+      <c r="H7401" s="2"/>
+      <c r="I7401" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
